--- a/research/traditional_assets/database/data/hong_kong/hong_kong_air_transport.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sehk_293" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.185</v>
+        <v>-0.123</v>
       </c>
       <c r="G2">
-        <v>-0.1118457422108219</v>
+        <v>0.1330754603520291</v>
       </c>
       <c r="H2">
-        <v>-0.1118457422108219</v>
+        <v>0.1330754603520291</v>
       </c>
       <c r="I2">
-        <v>-0.2837936448267475</v>
+        <v>0.05631490841716914</v>
       </c>
       <c r="J2">
-        <v>-0.2837936448267475</v>
+        <v>0.05631490841716914</v>
       </c>
       <c r="K2">
-        <v>-2491.4</v>
+        <v>-377.3</v>
       </c>
       <c r="L2">
-        <v>-0.550914357738319</v>
+        <v>-0.06132067805425084</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1188.5</v>
+        <v>802.8</v>
       </c>
       <c r="V2">
-        <v>0.2253037857102235</v>
+        <v>0.1141329845462688</v>
       </c>
       <c r="W2">
-        <v>-0.3911084598357953</v>
+        <v>-0.05815620327697027</v>
       </c>
       <c r="X2">
-        <v>0.1454064954518086</v>
+        <v>0.1593394545263018</v>
       </c>
       <c r="Y2">
-        <v>-0.536514955287604</v>
+        <v>-0.2174956578032721</v>
       </c>
       <c r="Z2">
-        <v>0.2654882322897281</v>
+        <v>0.2998591569887861</v>
       </c>
       <c r="AA2">
-        <v>-0.07534387310011213</v>
+        <v>0.01688654096387304</v>
       </c>
       <c r="AB2">
-        <v>0.05946125997440974</v>
+        <v>0.0909694013586252</v>
       </c>
       <c r="AC2">
-        <v>-0.1348051330745219</v>
+        <v>-0.07408286039475218</v>
       </c>
       <c r="AD2">
-        <v>12709.1</v>
+        <v>10604.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12709.1</v>
+        <v>10604.4</v>
       </c>
       <c r="AG2">
-        <v>11520.6</v>
+        <v>9801.6</v>
       </c>
       <c r="AH2">
-        <v>0.7066814203578696</v>
+        <v>0.6012144027485642</v>
       </c>
       <c r="AI2">
-        <v>0.5854461867295608</v>
+        <v>0.5487115802545793</v>
       </c>
       <c r="AJ2">
-        <v>0.6859255642813339</v>
+        <v>0.582198330907903</v>
       </c>
       <c r="AK2">
-        <v>0.5614354845783849</v>
+        <v>0.5291526302150816</v>
       </c>
       <c r="AL2">
-        <v>294.8</v>
+        <v>355.9</v>
       </c>
       <c r="AM2">
-        <v>276.5</v>
+        <v>351.57</v>
       </c>
       <c r="AN2">
-        <v>-35.53005311713727</v>
+        <v>8.687146719095601</v>
       </c>
       <c r="AO2">
-        <v>-4.353459972862958</v>
+        <v>0.9735880865411634</v>
       </c>
       <c r="AP2">
-        <v>-32.20743639921722</v>
+        <v>8.029491275497666</v>
       </c>
       <c r="AQ2">
-        <v>-4.641591320072333</v>
+        <v>0.9855789743152146</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.185</v>
+        <v>-0.123</v>
       </c>
       <c r="G3">
-        <v>-0.1118457422108219</v>
+        <v>0.1330754603520291</v>
       </c>
       <c r="H3">
-        <v>-0.1118457422108219</v>
+        <v>0.1330754603520291</v>
       </c>
       <c r="I3">
-        <v>-0.2837936448267475</v>
+        <v>0.05631490841716914</v>
       </c>
       <c r="J3">
-        <v>-0.2837936448267475</v>
+        <v>0.05631490841716914</v>
       </c>
       <c r="K3">
-        <v>-2491.4</v>
+        <v>-377.3</v>
       </c>
       <c r="L3">
-        <v>-0.550914357738319</v>
+        <v>-0.06132067805425084</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8774 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1188.5</v>
+        <v>802.8</v>
       </c>
       <c r="V3">
-        <v>0.2253037857102235</v>
+        <v>0.1141329845462688</v>
       </c>
       <c r="W3">
-        <v>-0.3911084598357953</v>
+        <v>-0.05815620327697027</v>
       </c>
       <c r="X3">
-        <v>0.1454064954518086</v>
+        <v>0.1593394545263018</v>
       </c>
       <c r="Y3">
-        <v>-0.536514955287604</v>
+        <v>-0.2174956578032721</v>
       </c>
       <c r="Z3">
-        <v>0.2654882322897281</v>
+        <v>0.2998591569887861</v>
       </c>
       <c r="AA3">
-        <v>-0.07534387310011213</v>
+        <v>0.01688654096387304</v>
       </c>
       <c r="AB3">
-        <v>0.05946125997440974</v>
+        <v>0.0909694013586252</v>
       </c>
       <c r="AC3">
-        <v>-0.1348051330745219</v>
+        <v>-0.07408286039475218</v>
       </c>
       <c r="AD3">
-        <v>12709.1</v>
+        <v>10604.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>12709.1</v>
+        <v>10604.4</v>
       </c>
       <c r="AG3">
-        <v>11520.6</v>
+        <v>9801.6</v>
       </c>
       <c r="AH3">
-        <v>0.7066814203578696</v>
+        <v>0.6012144027485642</v>
       </c>
       <c r="AI3">
-        <v>0.5854461867295608</v>
+        <v>0.5487115802545793</v>
       </c>
       <c r="AJ3">
-        <v>0.6859255642813339</v>
+        <v>0.582198330907903</v>
       </c>
       <c r="AK3">
-        <v>0.5614354845783849</v>
+        <v>0.5291526302150816</v>
       </c>
       <c r="AL3">
-        <v>294.8</v>
+        <v>355.9</v>
       </c>
       <c r="AM3">
-        <v>276.5</v>
+        <v>351.57</v>
       </c>
       <c r="AN3">
-        <v>-35.53005311713727</v>
+        <v>8.687146719095601</v>
       </c>
       <c r="AO3">
-        <v>-4.353459972862958</v>
+        <v>0.9735880865411634</v>
       </c>
       <c r="AP3">
-        <v>-32.20743639921722</v>
+        <v>8.029491275497666</v>
       </c>
       <c r="AQ3">
-        <v>-4.641591320072333</v>
+        <v>0.9855789743152146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cathay Pacific Airways Limited (SEHK:293)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SEHK:293</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.601214402748564</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>7033.9</v>
+      </c>
+      <c r="H2">
+        <v>15522.0082044566</v>
+      </c>
+      <c r="I2">
+        <v>16835.5</v>
+      </c>
+      <c r="J2">
+        <v>14895.5912044566</v>
+      </c>
+      <c r="K2">
+        <v>10604.4</v>
+      </c>
+      <c r="L2">
+        <v>176.383</v>
+      </c>
+      <c r="M2">
+        <v>0.0909694013586252</v>
+      </c>
+      <c r="N2">
+        <v>0.0985396229402374</v>
+      </c>
+      <c r="O2">
+        <v>0.0456195355504587</v>
+      </c>
+      <c r="P2">
+        <v>0.596521549128884</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.159339454526302</v>
+      </c>
+      <c r="T2">
+        <v>0.0935095024736854</v>
+      </c>
+      <c r="U2">
+        <v>1.73467591474432</v>
+      </c>
+      <c r="V2">
+        <v>0.787321102635641</v>
+      </c>
+      <c r="W2">
+        <v>-9.078766284170451</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>7033.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.06948816980840411</v>
+      </c>
+      <c r="AC2">
+        <v>0.0546341743119266</v>
+      </c>
+      <c r="AD2">
+        <v>0.165</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1220.7</v>
+      </c>
+      <c r="AH2">
+        <v>1603.1</v>
+      </c>
+      <c r="AI2">
+        <v>336.2999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>10604.4</v>
+      </c>
+      <c r="AK2">
+        <v>10604.4</v>
+      </c>
+      <c r="AL2">
+        <v>355.9</v>
+      </c>
+      <c r="AM2">
+        <v>10604.4</v>
+      </c>
+      <c r="AN2">
+        <v>802.8</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-10604.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>802.8</v>
+      </c>
+      <c r="H2">
+        <v>7033.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1220.7</v>
+      </c>
+      <c r="K2">
+        <v>1603.1</v>
+      </c>
+      <c r="L2">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="O2">
+        <v>-63.09599999999999</v>
+      </c>
+      <c r="P2">
+        <v>-319.3039999999999</v>
+      </c>
+      <c r="Q2">
+        <v>1283.796</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09853962294023741</v>
+      </c>
+      <c r="C3">
+        <v>15522.00820445662</v>
+      </c>
+      <c r="D3">
+        <v>14895.59120445662</v>
+      </c>
+      <c r="E3">
+        <v>-10428.017</v>
+      </c>
+      <c r="F3">
+        <v>176.383</v>
+      </c>
+      <c r="G3">
+        <v>802.8</v>
+      </c>
+      <c r="H3">
+        <v>7033.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1220.7</v>
+      </c>
+      <c r="K3">
+        <v>1603.1</v>
+      </c>
+      <c r="L3">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M3">
+        <v>42.12026040000001</v>
+      </c>
+      <c r="N3">
+        <v>-424.5202603999999</v>
+      </c>
+      <c r="O3">
+        <v>-70.045842966</v>
+      </c>
+      <c r="P3">
+        <v>-354.4744174339999</v>
+      </c>
+      <c r="Q3">
+        <v>1248.625582566</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09350950247368542</v>
+      </c>
+      <c r="T3">
+        <v>0.7873211026356415</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-1.497996436888125</v>
+      </c>
+      <c r="W3">
+        <v>0.5965215491288841</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-9.078766284170451</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1005396229402374</v>
+      </c>
+      <c r="C4">
+        <v>14905.56632717559</v>
+      </c>
+      <c r="D4">
+        <v>14455.53232717559</v>
+      </c>
+      <c r="E4">
+        <v>-10251.634</v>
+      </c>
+      <c r="F4">
+        <v>352.766</v>
+      </c>
+      <c r="G4">
+        <v>802.8</v>
+      </c>
+      <c r="H4">
+        <v>7033.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1220.7</v>
+      </c>
+      <c r="K4">
+        <v>1603.1</v>
+      </c>
+      <c r="L4">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M4">
+        <v>84.24052080000001</v>
+      </c>
+      <c r="N4">
+        <v>-466.6405207999999</v>
+      </c>
+      <c r="O4">
+        <v>-76.995685932</v>
+      </c>
+      <c r="P4">
+        <v>-389.6448348679999</v>
+      </c>
+      <c r="Q4">
+        <v>1213.455165132</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09406776270300873</v>
+      </c>
+      <c r="T4">
+        <v>0.7953549914380459</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-0.7489982184440623</v>
+      </c>
+      <c r="W4">
+        <v>0.4176607745644421</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-4.539383142085225</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1025396229402374</v>
+      </c>
+      <c r="C5">
+        <v>14314.37956649433</v>
+      </c>
+      <c r="D5">
+        <v>14040.72856649433</v>
+      </c>
+      <c r="E5">
+        <v>-10075.251</v>
+      </c>
+      <c r="F5">
+        <v>529.149</v>
+      </c>
+      <c r="G5">
+        <v>802.8</v>
+      </c>
+      <c r="H5">
+        <v>7033.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1220.7</v>
+      </c>
+      <c r="K5">
+        <v>1603.1</v>
+      </c>
+      <c r="L5">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M5">
+        <v>126.3607812</v>
+      </c>
+      <c r="N5">
+        <v>-508.7607811999999</v>
+      </c>
+      <c r="O5">
+        <v>-83.94552889799999</v>
+      </c>
+      <c r="P5">
+        <v>-424.8152523019999</v>
+      </c>
+      <c r="Q5">
+        <v>1178.284747698</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09463753345252429</v>
+      </c>
+      <c r="T5">
+        <v>0.8035545274322526</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-0.499332145629375</v>
+      </c>
+      <c r="W5">
+        <v>0.3580405163762948</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-3.026255428056817</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1045396229402374</v>
+      </c>
+      <c r="C6">
+        <v>13746.33446970806</v>
+      </c>
+      <c r="D6">
+        <v>13649.06646970806</v>
+      </c>
+      <c r="E6">
+        <v>-9898.868</v>
+      </c>
+      <c r="F6">
+        <v>705.532</v>
+      </c>
+      <c r="G6">
+        <v>802.8</v>
+      </c>
+      <c r="H6">
+        <v>7033.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1220.7</v>
+      </c>
+      <c r="K6">
+        <v>1603.1</v>
+      </c>
+      <c r="L6">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M6">
+        <v>168.4810416</v>
+      </c>
+      <c r="N6">
+        <v>-550.8810415999999</v>
+      </c>
+      <c r="O6">
+        <v>-90.895371864</v>
+      </c>
+      <c r="P6">
+        <v>-459.9856697359999</v>
+      </c>
+      <c r="Q6">
+        <v>1143.114330264</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09521917442598808</v>
+      </c>
+      <c r="T6">
+        <v>0.8119248870930053</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-0.3744991092220312</v>
+      </c>
+      <c r="W6">
+        <v>0.328230387282221</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-2.269691571042613</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1065396229402374</v>
+      </c>
+      <c r="C7">
+        <v>13199.54700121608</v>
+      </c>
+      <c r="D7">
+        <v>13278.66200121608</v>
+      </c>
+      <c r="E7">
+        <v>-9722.485000000001</v>
+      </c>
+      <c r="F7">
+        <v>881.915</v>
+      </c>
+      <c r="G7">
+        <v>802.8</v>
+      </c>
+      <c r="H7">
+        <v>7033.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1220.7</v>
+      </c>
+      <c r="K7">
+        <v>1603.1</v>
+      </c>
+      <c r="L7">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M7">
+        <v>210.601302</v>
+      </c>
+      <c r="N7">
+        <v>-593.0013019999999</v>
+      </c>
+      <c r="O7">
+        <v>-97.84521483</v>
+      </c>
+      <c r="P7">
+        <v>-495.1560871699999</v>
+      </c>
+      <c r="Q7">
+        <v>1107.94391283</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09581306047257743</v>
+      </c>
+      <c r="T7">
+        <v>0.8204714648518789</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.299599287377625</v>
+      </c>
+      <c r="W7">
+        <v>0.3103443098257769</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-1.815753256834091</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1085396229402374</v>
+      </c>
+      <c r="C8">
+        <v>12672.33223570035</v>
+      </c>
+      <c r="D8">
+        <v>12927.83023570035</v>
+      </c>
+      <c r="E8">
+        <v>-9546.101999999999</v>
+      </c>
+      <c r="F8">
+        <v>1058.298</v>
+      </c>
+      <c r="G8">
+        <v>802.8</v>
+      </c>
+      <c r="H8">
+        <v>7033.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1220.7</v>
+      </c>
+      <c r="K8">
+        <v>1603.1</v>
+      </c>
+      <c r="L8">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M8">
+        <v>252.7215624</v>
+      </c>
+      <c r="N8">
+        <v>-635.1215623999999</v>
+      </c>
+      <c r="O8">
+        <v>-104.795057796</v>
+      </c>
+      <c r="P8">
+        <v>-530.3265046039999</v>
+      </c>
+      <c r="Q8">
+        <v>1072.773495396</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09641958239249848</v>
+      </c>
+      <c r="T8">
+        <v>0.8291998846907289</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.2496660728146875</v>
+      </c>
+      <c r="W8">
+        <v>0.2984202581881474</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-1.513127714028409</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1105396229402374</v>
+      </c>
+      <c r="C9">
+        <v>12163.17873200425</v>
+      </c>
+      <c r="D9">
+        <v>12595.05973200425</v>
+      </c>
+      <c r="E9">
+        <v>-9369.718999999999</v>
+      </c>
+      <c r="F9">
+        <v>1234.681</v>
+      </c>
+      <c r="G9">
+        <v>802.8</v>
+      </c>
+      <c r="H9">
+        <v>7033.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1220.7</v>
+      </c>
+      <c r="K9">
+        <v>1603.1</v>
+      </c>
+      <c r="L9">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M9">
+        <v>294.8418228</v>
+      </c>
+      <c r="N9">
+        <v>-677.2418227999999</v>
+      </c>
+      <c r="O9">
+        <v>-111.744900762</v>
+      </c>
+      <c r="P9">
+        <v>-565.4969220379999</v>
+      </c>
+      <c r="Q9">
+        <v>1037.603077962</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09703914779456835</v>
+      </c>
+      <c r="T9">
+        <v>0.8381160124831022</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.2139994909840178</v>
+      </c>
+      <c r="W9">
+        <v>0.2899030784469834</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-1.29696661202435</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1125396229402374</v>
+      </c>
+      <c r="C10">
+        <v>11670.7267654868</v>
+      </c>
+      <c r="D10">
+        <v>12278.9907654868</v>
+      </c>
+      <c r="E10">
+        <v>-9193.335999999999</v>
+      </c>
+      <c r="F10">
+        <v>1411.064</v>
+      </c>
+      <c r="G10">
+        <v>802.8</v>
+      </c>
+      <c r="H10">
+        <v>7033.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1220.7</v>
+      </c>
+      <c r="K10">
+        <v>1603.1</v>
+      </c>
+      <c r="L10">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M10">
+        <v>336.9620832000001</v>
+      </c>
+      <c r="N10">
+        <v>-719.3620831999999</v>
+      </c>
+      <c r="O10">
+        <v>-118.694743728</v>
+      </c>
+      <c r="P10">
+        <v>-600.6673394719999</v>
+      </c>
+      <c r="Q10">
+        <v>1002.432660528</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09767218200972669</v>
+      </c>
+      <c r="T10">
+        <v>0.8472259691405272</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.1872495546110156</v>
+      </c>
+      <c r="W10">
+        <v>0.2835151936411106</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-1.134845785521307</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1145396229402374</v>
+      </c>
+      <c r="C11">
+        <v>11193.74975765468</v>
+      </c>
+      <c r="D11">
+        <v>11978.39675765468</v>
+      </c>
+      <c r="E11">
+        <v>-9016.953</v>
+      </c>
+      <c r="F11">
+        <v>1587.447</v>
+      </c>
+      <c r="G11">
+        <v>802.8</v>
+      </c>
+      <c r="H11">
+        <v>7033.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1220.7</v>
+      </c>
+      <c r="K11">
+        <v>1603.1</v>
+      </c>
+      <c r="L11">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M11">
+        <v>379.0823436</v>
+      </c>
+      <c r="N11">
+        <v>-761.4823435999999</v>
+      </c>
+      <c r="O11">
+        <v>-125.644586694</v>
+      </c>
+      <c r="P11">
+        <v>-635.8377569059999</v>
+      </c>
+      <c r="Q11">
+        <v>967.262243094</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09831912906477865</v>
+      </c>
+      <c r="T11">
+        <v>0.856536144625588</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.166444048543125</v>
+      </c>
+      <c r="W11">
+        <v>0.2785468387920982</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-1.008751809352272</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1165396229402374</v>
+      </c>
+      <c r="C12">
+        <v>10731.13836827069</v>
+      </c>
+      <c r="D12">
+        <v>11692.16836827069</v>
+      </c>
+      <c r="E12">
+        <v>-8840.57</v>
+      </c>
+      <c r="F12">
+        <v>1763.83</v>
+      </c>
+      <c r="G12">
+        <v>802.8</v>
+      </c>
+      <c r="H12">
+        <v>7033.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1220.7</v>
+      </c>
+      <c r="K12">
+        <v>1603.1</v>
+      </c>
+      <c r="L12">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M12">
+        <v>421.202604</v>
+      </c>
+      <c r="N12">
+        <v>-803.6026039999999</v>
+      </c>
+      <c r="O12">
+        <v>-132.59442966</v>
+      </c>
+      <c r="P12">
+        <v>-671.0081743399999</v>
+      </c>
+      <c r="Q12">
+        <v>932.09182566</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09898045272105396</v>
+      </c>
+      <c r="T12">
+        <v>0.8660532128992056</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.1497996436888125</v>
+      </c>
+      <c r="W12">
+        <v>0.2745721549128884</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-0.9078766284170454</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1185396229402374</v>
+      </c>
+      <c r="C13">
+        <v>10281.88681498558</v>
+      </c>
+      <c r="D13">
+        <v>11419.29981498558</v>
+      </c>
+      <c r="E13">
+        <v>-8664.187</v>
+      </c>
+      <c r="F13">
+        <v>1940.213</v>
+      </c>
+      <c r="G13">
+        <v>802.8</v>
+      </c>
+      <c r="H13">
+        <v>7033.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1220.7</v>
+      </c>
+      <c r="K13">
+        <v>1603.1</v>
+      </c>
+      <c r="L13">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M13">
+        <v>463.3228644</v>
+      </c>
+      <c r="N13">
+        <v>-845.7228643999999</v>
+      </c>
+      <c r="O13">
+        <v>-139.544272626</v>
+      </c>
+      <c r="P13">
+        <v>-706.1785917739999</v>
+      </c>
+      <c r="Q13">
+        <v>896.921408226</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09965663758308826</v>
+      </c>
+      <c r="T13">
+        <v>0.8757841478756012</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.1361814942625568</v>
+      </c>
+      <c r="W13">
+        <v>0.2713201408298986</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-0.8253423894700413</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1205396229402374</v>
+      </c>
+      <c r="C14">
+        <v>9845.081064895236</v>
+      </c>
+      <c r="D14">
+        <v>11158.87706489524</v>
+      </c>
+      <c r="E14">
+        <v>-8487.804</v>
+      </c>
+      <c r="F14">
+        <v>2116.596</v>
+      </c>
+      <c r="G14">
+        <v>802.8</v>
+      </c>
+      <c r="H14">
+        <v>7033.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1220.7</v>
+      </c>
+      <c r="K14">
+        <v>1603.1</v>
+      </c>
+      <c r="L14">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M14">
+        <v>505.4431248</v>
+      </c>
+      <c r="N14">
+        <v>-887.8431247999999</v>
+      </c>
+      <c r="O14">
+        <v>-146.494115592</v>
+      </c>
+      <c r="P14">
+        <v>-741.3490092079999</v>
+      </c>
+      <c r="Q14">
+        <v>861.750990792</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1003481902828961</v>
+      </c>
+      <c r="T14">
+        <v>0.8857362404650967</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.1248330364073438</v>
+      </c>
+      <c r="W14">
+        <v>0.2686101290940737</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-0.7565638570142044</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1225396229402374</v>
+      </c>
+      <c r="C15">
+        <v>9419.888605854703</v>
+      </c>
+      <c r="D15">
+        <v>10910.0676058547</v>
+      </c>
+      <c r="E15">
+        <v>-8311.421</v>
+      </c>
+      <c r="F15">
+        <v>2292.979</v>
+      </c>
+      <c r="G15">
+        <v>802.8</v>
+      </c>
+      <c r="H15">
+        <v>7033.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1220.7</v>
+      </c>
+      <c r="K15">
+        <v>1603.1</v>
+      </c>
+      <c r="L15">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M15">
+        <v>547.5633852</v>
+      </c>
+      <c r="N15">
+        <v>-929.9633851999998</v>
+      </c>
+      <c r="O15">
+        <v>-153.443958558</v>
+      </c>
+      <c r="P15">
+        <v>-776.5194266419999</v>
+      </c>
+      <c r="Q15">
+        <v>826.580573358</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1010556407459179</v>
+      </c>
+      <c r="T15">
+        <v>0.8959171167922817</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.1152304951452404</v>
+      </c>
+      <c r="W15">
+        <v>0.2663170422406834</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.698366637243881</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1245396229402374</v>
+      </c>
+      <c r="C16">
+        <v>9005.549556360114</v>
+      </c>
+      <c r="D16">
+        <v>10672.11155636011</v>
+      </c>
+      <c r="E16">
+        <v>-8135.038</v>
+      </c>
+      <c r="F16">
+        <v>2469.362</v>
+      </c>
+      <c r="G16">
+        <v>802.8</v>
+      </c>
+      <c r="H16">
+        <v>7033.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1220.7</v>
+      </c>
+      <c r="K16">
+        <v>1603.1</v>
+      </c>
+      <c r="L16">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M16">
+        <v>589.6836456000001</v>
+      </c>
+      <c r="N16">
+        <v>-972.0836456</v>
+      </c>
+      <c r="O16">
+        <v>-160.393801524</v>
+      </c>
+      <c r="P16">
+        <v>-811.6898440759999</v>
+      </c>
+      <c r="Q16">
+        <v>791.410155924</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.101779543545289</v>
+      </c>
+      <c r="T16">
+        <v>0.9063347576852152</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.1069997454920089</v>
+      </c>
+      <c r="W16">
+        <v>0.2643515392234917</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.6484833060121751</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1265396229402374</v>
+      </c>
+      <c r="C17">
+        <v>8601.368913995189</v>
+      </c>
+      <c r="D17">
+        <v>10444.31391399519</v>
+      </c>
+      <c r="E17">
+        <v>-7958.655</v>
+      </c>
+      <c r="F17">
+        <v>2645.745</v>
+      </c>
+      <c r="G17">
+        <v>802.8</v>
+      </c>
+      <c r="H17">
+        <v>7033.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1220.7</v>
+      </c>
+      <c r="K17">
+        <v>1603.1</v>
+      </c>
+      <c r="L17">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M17">
+        <v>631.803906</v>
+      </c>
+      <c r="N17">
+        <v>-1014.203906</v>
+      </c>
+      <c r="O17">
+        <v>-167.34364449</v>
+      </c>
+      <c r="P17">
+        <v>-846.8602615099999</v>
+      </c>
+      <c r="Q17">
+        <v>756.23973849</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1025204793517042</v>
+      </c>
+      <c r="T17">
+        <v>0.9169975195403354</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.09986642912587501</v>
+      </c>
+      <c r="W17">
+        <v>0.262648103275259</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.6052510856113635</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1285396229402374</v>
+      </c>
+      <c r="C18">
+        <v>8206.70977587786</v>
+      </c>
+      <c r="D18">
+        <v>10226.03777587786</v>
+      </c>
+      <c r="E18">
+        <v>-7782.271999999999</v>
+      </c>
+      <c r="F18">
+        <v>2822.128</v>
+      </c>
+      <c r="G18">
+        <v>802.8</v>
+      </c>
+      <c r="H18">
+        <v>7033.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1220.7</v>
+      </c>
+      <c r="K18">
+        <v>1603.1</v>
+      </c>
+      <c r="L18">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M18">
+        <v>673.9241664000001</v>
+      </c>
+      <c r="N18">
+        <v>-1056.3241664</v>
+      </c>
+      <c r="O18">
+        <v>-174.293487456</v>
+      </c>
+      <c r="P18">
+        <v>-882.0306789439999</v>
+      </c>
+      <c r="Q18">
+        <v>721.069321056</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1032790564868435</v>
+      </c>
+      <c r="T18">
+        <v>0.9279141566777204</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.09362477730550779</v>
+      </c>
+      <c r="W18">
+        <v>0.2611575968205553</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.5674228927606533</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1305396229402374</v>
+      </c>
+      <c r="C19">
+        <v>7820.987391820951</v>
+      </c>
+      <c r="D19">
+        <v>10016.69839182095</v>
+      </c>
+      <c r="E19">
+        <v>-7605.888999999999</v>
+      </c>
+      <c r="F19">
+        <v>2998.511</v>
+      </c>
+      <c r="G19">
+        <v>802.8</v>
+      </c>
+      <c r="H19">
+        <v>7033.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1220.7</v>
+      </c>
+      <c r="K19">
+        <v>1603.1</v>
+      </c>
+      <c r="L19">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M19">
+        <v>716.0444268</v>
+      </c>
+      <c r="N19">
+        <v>-1098.4444268</v>
+      </c>
+      <c r="O19">
+        <v>-181.243330422</v>
+      </c>
+      <c r="P19">
+        <v>-917.2010963779998</v>
+      </c>
+      <c r="Q19">
+        <v>685.8989036220001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1040559125890947</v>
+      </c>
+      <c r="T19">
+        <v>0.9390938453123917</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.08811743746400735</v>
+      </c>
+      <c r="W19">
+        <v>0.2598424440664049</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.5340450755394381</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1325396229402374</v>
+      </c>
+      <c r="C20">
+        <v>7443.663933274003</v>
+      </c>
+      <c r="D20">
+        <v>9815.757933274004</v>
+      </c>
+      <c r="E20">
+        <v>-7429.505999999999</v>
+      </c>
+      <c r="F20">
+        <v>3174.894</v>
+      </c>
+      <c r="G20">
+        <v>802.8</v>
+      </c>
+      <c r="H20">
+        <v>7033.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1220.7</v>
+      </c>
+      <c r="K20">
+        <v>1603.1</v>
+      </c>
+      <c r="L20">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M20">
+        <v>758.1646872</v>
+      </c>
+      <c r="N20">
+        <v>-1140.5646872</v>
+      </c>
+      <c r="O20">
+        <v>-188.193173388</v>
+      </c>
+      <c r="P20">
+        <v>-952.3715138119998</v>
+      </c>
+      <c r="Q20">
+        <v>650.7284861880001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1048517164011568</v>
+      </c>
+      <c r="T20">
+        <v>0.9505462092796159</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.0832220242715625</v>
+      </c>
+      <c r="W20">
+        <v>0.2586734193960491</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.504375904676136</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1345396229402374</v>
+      </c>
+      <c r="C21">
+        <v>7074.24387951017</v>
+      </c>
+      <c r="D21">
+        <v>9622.720879510171</v>
+      </c>
+      <c r="E21">
+        <v>-7253.123</v>
+      </c>
+      <c r="F21">
+        <v>3351.277</v>
+      </c>
+      <c r="G21">
+        <v>802.8</v>
+      </c>
+      <c r="H21">
+        <v>7033.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1220.7</v>
+      </c>
+      <c r="K21">
+        <v>1603.1</v>
+      </c>
+      <c r="L21">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M21">
+        <v>800.2849476</v>
+      </c>
+      <c r="N21">
+        <v>-1182.6849476</v>
+      </c>
+      <c r="O21">
+        <v>-195.143016354</v>
+      </c>
+      <c r="P21">
+        <v>-987.5419312459998</v>
+      </c>
+      <c r="Q21">
+        <v>615.5580687540001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.10566716969006</v>
+      </c>
+      <c r="T21">
+        <v>0.9622813476657841</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.07884191773095395</v>
+      </c>
+      <c r="W21">
+        <v>0.2576274499541518</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.4778298044300238</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1365396229402374</v>
+      </c>
+      <c r="C22">
+        <v>6712.269937725665</v>
+      </c>
+      <c r="D22">
+        <v>9437.129937725666</v>
+      </c>
+      <c r="E22">
+        <v>-7076.74</v>
+      </c>
+      <c r="F22">
+        <v>3527.66</v>
+      </c>
+      <c r="G22">
+        <v>802.8</v>
+      </c>
+      <c r="H22">
+        <v>7033.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1220.7</v>
+      </c>
+      <c r="K22">
+        <v>1603.1</v>
+      </c>
+      <c r="L22">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M22">
+        <v>842.405208</v>
+      </c>
+      <c r="N22">
+        <v>-1224.805208</v>
+      </c>
+      <c r="O22">
+        <v>-202.09285932</v>
+      </c>
+      <c r="P22">
+        <v>-1022.71234868</v>
+      </c>
+      <c r="Q22">
+        <v>580.3876513200001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1065030093111857</v>
+      </c>
+      <c r="T22">
+        <v>0.9743098645116063</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.07489982184440624</v>
+      </c>
+      <c r="W22">
+        <v>0.2566860774564442</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.4539383142085225</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1385396229402374</v>
+      </c>
+      <c r="C23">
+        <v>6357.319426333674</v>
+      </c>
+      <c r="D23">
+        <v>9258.562426333674</v>
+      </c>
+      <c r="E23">
+        <v>-6900.357</v>
+      </c>
+      <c r="F23">
+        <v>3704.043</v>
+      </c>
+      <c r="G23">
+        <v>802.8</v>
+      </c>
+      <c r="H23">
+        <v>7033.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1220.7</v>
+      </c>
+      <c r="K23">
+        <v>1603.1</v>
+      </c>
+      <c r="L23">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M23">
+        <v>884.5254683999999</v>
+      </c>
+      <c r="N23">
+        <v>-1266.9254684</v>
+      </c>
+      <c r="O23">
+        <v>-209.042702286</v>
+      </c>
+      <c r="P23">
+        <v>-1057.882766114</v>
+      </c>
+      <c r="Q23">
+        <v>545.217233886</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1073600094290488</v>
+      </c>
+      <c r="T23">
+        <v>0.9866429007712469</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.07133316366133929</v>
+      </c>
+      <c r="W23">
+        <v>0.2558343594823278</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.4323222040081169</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1405396229402374</v>
+      </c>
+      <c r="C24">
+        <v>6009.00106124068</v>
+      </c>
+      <c r="D24">
+        <v>9086.627061240681</v>
+      </c>
+      <c r="E24">
+        <v>-6723.974</v>
+      </c>
+      <c r="F24">
+        <v>3880.426</v>
+      </c>
+      <c r="G24">
+        <v>802.8</v>
+      </c>
+      <c r="H24">
+        <v>7033.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1220.7</v>
+      </c>
+      <c r="K24">
+        <v>1603.1</v>
+      </c>
+      <c r="L24">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M24">
+        <v>926.6457288</v>
+      </c>
+      <c r="N24">
+        <v>-1309.0457288</v>
+      </c>
+      <c r="O24">
+        <v>-215.992545252</v>
+      </c>
+      <c r="P24">
+        <v>-1093.053183548</v>
+      </c>
+      <c r="Q24">
+        <v>510.0468164520003</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1082389839089084</v>
+      </c>
+      <c r="T24">
+        <v>0.9992921687298527</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.06809074713127841</v>
+      </c>
+      <c r="W24">
+        <v>0.2550600704149493</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.4126711947350203</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1425396229402374</v>
+      </c>
+      <c r="C25">
+        <v>5666.952093675468</v>
+      </c>
+      <c r="D25">
+        <v>8920.961093675469</v>
+      </c>
+      <c r="E25">
+        <v>-6547.590999999999</v>
+      </c>
+      <c r="F25">
+        <v>4056.809</v>
+      </c>
+      <c r="G25">
+        <v>802.8</v>
+      </c>
+      <c r="H25">
+        <v>7033.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1220.7</v>
+      </c>
+      <c r="K25">
+        <v>1603.1</v>
+      </c>
+      <c r="L25">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M25">
+        <v>968.7659892000001</v>
+      </c>
+      <c r="N25">
+        <v>-1351.1659892</v>
+      </c>
+      <c r="O25">
+        <v>-222.942388218</v>
+      </c>
+      <c r="P25">
+        <v>-1128.223600982</v>
+      </c>
+      <c r="Q25">
+        <v>474.876399018</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1091407888947384</v>
+      </c>
+      <c r="T25">
+        <v>1.012269989102967</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.06513027986470107</v>
+      </c>
+      <c r="W25">
+        <v>0.2543531108316907</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.3947289688769762</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1445396229402374</v>
+      </c>
+      <c r="C26">
+        <v>5330.835755507941</v>
+      </c>
+      <c r="D26">
+        <v>8761.227755507942</v>
+      </c>
+      <c r="E26">
+        <v>-6371.208</v>
+      </c>
+      <c r="F26">
+        <v>4233.192</v>
+      </c>
+      <c r="G26">
+        <v>802.8</v>
+      </c>
+      <c r="H26">
+        <v>7033.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1220.7</v>
+      </c>
+      <c r="K26">
+        <v>1603.1</v>
+      </c>
+      <c r="L26">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M26">
+        <v>1010.8862496</v>
+      </c>
+      <c r="N26">
+        <v>-1393.2862496</v>
+      </c>
+      <c r="O26">
+        <v>-229.892231184</v>
+      </c>
+      <c r="P26">
+        <v>-1163.394018416</v>
+      </c>
+      <c r="Q26">
+        <v>439.7059815840003</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1100663255907218</v>
+      </c>
+      <c r="T26">
+        <v>1.025589331064849</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.06241651820367188</v>
+      </c>
+      <c r="W26">
+        <v>0.2537050645470368</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.378281928507102</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1465396229402374</v>
+      </c>
+      <c r="C27">
+        <v>5000.338974195588</v>
+      </c>
+      <c r="D27">
+        <v>8607.113974195589</v>
+      </c>
+      <c r="E27">
+        <v>-6194.825</v>
+      </c>
+      <c r="F27">
+        <v>4409.575</v>
+      </c>
+      <c r="G27">
+        <v>802.8</v>
+      </c>
+      <c r="H27">
+        <v>7033.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1220.7</v>
+      </c>
+      <c r="K27">
+        <v>1603.1</v>
+      </c>
+      <c r="L27">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M27">
+        <v>1053.00651</v>
+      </c>
+      <c r="N27">
+        <v>-1435.40651</v>
+      </c>
+      <c r="O27">
+        <v>-236.84207415</v>
+      </c>
+      <c r="P27">
+        <v>-1198.56443585</v>
+      </c>
+      <c r="Q27">
+        <v>404.53556415</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1110165432652647</v>
+      </c>
+      <c r="T27">
+        <v>1.039263855479047</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.059919857475525</v>
+      </c>
+      <c r="W27">
+        <v>0.2531088619651554</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.3631506513668181</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1485396229402374</v>
+      </c>
+      <c r="C28">
+        <v>4675.170324731539</v>
+      </c>
+      <c r="D28">
+        <v>8458.328324731539</v>
+      </c>
+      <c r="E28">
+        <v>-6018.442</v>
+      </c>
+      <c r="F28">
+        <v>4585.958</v>
+      </c>
+      <c r="G28">
+        <v>802.8</v>
+      </c>
+      <c r="H28">
+        <v>7033.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1220.7</v>
+      </c>
+      <c r="K28">
+        <v>1603.1</v>
+      </c>
+      <c r="L28">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M28">
+        <v>1095.1267704</v>
+      </c>
+      <c r="N28">
+        <v>-1477.5267704</v>
+      </c>
+      <c r="O28">
+        <v>-243.791917116</v>
+      </c>
+      <c r="P28">
+        <v>-1233.734853284</v>
+      </c>
+      <c r="Q28">
+        <v>369.365146716</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1119924424985791</v>
+      </c>
+      <c r="T28">
+        <v>1.053307961634169</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.0576152475726202</v>
+      </c>
+      <c r="W28">
+        <v>0.2525585211203417</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.3491833186219404</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1505396229402374</v>
+      </c>
+      <c r="C29">
+        <v>4355.058190403093</v>
+      </c>
+      <c r="D29">
+        <v>8314.599190403094</v>
+      </c>
+      <c r="E29">
+        <v>-5842.058999999999</v>
+      </c>
+      <c r="F29">
+        <v>4762.341</v>
+      </c>
+      <c r="G29">
+        <v>802.8</v>
+      </c>
+      <c r="H29">
+        <v>7033.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1220.7</v>
+      </c>
+      <c r="K29">
+        <v>1603.1</v>
+      </c>
+      <c r="L29">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M29">
+        <v>1137.2470308</v>
+      </c>
+      <c r="N29">
+        <v>-1519.6470308</v>
+      </c>
+      <c r="O29">
+        <v>-250.7417600820001</v>
+      </c>
+      <c r="P29">
+        <v>-1268.905270718</v>
+      </c>
+      <c r="Q29">
+        <v>334.194729282</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1129950786971898</v>
+      </c>
+      <c r="T29">
+        <v>1.067736837820938</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.05548134951437499</v>
+      </c>
+      <c r="W29">
+        <v>0.2520489462640327</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.3362506031174242</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1525396229402374</v>
+      </c>
+      <c r="C30">
+        <v>4039.749107938254</v>
+      </c>
+      <c r="D30">
+        <v>8175.673107938254</v>
+      </c>
+      <c r="E30">
+        <v>-5665.675999999999</v>
+      </c>
+      <c r="F30">
+        <v>4938.724</v>
+      </c>
+      <c r="G30">
+        <v>802.8</v>
+      </c>
+      <c r="H30">
+        <v>7033.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1220.7</v>
+      </c>
+      <c r="K30">
+        <v>1603.1</v>
+      </c>
+      <c r="L30">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M30">
+        <v>1179.3672912</v>
+      </c>
+      <c r="N30">
+        <v>-1561.7672912</v>
+      </c>
+      <c r="O30">
+        <v>-257.691603048</v>
+      </c>
+      <c r="P30">
+        <v>-1304.075688152</v>
+      </c>
+      <c r="Q30">
+        <v>299.0243118479998</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1140255659013175</v>
+      </c>
+      <c r="T30">
+        <v>1.082566516124007</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.05349987274600446</v>
+      </c>
+      <c r="W30">
+        <v>0.2515757696117459</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.3242416530060876</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1545396229402374</v>
+      </c>
+      <c r="C31">
+        <v>3729.006275828398</v>
+      </c>
+      <c r="D31">
+        <v>8041.313275828397</v>
+      </c>
+      <c r="E31">
+        <v>-5489.293000000001</v>
+      </c>
+      <c r="F31">
+        <v>5115.106999999999</v>
+      </c>
+      <c r="G31">
+        <v>802.8</v>
+      </c>
+      <c r="H31">
+        <v>7033.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1220.7</v>
+      </c>
+      <c r="K31">
+        <v>1603.1</v>
+      </c>
+      <c r="L31">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M31">
+        <v>1221.4875516</v>
+      </c>
+      <c r="N31">
+        <v>-1603.8875516</v>
+      </c>
+      <c r="O31">
+        <v>-264.641446014</v>
+      </c>
+      <c r="P31">
+        <v>-1339.246105586</v>
+      </c>
+      <c r="Q31">
+        <v>263.8538944140003</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1150850809140121</v>
+      </c>
+      <c r="T31">
+        <v>1.097813931844064</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.05165504954786639</v>
+      </c>
+      <c r="W31">
+        <v>0.2511352258320305</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.3130609063507053</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1565396229402374</v>
+      </c>
+      <c r="C32">
+        <v>3422.60820735903</v>
+      </c>
+      <c r="D32">
+        <v>7911.298207359029</v>
+      </c>
+      <c r="E32">
+        <v>-5312.91</v>
+      </c>
+      <c r="F32">
+        <v>5291.49</v>
+      </c>
+      <c r="G32">
+        <v>802.8</v>
+      </c>
+      <c r="H32">
+        <v>7033.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1220.7</v>
+      </c>
+      <c r="K32">
+        <v>1603.1</v>
+      </c>
+      <c r="L32">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M32">
+        <v>1263.607812</v>
+      </c>
+      <c r="N32">
+        <v>-1646.007812</v>
+      </c>
+      <c r="O32">
+        <v>-271.5912889800001</v>
+      </c>
+      <c r="P32">
+        <v>-1374.41652302</v>
+      </c>
+      <c r="Q32">
+        <v>228.6834769800003</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1161748677842122</v>
+      </c>
+      <c r="T32">
+        <v>1.113496988013264</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.04993321456293751</v>
+      </c>
+      <c r="W32">
+        <v>0.2507240516376295</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.3026255428056817</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1585396229402374</v>
+      </c>
+      <c r="C33">
+        <v>3120.347512231383</v>
+      </c>
+      <c r="D33">
+        <v>7785.420512231382</v>
+      </c>
+      <c r="E33">
+        <v>-5136.527</v>
+      </c>
+      <c r="F33">
+        <v>5467.873</v>
+      </c>
+      <c r="G33">
+        <v>802.8</v>
+      </c>
+      <c r="H33">
+        <v>7033.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1220.7</v>
+      </c>
+      <c r="K33">
+        <v>1603.1</v>
+      </c>
+      <c r="L33">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M33">
+        <v>1305.7280724</v>
+      </c>
+      <c r="N33">
+        <v>-1688.1280724</v>
+      </c>
+      <c r="O33">
+        <v>-278.541131946</v>
+      </c>
+      <c r="P33">
+        <v>-1409.586940454</v>
+      </c>
+      <c r="Q33">
+        <v>193.513059546</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1172962426796356</v>
+      </c>
+      <c r="T33">
+        <v>1.129634625520703</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.04832246570606855</v>
+      </c>
+      <c r="W33">
+        <v>0.2503394048106092</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.2928634285216276</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1605396229402374</v>
+      </c>
+      <c r="C34">
+        <v>2822.029792676975</v>
+      </c>
+      <c r="D34">
+        <v>7663.485792676976</v>
+      </c>
+      <c r="E34">
+        <v>-4960.143999999999</v>
+      </c>
+      <c r="F34">
+        <v>5644.256</v>
+      </c>
+      <c r="G34">
+        <v>802.8</v>
+      </c>
+      <c r="H34">
+        <v>7033.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1220.7</v>
+      </c>
+      <c r="K34">
+        <v>1603.1</v>
+      </c>
+      <c r="L34">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M34">
+        <v>1347.8483328</v>
+      </c>
+      <c r="N34">
+        <v>-1730.2483328</v>
+      </c>
+      <c r="O34">
+        <v>-285.4909749120001</v>
+      </c>
+      <c r="P34">
+        <v>-1444.757357888</v>
+      </c>
+      <c r="Q34">
+        <v>158.3426421119998</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1184505991896302</v>
+      </c>
+      <c r="T34">
+        <v>1.146246899425419</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.0468123886527539</v>
+      </c>
+      <c r="W34">
+        <v>0.2499787984102776</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.2837114463803265</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1625396229402374</v>
+      </c>
+      <c r="C35">
+        <v>2527.472641706366</v>
+      </c>
+      <c r="D35">
+        <v>7545.311641706367</v>
+      </c>
+      <c r="E35">
+        <v>-4783.761</v>
+      </c>
+      <c r="F35">
+        <v>5820.639</v>
+      </c>
+      <c r="G35">
+        <v>802.8</v>
+      </c>
+      <c r="H35">
+        <v>7033.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1220.7</v>
+      </c>
+      <c r="K35">
+        <v>1603.1</v>
+      </c>
+      <c r="L35">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M35">
+        <v>1389.9685932</v>
+      </c>
+      <c r="N35">
+        <v>-1772.3685932</v>
+      </c>
+      <c r="O35">
+        <v>-292.4408178780001</v>
+      </c>
+      <c r="P35">
+        <v>-1479.927775322</v>
+      </c>
+      <c r="Q35">
+        <v>123.172224678</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1196394141029083</v>
+      </c>
+      <c r="T35">
+        <v>1.163355062103411</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.04539383142085227</v>
+      </c>
+      <c r="W35">
+        <v>0.2496400469432995</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.275114129823347</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1645396229402374</v>
+      </c>
+      <c r="C36">
+        <v>2236.504732634984</v>
+      </c>
+      <c r="D36">
+        <v>7430.726732634984</v>
+      </c>
+      <c r="E36">
+        <v>-4607.378</v>
+      </c>
+      <c r="F36">
+        <v>5997.022</v>
+      </c>
+      <c r="G36">
+        <v>802.8</v>
+      </c>
+      <c r="H36">
+        <v>7033.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1220.7</v>
+      </c>
+      <c r="K36">
+        <v>1603.1</v>
+      </c>
+      <c r="L36">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M36">
+        <v>1432.0888536</v>
+      </c>
+      <c r="N36">
+        <v>-1814.4888536</v>
+      </c>
+      <c r="O36">
+        <v>-299.390660844</v>
+      </c>
+      <c r="P36">
+        <v>-1515.098192756</v>
+      </c>
+      <c r="Q36">
+        <v>88.00180724400002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1208642537105281</v>
+      </c>
+      <c r="T36">
+        <v>1.180981653953462</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.04405871873200368</v>
+      </c>
+      <c r="W36">
+        <v>0.2493212220332025</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.2670225377697193</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1665396229402374</v>
+      </c>
+      <c r="C37">
+        <v>1948.964990327958</v>
+      </c>
+      <c r="D37">
+        <v>7319.569990327958</v>
+      </c>
+      <c r="E37">
+        <v>-4430.994999999999</v>
+      </c>
+      <c r="F37">
+        <v>6173.405000000001</v>
+      </c>
+      <c r="G37">
+        <v>802.8</v>
+      </c>
+      <c r="H37">
+        <v>7033.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1220.7</v>
+      </c>
+      <c r="K37">
+        <v>1603.1</v>
+      </c>
+      <c r="L37">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M37">
+        <v>1474.209114</v>
+      </c>
+      <c r="N37">
+        <v>-1856.609114</v>
+      </c>
+      <c r="O37">
+        <v>-306.3405038100001</v>
+      </c>
+      <c r="P37">
+        <v>-1550.26861019</v>
+      </c>
+      <c r="Q37">
+        <v>52.83138981000002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1221267806906901</v>
+      </c>
+      <c r="T37">
+        <v>1.199150602475823</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.04279989819680356</v>
+      </c>
+      <c r="W37">
+        <v>0.2490206156893967</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.2593933224048701</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1685396229402374</v>
+      </c>
+      <c r="C38">
+        <v>1664.701835733106</v>
+      </c>
+      <c r="D38">
+        <v>7211.689835733106</v>
+      </c>
+      <c r="E38">
+        <v>-4254.612</v>
+      </c>
+      <c r="F38">
+        <v>6349.788</v>
+      </c>
+      <c r="G38">
+        <v>802.8</v>
+      </c>
+      <c r="H38">
+        <v>7033.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1220.7</v>
+      </c>
+      <c r="K38">
+        <v>1603.1</v>
+      </c>
+      <c r="L38">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M38">
+        <v>1516.3293744</v>
+      </c>
+      <c r="N38">
+        <v>-1898.7293744</v>
+      </c>
+      <c r="O38">
+        <v>-313.290346776</v>
+      </c>
+      <c r="P38">
+        <v>-1585.439027624</v>
+      </c>
+      <c r="Q38">
+        <v>17.66097237600002</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1234287616389821</v>
+      </c>
+      <c r="T38">
+        <v>1.217887330639508</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.04161101213578125</v>
+      </c>
+      <c r="W38">
+        <v>0.2487367096980246</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.2521879523380681</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1705396229402374</v>
+      </c>
+      <c r="C39">
+        <v>1383.572496250659</v>
+      </c>
+      <c r="D39">
+        <v>7106.943496250658</v>
+      </c>
+      <c r="E39">
+        <v>-4078.229</v>
+      </c>
+      <c r="F39">
+        <v>6526.170999999999</v>
+      </c>
+      <c r="G39">
+        <v>802.8</v>
+      </c>
+      <c r="H39">
+        <v>7033.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1220.7</v>
+      </c>
+      <c r="K39">
+        <v>1603.1</v>
+      </c>
+      <c r="L39">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M39">
+        <v>1558.4496348</v>
+      </c>
+      <c r="N39">
+        <v>-1940.8496348</v>
+      </c>
+      <c r="O39">
+        <v>-320.240189742</v>
+      </c>
+      <c r="P39">
+        <v>-1620.609445058</v>
+      </c>
+      <c r="Q39">
+        <v>-17.50944505799998</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1247720753157914</v>
+      </c>
+      <c r="T39">
+        <v>1.237218875570294</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.04048639018616555</v>
+      </c>
+      <c r="W39">
+        <v>0.2484681499764564</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.2453720617343365</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1725396229402374</v>
+      </c>
+      <c r="C40">
+        <v>1105.442375341908</v>
+      </c>
+      <c r="D40">
+        <v>7005.196375341908</v>
+      </c>
+      <c r="E40">
+        <v>-3901.846</v>
+      </c>
+      <c r="F40">
+        <v>6702.554</v>
+      </c>
+      <c r="G40">
+        <v>802.8</v>
+      </c>
+      <c r="H40">
+        <v>7033.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1220.7</v>
+      </c>
+      <c r="K40">
+        <v>1603.1</v>
+      </c>
+      <c r="L40">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M40">
+        <v>1600.5698952</v>
+      </c>
+      <c r="N40">
+        <v>-1982.9698952</v>
+      </c>
+      <c r="O40">
+        <v>-327.190032708</v>
+      </c>
+      <c r="P40">
+        <v>-1655.779862492</v>
+      </c>
+      <c r="Q40">
+        <v>-52.67986249199998</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1261587216918525</v>
+      </c>
+      <c r="T40">
+        <v>1.257174018724653</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.03942095886547697</v>
+      </c>
+      <c r="W40">
+        <v>0.2482137249770759</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.2389149022150119</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1745396229402374</v>
+      </c>
+      <c r="C41">
+        <v>830.1844755237844</v>
+      </c>
+      <c r="D41">
+        <v>6906.321475523784</v>
+      </c>
+      <c r="E41">
+        <v>-3725.463</v>
+      </c>
+      <c r="F41">
+        <v>6878.937</v>
+      </c>
+      <c r="G41">
+        <v>802.8</v>
+      </c>
+      <c r="H41">
+        <v>7033.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1220.7</v>
+      </c>
+      <c r="K41">
+        <v>1603.1</v>
+      </c>
+      <c r="L41">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M41">
+        <v>1642.6901556</v>
+      </c>
+      <c r="N41">
+        <v>-2025.0901556</v>
+      </c>
+      <c r="O41">
+        <v>-334.1398756740001</v>
+      </c>
+      <c r="P41">
+        <v>-1690.950279926</v>
+      </c>
+      <c r="Q41">
+        <v>-87.85027992599998</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1275908318835222</v>
+      </c>
+      <c r="T41">
+        <v>1.277783428867681</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.03841016504841346</v>
+      </c>
+      <c r="W41">
+        <v>0.2479723474135611</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.2327888790812938</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1765396229402374</v>
+      </c>
+      <c r="C42">
+        <v>557.6788695482746</v>
+      </c>
+      <c r="D42">
+        <v>6810.198869548274</v>
+      </c>
+      <c r="E42">
+        <v>-3549.08</v>
+      </c>
+      <c r="F42">
+        <v>7055.32</v>
+      </c>
+      <c r="G42">
+        <v>802.8</v>
+      </c>
+      <c r="H42">
+        <v>7033.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1220.7</v>
+      </c>
+      <c r="K42">
+        <v>1603.1</v>
+      </c>
+      <c r="L42">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M42">
+        <v>1684.810416</v>
+      </c>
+      <c r="N42">
+        <v>-2067.210416</v>
+      </c>
+      <c r="O42">
+        <v>-341.0897186400001</v>
+      </c>
+      <c r="P42">
+        <v>-1726.12069736</v>
+      </c>
+      <c r="Q42">
+        <v>-123.02069736</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1290706790815809</v>
+      </c>
+      <c r="T42">
+        <v>1.299079819348808</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.03744991092220312</v>
+      </c>
+      <c r="W42">
+        <v>0.2477430387282221</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.2269691571042614</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1785396229402374</v>
+      </c>
+      <c r="C43">
+        <v>287.8122151365251</v>
+      </c>
+      <c r="D43">
+        <v>6716.715215136525</v>
+      </c>
+      <c r="E43">
+        <v>-3372.696999999999</v>
+      </c>
+      <c r="F43">
+        <v>7231.703</v>
+      </c>
+      <c r="G43">
+        <v>802.8</v>
+      </c>
+      <c r="H43">
+        <v>7033.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1220.7</v>
+      </c>
+      <c r="K43">
+        <v>1603.1</v>
+      </c>
+      <c r="L43">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M43">
+        <v>1726.9306764</v>
+      </c>
+      <c r="N43">
+        <v>-2109.3306764</v>
+      </c>
+      <c r="O43">
+        <v>-348.0395616060001</v>
+      </c>
+      <c r="P43">
+        <v>-1761.291114794</v>
+      </c>
+      <c r="Q43">
+        <v>-158.191114794</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1306006905914383</v>
+      </c>
+      <c r="T43">
+        <v>1.32109812137167</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.03653649846068597</v>
+      </c>
+      <c r="W43">
+        <v>0.2475249158324118</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.2214333240041573</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1805396229402374</v>
+      </c>
+      <c r="C44">
+        <v>20.47730913929536</v>
+      </c>
+      <c r="D44">
+        <v>6625.763309139295</v>
+      </c>
+      <c r="E44">
+        <v>-3196.314</v>
+      </c>
+      <c r="F44">
+        <v>7408.085999999999</v>
+      </c>
+      <c r="G44">
+        <v>802.8</v>
+      </c>
+      <c r="H44">
+        <v>7033.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1220.7</v>
+      </c>
+      <c r="K44">
+        <v>1603.1</v>
+      </c>
+      <c r="L44">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M44">
+        <v>1769.0509368</v>
+      </c>
+      <c r="N44">
+        <v>-2151.4509368</v>
+      </c>
+      <c r="O44">
+        <v>-354.9894045720001</v>
+      </c>
+      <c r="P44">
+        <v>-1796.461532228</v>
+      </c>
+      <c r="Q44">
+        <v>-193.361532228</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1321834611188768</v>
+      </c>
+      <c r="T44">
+        <v>1.343875675188422</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.03566658183066965</v>
+      </c>
+      <c r="W44">
+        <v>0.2473171797411639</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.2161611020040586</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1825396229402374</v>
+      </c>
+      <c r="C45">
+        <v>-244.427322563577</v>
+      </c>
+      <c r="D45">
+        <v>6537.241677436422</v>
+      </c>
+      <c r="E45">
+        <v>-3019.931</v>
+      </c>
+      <c r="F45">
+        <v>7584.468999999999</v>
+      </c>
+      <c r="G45">
+        <v>802.8</v>
+      </c>
+      <c r="H45">
+        <v>7033.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1220.7</v>
+      </c>
+      <c r="K45">
+        <v>1603.1</v>
+      </c>
+      <c r="L45">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M45">
+        <v>1811.1711972</v>
+      </c>
+      <c r="N45">
+        <v>-2193.5711972</v>
+      </c>
+      <c r="O45">
+        <v>-361.9392475380001</v>
+      </c>
+      <c r="P45">
+        <v>-1831.631949662</v>
+      </c>
+      <c r="Q45">
+        <v>-228.531949662</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1338217674542957</v>
+      </c>
+      <c r="T45">
+        <v>1.367452441419798</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.03483712643925872</v>
+      </c>
+      <c r="W45">
+        <v>0.247119105793695</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.2111340996318711</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1845396229402374</v>
+      </c>
+      <c r="C46">
+        <v>-506.9978027228717</v>
+      </c>
+      <c r="D46">
+        <v>6451.054197277128</v>
+      </c>
+      <c r="E46">
+        <v>-2843.548</v>
+      </c>
+      <c r="F46">
+        <v>7760.852</v>
+      </c>
+      <c r="G46">
+        <v>802.8</v>
+      </c>
+      <c r="H46">
+        <v>7033.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1220.7</v>
+      </c>
+      <c r="K46">
+        <v>1603.1</v>
+      </c>
+      <c r="L46">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M46">
+        <v>1853.2914576</v>
+      </c>
+      <c r="N46">
+        <v>-2235.6914576</v>
+      </c>
+      <c r="O46">
+        <v>-368.8890905040001</v>
+      </c>
+      <c r="P46">
+        <v>-1866.802367096</v>
+      </c>
+      <c r="Q46">
+        <v>-263.702367096</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1355185847302653</v>
+      </c>
+      <c r="T46">
+        <v>1.39187123501658</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.03404537356563921</v>
+      </c>
+      <c r="W46">
+        <v>0.2469300352074746</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.2063355973675103</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1865396229402374</v>
+      </c>
+      <c r="C47">
+        <v>-767.3252508939122</v>
+      </c>
+      <c r="D47">
+        <v>6367.109749106087</v>
+      </c>
+      <c r="E47">
+        <v>-2667.165</v>
+      </c>
+      <c r="F47">
+        <v>7937.235</v>
+      </c>
+      <c r="G47">
+        <v>802.8</v>
+      </c>
+      <c r="H47">
+        <v>7033.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1220.7</v>
+      </c>
+      <c r="K47">
+        <v>1603.1</v>
+      </c>
+      <c r="L47">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M47">
+        <v>1895.411718</v>
+      </c>
+      <c r="N47">
+        <v>-2277.811718</v>
+      </c>
+      <c r="O47">
+        <v>-375.8389334700001</v>
+      </c>
+      <c r="P47">
+        <v>-1901.97278453</v>
+      </c>
+      <c r="Q47">
+        <v>-298.87278453</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1372771044526337</v>
+      </c>
+      <c r="T47">
+        <v>1.417177984744155</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.033288809708625</v>
+      </c>
+      <c r="W47">
+        <v>0.2467493677584197</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.2017503618704546</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1885396229402374</v>
+      </c>
+      <c r="C48">
+        <v>-1025.496104775941</v>
+      </c>
+      <c r="D48">
+        <v>6285.32189522406</v>
+      </c>
+      <c r="E48">
+        <v>-2490.781999999999</v>
+      </c>
+      <c r="F48">
+        <v>8113.618</v>
+      </c>
+      <c r="G48">
+        <v>802.8</v>
+      </c>
+      <c r="H48">
+        <v>7033.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1220.7</v>
+      </c>
+      <c r="K48">
+        <v>1603.1</v>
+      </c>
+      <c r="L48">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M48">
+        <v>1937.5319784</v>
+      </c>
+      <c r="N48">
+        <v>-2319.9319784</v>
+      </c>
+      <c r="O48">
+        <v>-382.7887764360001</v>
+      </c>
+      <c r="P48">
+        <v>-1937.143201964</v>
+      </c>
+      <c r="Q48">
+        <v>-334.043201964</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1391007545350899</v>
+      </c>
+      <c r="T48">
+        <v>1.443422021498676</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.03256513993235054</v>
+      </c>
+      <c r="W48">
+        <v>0.2465765554158453</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.1973644844384879</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1905396229402374</v>
+      </c>
+      <c r="C49">
+        <v>-1281.592417099261</v>
+      </c>
+      <c r="D49">
+        <v>6205.608582900739</v>
+      </c>
+      <c r="E49">
+        <v>-2314.398999999999</v>
+      </c>
+      <c r="F49">
+        <v>8290.001</v>
+      </c>
+      <c r="G49">
+        <v>802.8</v>
+      </c>
+      <c r="H49">
+        <v>7033.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1220.7</v>
+      </c>
+      <c r="K49">
+        <v>1603.1</v>
+      </c>
+      <c r="L49">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M49">
+        <v>1979.6522388</v>
+      </c>
+      <c r="N49">
+        <v>-2362.0522388</v>
+      </c>
+      <c r="O49">
+        <v>-389.7386194020001</v>
+      </c>
+      <c r="P49">
+        <v>-1972.313619398</v>
+      </c>
+      <c r="Q49">
+        <v>-369.213619398</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1409932216017897</v>
+      </c>
+      <c r="T49">
+        <v>1.470656399262802</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.03187226461464096</v>
+      </c>
+      <c r="W49">
+        <v>0.2464110967899763</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.1931652400887329</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1925396229402374</v>
+      </c>
+      <c r="C50">
+        <v>-1535.692130203768</v>
+      </c>
+      <c r="D50">
+        <v>6127.891869796232</v>
+      </c>
+      <c r="E50">
+        <v>-2138.016</v>
+      </c>
+      <c r="F50">
+        <v>8466.384</v>
+      </c>
+      <c r="G50">
+        <v>802.8</v>
+      </c>
+      <c r="H50">
+        <v>7033.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1220.7</v>
+      </c>
+      <c r="K50">
+        <v>1603.1</v>
+      </c>
+      <c r="L50">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M50">
+        <v>2021.7724992</v>
+      </c>
+      <c r="N50">
+        <v>-2404.1724992</v>
+      </c>
+      <c r="O50">
+        <v>-396.6884623680001</v>
+      </c>
+      <c r="P50">
+        <v>-2007.484036832</v>
+      </c>
+      <c r="Q50">
+        <v>-404.384036832</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1429584758633626</v>
+      </c>
+      <c r="T50">
+        <v>1.498938253094779</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.03120825910183594</v>
+      </c>
+      <c r="W50">
+        <v>0.2462525322735184</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.1891409642535511</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1945396229402374</v>
+      </c>
+      <c r="C51">
+        <v>-1787.869330240358</v>
+      </c>
+      <c r="D51">
+        <v>6052.097669759642</v>
+      </c>
+      <c r="E51">
+        <v>-1961.633</v>
+      </c>
+      <c r="F51">
+        <v>8642.767</v>
+      </c>
+      <c r="G51">
+        <v>802.8</v>
+      </c>
+      <c r="H51">
+        <v>7033.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1220.7</v>
+      </c>
+      <c r="K51">
+        <v>1603.1</v>
+      </c>
+      <c r="L51">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M51">
+        <v>2063.8927596</v>
+      </c>
+      <c r="N51">
+        <v>-2446.2927596</v>
+      </c>
+      <c r="O51">
+        <v>-403.6383053340001</v>
+      </c>
+      <c r="P51">
+        <v>-2042.654454266</v>
+      </c>
+      <c r="Q51">
+        <v>-439.554454266</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.145000798919507</v>
+      </c>
+      <c r="T51">
+        <v>1.528329199233892</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.03057135585485969</v>
+      </c>
+      <c r="W51">
+        <v>0.2461004397781405</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.1852809445749073</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1965396229402374</v>
+      </c>
+      <c r="C52">
+        <v>-2038.194482737946</v>
+      </c>
+      <c r="D52">
+        <v>5978.155517262054</v>
+      </c>
+      <c r="E52">
+        <v>-1785.25</v>
+      </c>
+      <c r="F52">
+        <v>8819.15</v>
+      </c>
+      <c r="G52">
+        <v>802.8</v>
+      </c>
+      <c r="H52">
+        <v>7033.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1220.7</v>
+      </c>
+      <c r="K52">
+        <v>1603.1</v>
+      </c>
+      <c r="L52">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M52">
+        <v>2106.01302</v>
+      </c>
+      <c r="N52">
+        <v>-2488.41302</v>
+      </c>
+      <c r="O52">
+        <v>-410.5881483000001</v>
+      </c>
+      <c r="P52">
+        <v>-2077.8248717</v>
+      </c>
+      <c r="Q52">
+        <v>-474.7248716999998</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1471248148978971</v>
+      </c>
+      <c r="T52">
+        <v>1.55889578321857</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.0299599287377625</v>
+      </c>
+      <c r="W52">
+        <v>0.2459544309825777</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.1815753256834092</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1985396229402374</v>
+      </c>
+      <c r="C53">
+        <v>-2286.734651110516</v>
+      </c>
+      <c r="D53">
+        <v>5905.998348889483</v>
+      </c>
+      <c r="E53">
+        <v>-1608.867</v>
+      </c>
+      <c r="F53">
+        <v>8995.532999999999</v>
+      </c>
+      <c r="G53">
+        <v>802.8</v>
+      </c>
+      <c r="H53">
+        <v>7033.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1220.7</v>
+      </c>
+      <c r="K53">
+        <v>1603.1</v>
+      </c>
+      <c r="L53">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M53">
+        <v>2148.1332804</v>
+      </c>
+      <c r="N53">
+        <v>-2530.5332804</v>
+      </c>
+      <c r="O53">
+        <v>-417.5379912660001</v>
+      </c>
+      <c r="P53">
+        <v>-2112.995289134</v>
+      </c>
+      <c r="Q53">
+        <v>-509.895289134</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1493355254060175</v>
+      </c>
+      <c r="T53">
+        <v>1.590709982876092</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.02937247915466912</v>
+      </c>
+      <c r="W53">
+        <v>0.245814148022135</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.1780150251798129</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2005396229402374</v>
+      </c>
+      <c r="C54">
+        <v>-2533.55369952844</v>
+      </c>
+      <c r="D54">
+        <v>5835.562300471559</v>
+      </c>
+      <c r="E54">
+        <v>-1432.484</v>
+      </c>
+      <c r="F54">
+        <v>9171.915999999999</v>
+      </c>
+      <c r="G54">
+        <v>802.8</v>
+      </c>
+      <c r="H54">
+        <v>7033.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1220.7</v>
+      </c>
+      <c r="K54">
+        <v>1603.1</v>
+      </c>
+      <c r="L54">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M54">
+        <v>2190.2535408</v>
+      </c>
+      <c r="N54">
+        <v>-2572.6535408</v>
+      </c>
+      <c r="O54">
+        <v>-424.4878342320001</v>
+      </c>
+      <c r="P54">
+        <v>-2148.165706568</v>
+      </c>
+      <c r="Q54">
+        <v>-545.0657065680002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1516383488519762</v>
+      </c>
+      <c r="T54">
+        <v>1.623849774186011</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.0288076237863101</v>
+      </c>
+      <c r="W54">
+        <v>0.2456792605601709</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.1745916593109704</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2025396229402374</v>
+      </c>
+      <c r="C55">
+        <v>-2778.712481443996</v>
+      </c>
+      <c r="D55">
+        <v>5766.786518556005</v>
+      </c>
+      <c r="E55">
+        <v>-1256.100999999999</v>
+      </c>
+      <c r="F55">
+        <v>9348.299000000001</v>
+      </c>
+      <c r="G55">
+        <v>802.8</v>
+      </c>
+      <c r="H55">
+        <v>7033.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1220.7</v>
+      </c>
+      <c r="K55">
+        <v>1603.1</v>
+      </c>
+      <c r="L55">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M55">
+        <v>2232.3738012</v>
+      </c>
+      <c r="N55">
+        <v>-2614.7738012</v>
+      </c>
+      <c r="O55">
+        <v>-431.4376771980001</v>
+      </c>
+      <c r="P55">
+        <v>-2183.336124002</v>
+      </c>
+      <c r="Q55">
+        <v>-580.236124002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.154039164784997</v>
+      </c>
+      <c r="T55">
+        <v>1.658399769381458</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.02826408371487028</v>
+      </c>
+      <c r="W55">
+        <v>0.245549463191111</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.1712974770598197</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2045396229402374</v>
+      </c>
+      <c r="C56">
+        <v>-3022.269014940814</v>
+      </c>
+      <c r="D56">
+        <v>5699.612985059186</v>
+      </c>
+      <c r="E56">
+        <v>-1079.717999999999</v>
+      </c>
+      <c r="F56">
+        <v>9524.682000000001</v>
+      </c>
+      <c r="G56">
+        <v>802.8</v>
+      </c>
+      <c r="H56">
+        <v>7033.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1220.7</v>
+      </c>
+      <c r="K56">
+        <v>1603.1</v>
+      </c>
+      <c r="L56">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M56">
+        <v>2274.4940616</v>
+      </c>
+      <c r="N56">
+        <v>-2656.8940616</v>
+      </c>
+      <c r="O56">
+        <v>-438.3875201640001</v>
+      </c>
+      <c r="P56">
+        <v>-2218.506541436</v>
+      </c>
+      <c r="Q56">
+        <v>-615.4065414359998</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1565443640194534</v>
+      </c>
+      <c r="T56">
+        <v>1.694451938281055</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.02774067475718749</v>
+      </c>
+      <c r="W56">
+        <v>0.2454244731320164</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.1681253015587119</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2065396229402374</v>
+      </c>
+      <c r="C57">
+        <v>-3264.278645969261</v>
+      </c>
+      <c r="D57">
+        <v>5633.98635403074</v>
+      </c>
+      <c r="E57">
+        <v>-903.3349999999991</v>
+      </c>
+      <c r="F57">
+        <v>9701.065000000001</v>
+      </c>
+      <c r="G57">
+        <v>802.8</v>
+      </c>
+      <c r="H57">
+        <v>7033.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1220.7</v>
+      </c>
+      <c r="K57">
+        <v>1603.1</v>
+      </c>
+      <c r="L57">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M57">
+        <v>2316.614322</v>
+      </c>
+      <c r="N57">
+        <v>-2699.014322</v>
+      </c>
+      <c r="O57">
+        <v>-445.3373631300001</v>
+      </c>
+      <c r="P57">
+        <v>-2253.67695887</v>
+      </c>
+      <c r="Q57">
+        <v>-650.57695887</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1591609054421079</v>
+      </c>
+      <c r="T57">
+        <v>1.732106425798412</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.02723629885251136</v>
+      </c>
+      <c r="W57">
+        <v>0.2453040281659797</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.1650684778940081</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2085396229402374</v>
+      </c>
+      <c r="C58">
+        <v>-3504.794200433006</v>
+      </c>
+      <c r="D58">
+        <v>5569.853799566994</v>
+      </c>
+      <c r="E58">
+        <v>-726.9519999999993</v>
+      </c>
+      <c r="F58">
+        <v>9877.448</v>
+      </c>
+      <c r="G58">
+        <v>802.8</v>
+      </c>
+      <c r="H58">
+        <v>7033.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1220.7</v>
+      </c>
+      <c r="K58">
+        <v>1603.1</v>
+      </c>
+      <c r="L58">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M58">
+        <v>2358.7345824</v>
+      </c>
+      <c r="N58">
+        <v>-2741.1345824</v>
+      </c>
+      <c r="O58">
+        <v>-452.2872060960001</v>
+      </c>
+      <c r="P58">
+        <v>-2288.847376304</v>
+      </c>
+      <c r="Q58">
+        <v>-685.7473763040002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1618963805657922</v>
+      </c>
+      <c r="T58">
+        <v>1.771472480930193</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.02674993637300223</v>
+      </c>
+      <c r="W58">
+        <v>0.2451878848058729</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.1621208265030436</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2105396229402374</v>
+      </c>
+      <c r="C59">
+        <v>-3743.866126005148</v>
+      </c>
+      <c r="D59">
+        <v>5507.164873994852</v>
+      </c>
+      <c r="E59">
+        <v>-550.5689999999995</v>
+      </c>
+      <c r="F59">
+        <v>10053.831</v>
+      </c>
+      <c r="G59">
+        <v>802.8</v>
+      </c>
+      <c r="H59">
+        <v>7033.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1220.7</v>
+      </c>
+      <c r="K59">
+        <v>1603.1</v>
+      </c>
+      <c r="L59">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M59">
+        <v>2400.8548428</v>
+      </c>
+      <c r="N59">
+        <v>-2783.2548428</v>
+      </c>
+      <c r="O59">
+        <v>-459.2370490620001</v>
+      </c>
+      <c r="P59">
+        <v>-2324.017793738</v>
+      </c>
+      <c r="Q59">
+        <v>-720.917793738</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1647590870905781</v>
+      </c>
+      <c r="T59">
+        <v>1.812669515370431</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.02628063924365131</v>
+      </c>
+      <c r="W59">
+        <v>0.2450758166513839</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.1592766014766744</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2125396229402374</v>
+      </c>
+      <c r="C60">
+        <v>-3981.542624474055</v>
+      </c>
+      <c r="D60">
+        <v>5445.871375525943</v>
+      </c>
+      <c r="E60">
+        <v>-374.1860000000015</v>
+      </c>
+      <c r="F60">
+        <v>10230.214</v>
+      </c>
+      <c r="G60">
+        <v>802.8</v>
+      </c>
+      <c r="H60">
+        <v>7033.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1220.7</v>
+      </c>
+      <c r="K60">
+        <v>1603.1</v>
+      </c>
+      <c r="L60">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M60">
+        <v>2442.975103199999</v>
+      </c>
+      <c r="N60">
+        <v>-2825.375103199999</v>
+      </c>
+      <c r="O60">
+        <v>-466.1868920279999</v>
+      </c>
+      <c r="P60">
+        <v>-2359.188211171999</v>
+      </c>
+      <c r="Q60">
+        <v>-756.0882111719993</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.167758112973687</v>
+      </c>
+      <c r="T60">
+        <v>1.855828313355441</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.0258275247739332</v>
+      </c>
+      <c r="W60">
+        <v>0.2449676129160153</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.1565304531753526</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2145396229402374</v>
+      </c>
+      <c r="C61">
+        <v>-4217.869775348616</v>
+      </c>
+      <c r="D61">
+        <v>5385.927224651384</v>
+      </c>
+      <c r="E61">
+        <v>-197.8029999999999</v>
+      </c>
+      <c r="F61">
+        <v>10406.597</v>
+      </c>
+      <c r="G61">
+        <v>802.8</v>
+      </c>
+      <c r="H61">
+        <v>7033.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1220.7</v>
+      </c>
+      <c r="K61">
+        <v>1603.1</v>
+      </c>
+      <c r="L61">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M61">
+        <v>2485.0953636</v>
+      </c>
+      <c r="N61">
+        <v>-2867.4953636</v>
+      </c>
+      <c r="O61">
+        <v>-473.1367349940001</v>
+      </c>
+      <c r="P61">
+        <v>-2394.358628606</v>
+      </c>
+      <c r="Q61">
+        <v>-791.258628606</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1709034328023135</v>
+      </c>
+      <c r="T61">
+        <v>1.901092418559232</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.02538977011674788</v>
+      </c>
+      <c r="W61">
+        <v>0.2448630771038794</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.1538773946469569</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2165396229402374</v>
+      </c>
+      <c r="C62">
+        <v>-4452.891651389014</v>
+      </c>
+      <c r="D62">
+        <v>5327.288348610985</v>
+      </c>
+      <c r="E62">
+        <v>-21.42000000000007</v>
+      </c>
+      <c r="F62">
+        <v>10582.98</v>
+      </c>
+      <c r="G62">
+        <v>802.8</v>
+      </c>
+      <c r="H62">
+        <v>7033.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1220.7</v>
+      </c>
+      <c r="K62">
+        <v>1603.1</v>
+      </c>
+      <c r="L62">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M62">
+        <v>2527.215624</v>
+      </c>
+      <c r="N62">
+        <v>-2909.615624</v>
+      </c>
+      <c r="O62">
+        <v>-480.0865779600001</v>
+      </c>
+      <c r="P62">
+        <v>-2429.52904604</v>
+      </c>
+      <c r="Q62">
+        <v>-826.4290460400002</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1742060186223714</v>
+      </c>
+      <c r="T62">
+        <v>1.948619729023213</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.02496660728146875</v>
+      </c>
+      <c r="W62">
+        <v>0.2447620258188147</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.1513127714028411</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2185396229402374</v>
+      </c>
+      <c r="C63">
+        <v>-4686.650426671819</v>
+      </c>
+      <c r="D63">
+        <v>5269.91257332818</v>
+      </c>
+      <c r="E63">
+        <v>154.9629999999997</v>
+      </c>
+      <c r="F63">
+        <v>10759.363</v>
+      </c>
+      <c r="G63">
+        <v>802.8</v>
+      </c>
+      <c r="H63">
+        <v>7033.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1220.7</v>
+      </c>
+      <c r="K63">
+        <v>1603.1</v>
+      </c>
+      <c r="L63">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M63">
+        <v>2569.3358844</v>
+      </c>
+      <c r="N63">
+        <v>-2951.7358844</v>
+      </c>
+      <c r="O63">
+        <v>-487.0364209260001</v>
+      </c>
+      <c r="P63">
+        <v>-2464.699463474</v>
+      </c>
+      <c r="Q63">
+        <v>-861.599463474</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1776779678178168</v>
+      </c>
+      <c r="T63">
+        <v>1.998584337459705</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.02455731863751024</v>
+      </c>
+      <c r="W63">
+        <v>0.2446642876906375</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.1488322341667287</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2205396229402374</v>
+      </c>
+      <c r="C64">
+        <v>-4919.186477746182</v>
+      </c>
+      <c r="D64">
+        <v>5213.759522253817</v>
+      </c>
+      <c r="E64">
+        <v>331.3459999999995</v>
+      </c>
+      <c r="F64">
+        <v>10935.746</v>
+      </c>
+      <c r="G64">
+        <v>802.8</v>
+      </c>
+      <c r="H64">
+        <v>7033.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1220.7</v>
+      </c>
+      <c r="K64">
+        <v>1603.1</v>
+      </c>
+      <c r="L64">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M64">
+        <v>2611.4561448</v>
+      </c>
+      <c r="N64">
+        <v>-2993.8561448</v>
+      </c>
+      <c r="O64">
+        <v>-493.9862638920001</v>
+      </c>
+      <c r="P64">
+        <v>-2499.869880908</v>
+      </c>
+      <c r="Q64">
+        <v>-896.7698809079998</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1813326511814436</v>
+      </c>
+      <c r="T64">
+        <v>2.051178662129697</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.02416123285303427</v>
+      </c>
+      <c r="W64">
+        <v>0.2445697024053046</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.1464317142608138</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2225396229402374</v>
+      </c>
+      <c r="C65">
+        <v>-5150.538478391081</v>
+      </c>
+      <c r="D65">
+        <v>5158.790521608918</v>
+      </c>
+      <c r="E65">
+        <v>507.7289999999994</v>
+      </c>
+      <c r="F65">
+        <v>11112.129</v>
+      </c>
+      <c r="G65">
+        <v>802.8</v>
+      </c>
+      <c r="H65">
+        <v>7033.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1220.7</v>
+      </c>
+      <c r="K65">
+        <v>1603.1</v>
+      </c>
+      <c r="L65">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M65">
+        <v>2653.5764052</v>
+      </c>
+      <c r="N65">
+        <v>-3035.9764052</v>
+      </c>
+      <c r="O65">
+        <v>-500.9361068580001</v>
+      </c>
+      <c r="P65">
+        <v>-2535.040298342</v>
+      </c>
+      <c r="Q65">
+        <v>-931.940298342</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1851848849971583</v>
+      </c>
+      <c r="T65">
+        <v>2.106615923268338</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.02377772122044643</v>
+      </c>
+      <c r="W65">
+        <v>0.2444781198274426</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.1441074013360391</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2245396229402374</v>
+      </c>
+      <c r="C66">
+        <v>-5380.743488440903</v>
+      </c>
+      <c r="D66">
+        <v>5104.968511559097</v>
+      </c>
+      <c r="E66">
+        <v>684.112000000001</v>
+      </c>
+      <c r="F66">
+        <v>11288.512</v>
+      </c>
+      <c r="G66">
+        <v>802.8</v>
+      </c>
+      <c r="H66">
+        <v>7033.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1220.7</v>
+      </c>
+      <c r="K66">
+        <v>1603.1</v>
+      </c>
+      <c r="L66">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M66">
+        <v>2695.6966656</v>
+      </c>
+      <c r="N66">
+        <v>-3078.0966656</v>
+      </c>
+      <c r="O66">
+        <v>-507.8859498240001</v>
+      </c>
+      <c r="P66">
+        <v>-2570.210715776</v>
+      </c>
+      <c r="Q66">
+        <v>-967.1107157760002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1892511318026349</v>
+      </c>
+      <c r="T66">
+        <v>2.165133032248014</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.02340619432637695</v>
+      </c>
+      <c r="W66">
+        <v>0.2443893992051389</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.1418557231901632</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2265396229402374</v>
+      </c>
+      <c r="C67">
+        <v>-5609.837037108082</v>
+      </c>
+      <c r="D67">
+        <v>5052.257962891918</v>
+      </c>
+      <c r="E67">
+        <v>860.4950000000008</v>
+      </c>
+      <c r="F67">
+        <v>11464.895</v>
+      </c>
+      <c r="G67">
+        <v>802.8</v>
+      </c>
+      <c r="H67">
+        <v>7033.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1220.7</v>
+      </c>
+      <c r="K67">
+        <v>1603.1</v>
+      </c>
+      <c r="L67">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M67">
+        <v>2737.816926</v>
+      </c>
+      <c r="N67">
+        <v>-3120.216926</v>
+      </c>
+      <c r="O67">
+        <v>-514.8357927900001</v>
+      </c>
+      <c r="P67">
+        <v>-2605.38113321</v>
+      </c>
+      <c r="Q67">
+        <v>-1002.28113321</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1935497355684244</v>
+      </c>
+      <c r="T67">
+        <v>2.226993976026529</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.02304609902904807</v>
+      </c>
+      <c r="W67">
+        <v>0.2443034084481367</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.139673327448776</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2285396229402374</v>
+      </c>
+      <c r="C68">
+        <v>-5837.85320119652</v>
+      </c>
+      <c r="D68">
+        <v>5000.62479880348</v>
+      </c>
+      <c r="E68">
+        <v>1036.878000000001</v>
+      </c>
+      <c r="F68">
+        <v>11641.278</v>
+      </c>
+      <c r="G68">
+        <v>802.8</v>
+      </c>
+      <c r="H68">
+        <v>7033.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1220.7</v>
+      </c>
+      <c r="K68">
+        <v>1603.1</v>
+      </c>
+      <c r="L68">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M68">
+        <v>2779.9371864</v>
+      </c>
+      <c r="N68">
+        <v>-3162.3371864</v>
+      </c>
+      <c r="O68">
+        <v>-521.7856357560001</v>
+      </c>
+      <c r="P68">
+        <v>-2640.551550644</v>
+      </c>
+      <c r="Q68">
+        <v>-1037.451550644</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1981011983792605</v>
+      </c>
+      <c r="T68">
+        <v>2.292493798850839</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.02269691571042613</v>
+      </c>
+      <c r="W68">
+        <v>0.2442200234716498</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.1375570649116735</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2305396229402374</v>
+      </c>
+      <c r="C69">
+        <v>-6064.824678567523</v>
+      </c>
+      <c r="D69">
+        <v>4950.036321432477</v>
+      </c>
+      <c r="E69">
+        <v>1213.261</v>
+      </c>
+      <c r="F69">
+        <v>11817.661</v>
+      </c>
+      <c r="G69">
+        <v>802.8</v>
+      </c>
+      <c r="H69">
+        <v>7033.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1220.7</v>
+      </c>
+      <c r="K69">
+        <v>1603.1</v>
+      </c>
+      <c r="L69">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M69">
+        <v>2822.0574468</v>
+      </c>
+      <c r="N69">
+        <v>-3204.4574468</v>
+      </c>
+      <c r="O69">
+        <v>-528.7354787220002</v>
+      </c>
+      <c r="P69">
+        <v>-2675.721968078</v>
+      </c>
+      <c r="Q69">
+        <v>-1072.621968078</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2029285074210563</v>
+      </c>
+      <c r="T69">
+        <v>2.361963307906925</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.02235815577444963</v>
+      </c>
+      <c r="W69">
+        <v>0.2441391275989386</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.1355039743906039</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2325396229402374</v>
+      </c>
+      <c r="C70">
+        <v>-6290.782857191164</v>
+      </c>
+      <c r="D70">
+        <v>4900.461142808836</v>
+      </c>
+      <c r="E70">
+        <v>1389.644</v>
+      </c>
+      <c r="F70">
+        <v>11994.044</v>
+      </c>
+      <c r="G70">
+        <v>802.8</v>
+      </c>
+      <c r="H70">
+        <v>7033.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1220.7</v>
+      </c>
+      <c r="K70">
+        <v>1603.1</v>
+      </c>
+      <c r="L70">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M70">
+        <v>2864.1777072</v>
+      </c>
+      <c r="N70">
+        <v>-3246.5777072</v>
+      </c>
+      <c r="O70">
+        <v>-535.6853216880002</v>
+      </c>
+      <c r="P70">
+        <v>-2710.892385512</v>
+      </c>
+      <c r="Q70">
+        <v>-1107.792385512</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2080575232779643</v>
+      </c>
+      <c r="T70">
+        <v>2.435774661279016</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.02202935936600184</v>
+      </c>
+      <c r="W70">
+        <v>0.2440606110166013</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.1335112688848596</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2345396229402374</v>
+      </c>
+      <c r="C71">
+        <v>-6515.757880089389</v>
+      </c>
+      <c r="D71">
+        <v>4851.869119910611</v>
+      </c>
+      <c r="E71">
+        <v>1566.027</v>
+      </c>
+      <c r="F71">
+        <v>12170.427</v>
+      </c>
+      <c r="G71">
+        <v>802.8</v>
+      </c>
+      <c r="H71">
+        <v>7033.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1220.7</v>
+      </c>
+      <c r="K71">
+        <v>1603.1</v>
+      </c>
+      <c r="L71">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M71">
+        <v>2906.2979676</v>
+      </c>
+      <c r="N71">
+        <v>-3288.6979676</v>
+      </c>
+      <c r="O71">
+        <v>-542.6351646540002</v>
+      </c>
+      <c r="P71">
+        <v>-2746.062802946</v>
+      </c>
+      <c r="Q71">
+        <v>-1142.962802946</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2135174433837051</v>
+      </c>
+      <c r="T71">
+        <v>2.514348037449307</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.0217100932882337</v>
+      </c>
+      <c r="W71">
+        <v>0.2439843702772302</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.1315763229589921</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2365396229402374</v>
+      </c>
+      <c r="C72">
+        <v>-6739.778706453335</v>
+      </c>
+      <c r="D72">
+        <v>4804.231293546666</v>
+      </c>
+      <c r="E72">
+        <v>1742.410000000002</v>
+      </c>
+      <c r="F72">
+        <v>12346.81</v>
+      </c>
+      <c r="G72">
+        <v>802.8</v>
+      </c>
+      <c r="H72">
+        <v>7033.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1220.7</v>
+      </c>
+      <c r="K72">
+        <v>1603.1</v>
+      </c>
+      <c r="L72">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M72">
+        <v>2948.418228</v>
+      </c>
+      <c r="N72">
+        <v>-3330.818228</v>
+      </c>
+      <c r="O72">
+        <v>-549.5850076200002</v>
+      </c>
+      <c r="P72">
+        <v>-2781.23322038</v>
+      </c>
+      <c r="Q72">
+        <v>-1178.13322038</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2193413581631619</v>
+      </c>
+      <c r="T72">
+        <v>2.598159638697617</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.02139994909840178</v>
+      </c>
+      <c r="W72">
+        <v>0.2439103078446984</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.1296966612024348</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2385396229402374</v>
+      </c>
+      <c r="C73">
+        <v>-6962.873169195153</v>
+      </c>
+      <c r="D73">
+        <v>4757.519830804846</v>
+      </c>
+      <c r="E73">
+        <v>1918.793</v>
+      </c>
+      <c r="F73">
+        <v>12523.193</v>
+      </c>
+      <c r="G73">
+        <v>802.8</v>
+      </c>
+      <c r="H73">
+        <v>7033.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1220.7</v>
+      </c>
+      <c r="K73">
+        <v>1603.1</v>
+      </c>
+      <c r="L73">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M73">
+        <v>2990.5384884</v>
+      </c>
+      <c r="N73">
+        <v>-3372.9384884</v>
+      </c>
+      <c r="O73">
+        <v>-556.5348505860002</v>
+      </c>
+      <c r="P73">
+        <v>-2816.403637814</v>
+      </c>
+      <c r="Q73">
+        <v>-1213.303637814</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2255669222377536</v>
+      </c>
+      <c r="T73">
+        <v>2.687751350376844</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.02109854136462148</v>
+      </c>
+      <c r="W73">
+        <v>0.2438383316778716</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.1278699476643725</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2405396229402374</v>
+      </c>
+      <c r="C74">
+        <v>-7185.068029174749</v>
+      </c>
+      <c r="D74">
+        <v>4711.70797082525</v>
+      </c>
+      <c r="E74">
+        <v>2095.175999999999</v>
+      </c>
+      <c r="F74">
+        <v>12699.576</v>
+      </c>
+      <c r="G74">
+        <v>802.8</v>
+      </c>
+      <c r="H74">
+        <v>7033.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1220.7</v>
+      </c>
+      <c r="K74">
+        <v>1603.1</v>
+      </c>
+      <c r="L74">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M74">
+        <v>3032.6587488</v>
+      </c>
+      <c r="N74">
+        <v>-3415.0587488</v>
+      </c>
+      <c r="O74">
+        <v>-563.4846935520002</v>
+      </c>
+      <c r="P74">
+        <v>-2851.574055248</v>
+      </c>
+      <c r="Q74">
+        <v>-1248.474055248</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2322371694605306</v>
+      </c>
+      <c r="T74">
+        <v>2.783742470033161</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.02080550606789063</v>
+      </c>
+      <c r="W74">
+        <v>0.2437683548490123</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.1260939761690341</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2425396229402374</v>
+      </c>
+      <c r="C75">
+        <v>-7406.389026323337</v>
+      </c>
+      <c r="D75">
+        <v>4666.769973676662</v>
+      </c>
+      <c r="E75">
+        <v>2271.558999999999</v>
+      </c>
+      <c r="F75">
+        <v>12875.959</v>
+      </c>
+      <c r="G75">
+        <v>802.8</v>
+      </c>
+      <c r="H75">
+        <v>7033.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1220.7</v>
+      </c>
+      <c r="K75">
+        <v>1603.1</v>
+      </c>
+      <c r="L75">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M75">
+        <v>3074.7790092</v>
+      </c>
+      <c r="N75">
+        <v>-3457.1790092</v>
+      </c>
+      <c r="O75">
+        <v>-570.4345365180002</v>
+      </c>
+      <c r="P75">
+        <v>-2886.744472682</v>
+      </c>
+      <c r="Q75">
+        <v>-1283.644472682</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2394015090701798</v>
+      </c>
+      <c r="T75">
+        <v>2.886844042997351</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.02052049913545377</v>
+      </c>
+      <c r="W75">
+        <v>0.2437002951935464</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.1243666614269925</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2445396229402374</v>
+      </c>
+      <c r="C76">
+        <v>-7626.860927869127</v>
+      </c>
+      <c r="D76">
+        <v>4622.681072130871</v>
+      </c>
+      <c r="E76">
+        <v>2447.941999999999</v>
+      </c>
+      <c r="F76">
+        <v>13052.342</v>
+      </c>
+      <c r="G76">
+        <v>802.8</v>
+      </c>
+      <c r="H76">
+        <v>7033.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1220.7</v>
+      </c>
+      <c r="K76">
+        <v>1603.1</v>
+      </c>
+      <c r="L76">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M76">
+        <v>3116.8992696</v>
+      </c>
+      <c r="N76">
+        <v>-3499.2992696</v>
+      </c>
+      <c r="O76">
+        <v>-577.3843794840002</v>
+      </c>
+      <c r="P76">
+        <v>-2921.914890116</v>
+      </c>
+      <c r="Q76">
+        <v>-1318.814890116</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2471169517267252</v>
+      </c>
+      <c r="T76">
+        <v>2.997876506189558</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.02024319509308277</v>
+      </c>
+      <c r="W76">
+        <v>0.2436340749882282</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.1226860308671684</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2465396229402374</v>
+      </c>
+      <c r="C77">
+        <v>-7846.507573854948</v>
+      </c>
+      <c r="D77">
+        <v>4579.417426145051</v>
+      </c>
+      <c r="E77">
+        <v>2624.324999999999</v>
+      </c>
+      <c r="F77">
+        <v>13228.725</v>
+      </c>
+      <c r="G77">
+        <v>802.8</v>
+      </c>
+      <c r="H77">
+        <v>7033.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1220.7</v>
+      </c>
+      <c r="K77">
+        <v>1603.1</v>
+      </c>
+      <c r="L77">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M77">
+        <v>3159.01953</v>
+      </c>
+      <c r="N77">
+        <v>-3541.41953</v>
+      </c>
+      <c r="O77">
+        <v>-584.3342224500002</v>
+      </c>
+      <c r="P77">
+        <v>-2957.08530755</v>
+      </c>
+      <c r="Q77">
+        <v>-1353.98530755</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2554496297957942</v>
+      </c>
+      <c r="T77">
+        <v>3.11779156643714</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.019973285825175</v>
+      </c>
+      <c r="W77">
+        <v>0.2435696206550518</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.1210502171222727</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2485396229402374</v>
+      </c>
+      <c r="C78">
+        <v>-8065.351920123536</v>
+      </c>
+      <c r="D78">
+        <v>4536.956079876464</v>
+      </c>
+      <c r="E78">
+        <v>2800.708000000001</v>
+      </c>
+      <c r="F78">
+        <v>13405.108</v>
+      </c>
+      <c r="G78">
+        <v>802.8</v>
+      </c>
+      <c r="H78">
+        <v>7033.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1220.7</v>
+      </c>
+      <c r="K78">
+        <v>1603.1</v>
+      </c>
+      <c r="L78">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M78">
+        <v>3201.1397904</v>
+      </c>
+      <c r="N78">
+        <v>-3583.5397904</v>
+      </c>
+      <c r="O78">
+        <v>-591.2840654160002</v>
+      </c>
+      <c r="P78">
+        <v>-2992.255724984</v>
+      </c>
+      <c r="Q78">
+        <v>-1389.155724984</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2644766977039523</v>
+      </c>
+      <c r="T78">
+        <v>3.247699548372021</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.01971047943273849</v>
+      </c>
+      <c r="W78">
+        <v>0.243506862488538</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.1194574511075059</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2505396229402375</v>
+      </c>
+      <c r="C79">
+        <v>-8283.416078933424</v>
+      </c>
+      <c r="D79">
+        <v>4495.274921066577</v>
+      </c>
+      <c r="E79">
+        <v>2977.091</v>
+      </c>
+      <c r="F79">
+        <v>13581.491</v>
+      </c>
+      <c r="G79">
+        <v>802.8</v>
+      </c>
+      <c r="H79">
+        <v>7033.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1220.7</v>
+      </c>
+      <c r="K79">
+        <v>1603.1</v>
+      </c>
+      <c r="L79">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M79">
+        <v>3243.2600508</v>
+      </c>
+      <c r="N79">
+        <v>-3625.6600508</v>
+      </c>
+      <c r="O79">
+        <v>-598.2339083820001</v>
+      </c>
+      <c r="P79">
+        <v>-3027.426142418</v>
+      </c>
+      <c r="Q79">
+        <v>-1424.326142418</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2742887280389068</v>
+      </c>
+      <c r="T79">
+        <v>3.38890387656211</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.01945449918036526</v>
+      </c>
+      <c r="W79">
+        <v>0.2434457344042713</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.1179060556385774</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2525396229402375</v>
+      </c>
+      <c r="C80">
+        <v>-8500.72135735634</v>
+      </c>
+      <c r="D80">
+        <v>4454.352642643659</v>
+      </c>
+      <c r="E80">
+        <v>3153.474</v>
+      </c>
+      <c r="F80">
+        <v>13757.874</v>
+      </c>
+      <c r="G80">
+        <v>802.8</v>
+      </c>
+      <c r="H80">
+        <v>7033.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1220.7</v>
+      </c>
+      <c r="K80">
+        <v>1603.1</v>
+      </c>
+      <c r="L80">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M80">
+        <v>3285.3803112</v>
+      </c>
+      <c r="N80">
+        <v>-3667.7803112</v>
+      </c>
+      <c r="O80">
+        <v>-605.1837513480001</v>
+      </c>
+      <c r="P80">
+        <v>-3062.596559852</v>
+      </c>
+      <c r="Q80">
+        <v>-1459.496559852</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2849927611315844</v>
+      </c>
+      <c r="T80">
+        <v>3.542944961860387</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.01920508252420673</v>
+      </c>
+      <c r="W80">
+        <v>0.2433861737067806</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.1163944395406469</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2545396229402374</v>
+      </c>
+      <c r="C81">
+        <v>-8717.288293596288</v>
+      </c>
+      <c r="D81">
+        <v>4414.168706403711</v>
+      </c>
+      <c r="E81">
+        <v>3329.857</v>
+      </c>
+      <c r="F81">
+        <v>13934.257</v>
+      </c>
+      <c r="G81">
+        <v>802.8</v>
+      </c>
+      <c r="H81">
+        <v>7033.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1220.7</v>
+      </c>
+      <c r="K81">
+        <v>1603.1</v>
+      </c>
+      <c r="L81">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M81">
+        <v>3327.5005716</v>
+      </c>
+      <c r="N81">
+        <v>-3709.9005716</v>
+      </c>
+      <c r="O81">
+        <v>-612.1335943140001</v>
+      </c>
+      <c r="P81">
+        <v>-3097.766977286</v>
+      </c>
+      <c r="Q81">
+        <v>-1494.666977286</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2967162259473742</v>
+      </c>
+      <c r="T81">
+        <v>3.711656626710882</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.01896198021377373</v>
+      </c>
+      <c r="W81">
+        <v>0.2433281208750492</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.1149210922046893</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2565396229402374</v>
+      </c>
+      <c r="C82">
+        <v>-8933.136691360292</v>
+      </c>
+      <c r="D82">
+        <v>4374.703308639707</v>
+      </c>
+      <c r="E82">
+        <v>3506.24</v>
+      </c>
+      <c r="F82">
+        <v>14110.64</v>
+      </c>
+      <c r="G82">
+        <v>802.8</v>
+      </c>
+      <c r="H82">
+        <v>7033.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1220.7</v>
+      </c>
+      <c r="K82">
+        <v>1603.1</v>
+      </c>
+      <c r="L82">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M82">
+        <v>3369.620832</v>
+      </c>
+      <c r="N82">
+        <v>-3752.020832</v>
+      </c>
+      <c r="O82">
+        <v>-619.0834372800001</v>
+      </c>
+      <c r="P82">
+        <v>-3132.93739472</v>
+      </c>
+      <c r="Q82">
+        <v>-1529.83739472</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3096120372447428</v>
+      </c>
+      <c r="T82">
+        <v>3.897239458046426</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.01872495546110156</v>
+      </c>
+      <c r="W82">
+        <v>0.2432715193641111</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.1134845785521308</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2585396229402374</v>
+      </c>
+      <c r="C83">
+        <v>-9148.285652401728</v>
+      </c>
+      <c r="D83">
+        <v>4335.937347598273</v>
+      </c>
+      <c r="E83">
+        <v>3682.623000000001</v>
+      </c>
+      <c r="F83">
+        <v>14287.023</v>
+      </c>
+      <c r="G83">
+        <v>802.8</v>
+      </c>
+      <c r="H83">
+        <v>7033.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1220.7</v>
+      </c>
+      <c r="K83">
+        <v>1603.1</v>
+      </c>
+      <c r="L83">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M83">
+        <v>3411.741092400001</v>
+      </c>
+      <c r="N83">
+        <v>-3794.1410924</v>
+      </c>
+      <c r="O83">
+        <v>-626.0332802460001</v>
+      </c>
+      <c r="P83">
+        <v>-3168.107812154</v>
+      </c>
+      <c r="Q83">
+        <v>-1565.007812154</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3238653023628872</v>
+      </c>
+      <c r="T83">
+        <v>4.102357324259396</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.01849378317145833</v>
+      </c>
+      <c r="W83">
+        <v>0.2432163154213442</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.1120835343724746</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2605396229402374</v>
+      </c>
+      <c r="C84">
+        <v>-9362.753607348573</v>
+      </c>
+      <c r="D84">
+        <v>4297.852392651427</v>
+      </c>
+      <c r="E84">
+        <v>3859.006000000001</v>
+      </c>
+      <c r="F84">
+        <v>14463.406</v>
+      </c>
+      <c r="G84">
+        <v>802.8</v>
+      </c>
+      <c r="H84">
+        <v>7033.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1220.7</v>
+      </c>
+      <c r="K84">
+        <v>1603.1</v>
+      </c>
+      <c r="L84">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M84">
+        <v>3453.861352800001</v>
+      </c>
+      <c r="N84">
+        <v>-3836.2613528</v>
+      </c>
+      <c r="O84">
+        <v>-632.9831232120001</v>
+      </c>
+      <c r="P84">
+        <v>-3203.278229588</v>
+      </c>
+      <c r="Q84">
+        <v>-1600.178229588</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3397022636052699</v>
+      </c>
+      <c r="T84">
+        <v>4.33026606449603</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.01826824923034298</v>
+      </c>
+      <c r="W84">
+        <v>0.2431624579162059</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.1107166620020785</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2625396229402374</v>
+      </c>
+      <c r="C85">
+        <v>-9576.558344921126</v>
+      </c>
+      <c r="D85">
+        <v>4260.430655078875</v>
+      </c>
+      <c r="E85">
+        <v>4035.389000000001</v>
+      </c>
+      <c r="F85">
+        <v>14639.789</v>
+      </c>
+      <c r="G85">
+        <v>802.8</v>
+      </c>
+      <c r="H85">
+        <v>7033.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1220.7</v>
+      </c>
+      <c r="K85">
+        <v>1603.1</v>
+      </c>
+      <c r="L85">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M85">
+        <v>3495.981613200001</v>
+      </c>
+      <c r="N85">
+        <v>-3878.3816132</v>
+      </c>
+      <c r="O85">
+        <v>-639.9329661780001</v>
+      </c>
+      <c r="P85">
+        <v>-3238.448647022</v>
+      </c>
+      <c r="Q85">
+        <v>-1635.348647022</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.357402396758521</v>
+      </c>
+      <c r="T85">
+        <v>4.584987597701678</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.0180481498420256</v>
+      </c>
+      <c r="W85">
+        <v>0.2431098981822757</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.1093827263153067</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2645396229402374</v>
+      </c>
+      <c r="C86">
+        <v>-9789.717039636458</v>
+      </c>
+      <c r="D86">
+        <v>4223.65496036354</v>
+      </c>
+      <c r="E86">
+        <v>4211.771999999999</v>
+      </c>
+      <c r="F86">
+        <v>14816.172</v>
+      </c>
+      <c r="G86">
+        <v>802.8</v>
+      </c>
+      <c r="H86">
+        <v>7033.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1220.7</v>
+      </c>
+      <c r="K86">
+        <v>1603.1</v>
+      </c>
+      <c r="L86">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M86">
+        <v>3538.1018736</v>
+      </c>
+      <c r="N86">
+        <v>-3920.501873599999</v>
+      </c>
+      <c r="O86">
+        <v>-646.882809144</v>
+      </c>
+      <c r="P86">
+        <v>-3273.619064455999</v>
+      </c>
+      <c r="Q86">
+        <v>-1670.519064455999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3773150465559285</v>
+      </c>
+      <c r="T86">
+        <v>4.871549322558031</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.01783329091533482</v>
+      </c>
+      <c r="W86">
+        <v>0.243058589870582</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.1080805510020291</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2665396229402374</v>
+      </c>
+      <c r="C87">
+        <v>-10002.24627809035</v>
+      </c>
+      <c r="D87">
+        <v>4187.508721909649</v>
+      </c>
+      <c r="E87">
+        <v>4388.154999999999</v>
+      </c>
+      <c r="F87">
+        <v>14992.555</v>
+      </c>
+      <c r="G87">
+        <v>802.8</v>
+      </c>
+      <c r="H87">
+        <v>7033.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1220.7</v>
+      </c>
+      <c r="K87">
+        <v>1603.1</v>
+      </c>
+      <c r="L87">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M87">
+        <v>3580.222134</v>
+      </c>
+      <c r="N87">
+        <v>-3962.622133999999</v>
+      </c>
+      <c r="O87">
+        <v>-653.83265211</v>
+      </c>
+      <c r="P87">
+        <v>-3308.789481889999</v>
+      </c>
+      <c r="Q87">
+        <v>-1705.68948189</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3998827163263237</v>
+      </c>
+      <c r="T87">
+        <v>5.196319277395233</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.01762348749280147</v>
+      </c>
+      <c r="W87">
+        <v>0.243008488813281</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.1068090151078875</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2685396229402374</v>
+      </c>
+      <c r="C88">
+        <v>-10214.16208390108</v>
+      </c>
+      <c r="D88">
+        <v>4151.975916098917</v>
+      </c>
+      <c r="E88">
+        <v>4564.537999999999</v>
+      </c>
+      <c r="F88">
+        <v>15168.938</v>
+      </c>
+      <c r="G88">
+        <v>802.8</v>
+      </c>
+      <c r="H88">
+        <v>7033.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1220.7</v>
+      </c>
+      <c r="K88">
+        <v>1603.1</v>
+      </c>
+      <c r="L88">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M88">
+        <v>3622.3423944</v>
+      </c>
+      <c r="N88">
+        <v>-4004.742394399999</v>
+      </c>
+      <c r="O88">
+        <v>-660.782495076</v>
+      </c>
+      <c r="P88">
+        <v>-3343.959899323999</v>
+      </c>
+      <c r="Q88">
+        <v>-1740.859899323999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4256743389210611</v>
+      </c>
+      <c r="T88">
+        <v>5.567484940066321</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.01741856321962936</v>
+      </c>
+      <c r="W88">
+        <v>0.2429595528968475</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.1055670498159353</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2705396229402374</v>
+      </c>
+      <c r="C89">
+        <v>-10425.479941394</v>
+      </c>
+      <c r="D89">
+        <v>4117.041058606001</v>
+      </c>
+      <c r="E89">
+        <v>4740.921</v>
+      </c>
+      <c r="F89">
+        <v>15345.321</v>
+      </c>
+      <c r="G89">
+        <v>802.8</v>
+      </c>
+      <c r="H89">
+        <v>7033.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1220.7</v>
+      </c>
+      <c r="K89">
+        <v>1603.1</v>
+      </c>
+      <c r="L89">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M89">
+        <v>3664.4626548</v>
+      </c>
+      <c r="N89">
+        <v>-4046.8626548</v>
+      </c>
+      <c r="O89">
+        <v>-667.7323380420002</v>
+      </c>
+      <c r="P89">
+        <v>-3379.130316758</v>
+      </c>
+      <c r="Q89">
+        <v>-1776.030316758</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4554339034534504</v>
+      </c>
+      <c r="T89">
+        <v>5.995753012379115</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.01721834984928879</v>
+      </c>
+      <c r="W89">
+        <v>0.2429117419440102</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.1043536354502352</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2725396229402374</v>
+      </c>
+      <c r="C90">
+        <v>-10636.21481810034</v>
+      </c>
+      <c r="D90">
+        <v>4082.68918189966</v>
+      </c>
+      <c r="E90">
+        <v>4917.304</v>
+      </c>
+      <c r="F90">
+        <v>15521.704</v>
+      </c>
+      <c r="G90">
+        <v>802.8</v>
+      </c>
+      <c r="H90">
+        <v>7033.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1220.7</v>
+      </c>
+      <c r="K90">
+        <v>1603.1</v>
+      </c>
+      <c r="L90">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M90">
+        <v>3706.5829152</v>
+      </c>
+      <c r="N90">
+        <v>-4088.9829152</v>
+      </c>
+      <c r="O90">
+        <v>-674.6821810080002</v>
+      </c>
+      <c r="P90">
+        <v>-3414.300734192</v>
+      </c>
+      <c r="Q90">
+        <v>-1811.200734192</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4901533954079046</v>
+      </c>
+      <c r="T90">
+        <v>6.495399096744042</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.0170226867828196</v>
+      </c>
+      <c r="W90">
+        <v>0.2428650176037373</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.1031677986837551</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2745396229402374</v>
+      </c>
+      <c r="C91">
+        <v>-10846.38118613905</v>
+      </c>
+      <c r="D91">
+        <v>4048.905813860954</v>
+      </c>
+      <c r="E91">
+        <v>5093.687</v>
+      </c>
+      <c r="F91">
+        <v>15698.087</v>
+      </c>
+      <c r="G91">
+        <v>802.8</v>
+      </c>
+      <c r="H91">
+        <v>7033.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1220.7</v>
+      </c>
+      <c r="K91">
+        <v>1603.1</v>
+      </c>
+      <c r="L91">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M91">
+        <v>3748.7031756</v>
+      </c>
+      <c r="N91">
+        <v>-4131.1031756</v>
+      </c>
+      <c r="O91">
+        <v>-681.6320239740002</v>
+      </c>
+      <c r="P91">
+        <v>-3449.471151626</v>
+      </c>
+      <c r="Q91">
+        <v>-1846.371151626</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5311855222631687</v>
+      </c>
+      <c r="T91">
+        <v>7.085889923720774</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.01683142063919241</v>
+      </c>
+      <c r="W91">
+        <v>0.2428193432486392</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.1020086099344995</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2765396229402374</v>
+      </c>
+      <c r="C92">
+        <v>-11055.99304254567</v>
+      </c>
+      <c r="D92">
+        <v>4015.67695745433</v>
+      </c>
+      <c r="E92">
+        <v>5270.07</v>
+      </c>
+      <c r="F92">
+        <v>15874.47</v>
+      </c>
+      <c r="G92">
+        <v>802.8</v>
+      </c>
+      <c r="H92">
+        <v>7033.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1220.7</v>
+      </c>
+      <c r="K92">
+        <v>1603.1</v>
+      </c>
+      <c r="L92">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M92">
+        <v>3790.823436</v>
+      </c>
+      <c r="N92">
+        <v>-4173.223436</v>
+      </c>
+      <c r="O92">
+        <v>-688.5818669400002</v>
+      </c>
+      <c r="P92">
+        <v>-3484.64156906</v>
+      </c>
+      <c r="Q92">
+        <v>-1881.54156906</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5804240744894857</v>
+      </c>
+      <c r="T92">
+        <v>7.794478916092852</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.0166444048543125</v>
+      </c>
+      <c r="W92">
+        <v>0.2427746838792098</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.1008751809352273</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2785396229402374</v>
+      </c>
+      <c r="C93">
+        <v>-11265.06392860846</v>
+      </c>
+      <c r="D93">
+        <v>3982.989071391545</v>
+      </c>
+      <c r="E93">
+        <v>5446.453</v>
+      </c>
+      <c r="F93">
+        <v>16050.853</v>
+      </c>
+      <c r="G93">
+        <v>802.8</v>
+      </c>
+      <c r="H93">
+        <v>7033.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1220.7</v>
+      </c>
+      <c r="K93">
+        <v>1603.1</v>
+      </c>
+      <c r="L93">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M93">
+        <v>3832.9436964</v>
+      </c>
+      <c r="N93">
+        <v>-4215.3436964</v>
+      </c>
+      <c r="O93">
+        <v>-695.5317099060002</v>
+      </c>
+      <c r="P93">
+        <v>-3519.811986494</v>
+      </c>
+      <c r="Q93">
+        <v>-1916.711986494</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6406045272105398</v>
+      </c>
+      <c r="T93">
+        <v>8.66053212899206</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.01646149930646291</v>
+      </c>
+      <c r="W93">
+        <v>0.2427310060343834</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.0997666624634117</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2805396229402374</v>
+      </c>
+      <c r="C94">
+        <v>-11473.60694826761</v>
+      </c>
+      <c r="D94">
+        <v>3950.829051732387</v>
+      </c>
+      <c r="E94">
+        <v>5622.836000000001</v>
+      </c>
+      <c r="F94">
+        <v>16227.236</v>
+      </c>
+      <c r="G94">
+        <v>802.8</v>
+      </c>
+      <c r="H94">
+        <v>7033.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1220.7</v>
+      </c>
+      <c r="K94">
+        <v>1603.1</v>
+      </c>
+      <c r="L94">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M94">
+        <v>3875.063956800001</v>
+      </c>
+      <c r="N94">
+        <v>-4257.4639568</v>
+      </c>
+      <c r="O94">
+        <v>-702.4815528720002</v>
+      </c>
+      <c r="P94">
+        <v>-3554.982403928</v>
+      </c>
+      <c r="Q94">
+        <v>-1951.882403928</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7158300931118573</v>
+      </c>
+      <c r="T94">
+        <v>9.743098645116069</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.01628256996617527</v>
+      </c>
+      <c r="W94">
+        <v>0.2426882777079227</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.09868224221924393</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2825396229402374</v>
+      </c>
+      <c r="C95">
+        <v>-11681.63478563041</v>
+      </c>
+      <c r="D95">
+        <v>3919.184214369588</v>
+      </c>
+      <c r="E95">
+        <v>5799.218999999999</v>
+      </c>
+      <c r="F95">
+        <v>16403.619</v>
+      </c>
+      <c r="G95">
+        <v>802.8</v>
+      </c>
+      <c r="H95">
+        <v>7033.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1220.7</v>
+      </c>
+      <c r="K95">
+        <v>1603.1</v>
+      </c>
+      <c r="L95">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M95">
+        <v>3917.1842172</v>
+      </c>
+      <c r="N95">
+        <v>-4299.584217199999</v>
+      </c>
+      <c r="O95">
+        <v>-709.4313958380001</v>
+      </c>
+      <c r="P95">
+        <v>-3590.152821361999</v>
+      </c>
+      <c r="Q95">
+        <v>-1987.052821362</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8125486778421229</v>
+      </c>
+      <c r="T95">
+        <v>11.13496988013265</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.01610748856868952</v>
+      </c>
+      <c r="W95">
+        <v>0.2426464682702031</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.09762114284054246</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2845396229402374</v>
+      </c>
+      <c r="C96">
+        <v>-11889.15972165118</v>
+      </c>
+      <c r="D96">
+        <v>3888.042278348822</v>
+      </c>
+      <c r="E96">
+        <v>5975.602000000001</v>
+      </c>
+      <c r="F96">
+        <v>16580.002</v>
+      </c>
+      <c r="G96">
+        <v>802.8</v>
+      </c>
+      <c r="H96">
+        <v>7033.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1220.7</v>
+      </c>
+      <c r="K96">
+        <v>1603.1</v>
+      </c>
+      <c r="L96">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M96">
+        <v>3959.3044776</v>
+      </c>
+      <c r="N96">
+        <v>-4341.7044776</v>
+      </c>
+      <c r="O96">
+        <v>-716.3812388040002</v>
+      </c>
+      <c r="P96">
+        <v>-3625.323238796</v>
+      </c>
+      <c r="Q96">
+        <v>-2022.223238796</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9415067908158101</v>
+      </c>
+      <c r="T96">
+        <v>12.9907981934881</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.01593613230732048</v>
+      </c>
+      <c r="W96">
+        <v>0.2426055483949881</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.09658262004436646</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2865396229402374</v>
+      </c>
+      <c r="C97">
+        <v>-12096.19365002235</v>
+      </c>
+      <c r="D97">
+        <v>3857.391349977653</v>
+      </c>
+      <c r="E97">
+        <v>6151.985000000002</v>
+      </c>
+      <c r="F97">
+        <v>16756.385</v>
+      </c>
+      <c r="G97">
+        <v>802.8</v>
+      </c>
+      <c r="H97">
+        <v>7033.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1220.7</v>
+      </c>
+      <c r="K97">
+        <v>1603.1</v>
+      </c>
+      <c r="L97">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M97">
+        <v>4001.424738000001</v>
+      </c>
+      <c r="N97">
+        <v>-4383.824738</v>
+      </c>
+      <c r="O97">
+        <v>-723.3310817700002</v>
+      </c>
+      <c r="P97">
+        <v>-3660.49365623</v>
+      </c>
+      <c r="Q97">
+        <v>-2057.39365623</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.122048148978973</v>
+      </c>
+      <c r="T97">
+        <v>15.58895783218572</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.01576838354619079</v>
+      </c>
+      <c r="W97">
+        <v>0.2425654899908304</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.09556596088600466</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2885396229402374</v>
+      </c>
+      <c r="C98">
+        <v>-12302.74809231974</v>
+      </c>
+      <c r="D98">
+        <v>3827.219907680262</v>
+      </c>
+      <c r="E98">
+        <v>6328.368</v>
+      </c>
+      <c r="F98">
+        <v>16932.768</v>
+      </c>
+      <c r="G98">
+        <v>802.8</v>
+      </c>
+      <c r="H98">
+        <v>7033.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1220.7</v>
+      </c>
+      <c r="K98">
+        <v>1603.1</v>
+      </c>
+      <c r="L98">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M98">
+        <v>4043.5449984</v>
+      </c>
+      <c r="N98">
+        <v>-4425.9449984</v>
+      </c>
+      <c r="O98">
+        <v>-730.2809247360002</v>
+      </c>
+      <c r="P98">
+        <v>-3695.664073664</v>
+      </c>
+      <c r="Q98">
+        <v>-2092.564073664</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.392860186223713</v>
+      </c>
+      <c r="T98">
+        <v>19.48619729023211</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.01560412955091797</v>
+      </c>
+      <c r="W98">
+        <v>0.2425262661367592</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.09457048212677566</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2905396229402374</v>
+      </c>
+      <c r="C99">
+        <v>-12508.83421244257</v>
+      </c>
+      <c r="D99">
+        <v>3797.516787557428</v>
+      </c>
+      <c r="E99">
+        <v>6504.750999999998</v>
+      </c>
+      <c r="F99">
+        <v>17109.151</v>
+      </c>
+      <c r="G99">
+        <v>802.8</v>
+      </c>
+      <c r="H99">
+        <v>7033.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1220.7</v>
+      </c>
+      <c r="K99">
+        <v>1603.1</v>
+      </c>
+      <c r="L99">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M99">
+        <v>4085.6652588</v>
+      </c>
+      <c r="N99">
+        <v>-4468.065258799999</v>
+      </c>
+      <c r="O99">
+        <v>-737.2307677020001</v>
+      </c>
+      <c r="P99">
+        <v>-3730.834491097999</v>
+      </c>
+      <c r="Q99">
+        <v>-2127.734491098</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.844213581631618</v>
+      </c>
+      <c r="T99">
+        <v>25.98159638697615</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.01544326223596005</v>
+      </c>
+      <c r="W99">
+        <v>0.2424878510219473</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.09359552870278809</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2925396229402374</v>
+      </c>
+      <c r="C100">
+        <v>-12714.46283038625</v>
+      </c>
+      <c r="D100">
+        <v>3768.271169613751</v>
+      </c>
+      <c r="E100">
+        <v>6681.134</v>
+      </c>
+      <c r="F100">
+        <v>17285.534</v>
+      </c>
+      <c r="G100">
+        <v>802.8</v>
+      </c>
+      <c r="H100">
+        <v>7033.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1220.7</v>
+      </c>
+      <c r="K100">
+        <v>1603.1</v>
+      </c>
+      <c r="L100">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M100">
+        <v>4127.7855192</v>
+      </c>
+      <c r="N100">
+        <v>-4510.185519199999</v>
+      </c>
+      <c r="O100">
+        <v>-744.1806106680001</v>
+      </c>
+      <c r="P100">
+        <v>-3766.004908531999</v>
+      </c>
+      <c r="Q100">
+        <v>-2162.904908531999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.746920372447426</v>
+      </c>
+      <c r="T100">
+        <v>38.97239458046422</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.01528567792742985</v>
+      </c>
+      <c r="W100">
+        <v>0.2424502198890702</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.09264047228745365</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2945396229402374</v>
+      </c>
+      <c r="C101">
+        <v>-12919.64443538359</v>
+      </c>
+      <c r="D101">
+        <v>3739.472564616412</v>
+      </c>
+      <c r="E101">
+        <v>6857.516999999998</v>
+      </c>
+      <c r="F101">
+        <v>17461.917</v>
+      </c>
+      <c r="G101">
+        <v>802.8</v>
+      </c>
+      <c r="H101">
+        <v>7033.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1220.7</v>
+      </c>
+      <c r="K101">
+        <v>1603.1</v>
+      </c>
+      <c r="L101">
+        <v>-382.3999999999999</v>
+      </c>
+      <c r="M101">
+        <v>4169.9057796</v>
+      </c>
+      <c r="N101">
+        <v>-4552.305779599999</v>
+      </c>
+      <c r="O101">
+        <v>-751.1304536340001</v>
+      </c>
+      <c r="P101">
+        <v>-3801.175325965999</v>
+      </c>
+      <c r="Q101">
+        <v>-2198.075325965999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.455040744894852</v>
+      </c>
+      <c r="T101">
+        <v>77.94478916092844</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.01513127714028409</v>
+      </c>
+      <c r="W101">
+        <v>0.2424133489810998</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.09170470994111568</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_air_transport.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_air_transport.xlsx
@@ -1133,7 +1133,7 @@
         <v>1.94155175962132</v>
       </c>
       <c r="F2">
-        <v>3.03497919523652</v>
+        <v>3.03497919523651</v>
       </c>
       <c r="G2">
         <v>3.40143112701252</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08705920913303966</v>
+        <v>0.08695313643797013</v>
       </c>
       <c r="C2">
-        <v>16084.88481316459</v>
+        <v>15937.40799791325</v>
       </c>
       <c r="D2">
-        <v>14852.68481316459</v>
+        <v>14869.84399791325</v>
       </c>
       <c r="E2">
-        <v>-8556.299999999997</v>
+        <v>-8391.663999999997</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>164.636</v>
       </c>
       <c r="G2">
         <v>1232.2</v>
@@ -1451,28 +1451,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.281190799999999</v>
       </c>
       <c r="N2">
-        <v>994.7367346938777</v>
+        <v>986.4555438938777</v>
       </c>
       <c r="O2">
-        <v>164.1315612244898</v>
+        <v>162.7651647424898</v>
       </c>
       <c r="P2">
-        <v>830.6051734693879</v>
+        <v>823.6903791513879</v>
       </c>
       <c r="Q2">
-        <v>2402.705173469388</v>
+        <v>2395.790379151388</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08705920913303966</v>
+        <v>0.08740720347269711</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285176</v>
+        <v>0.8110018391299652</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>120.1200115681283</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08695313643797013</v>
+        <v>0.08684706374290063</v>
       </c>
       <c r="C3">
-        <v>15937.40799791325</v>
+        <v>15789.97087624993</v>
       </c>
       <c r="D3">
-        <v>14869.84399791325</v>
+        <v>14887.04287624993</v>
       </c>
       <c r="E3">
-        <v>-8391.663999999997</v>
+        <v>-8227.027999999997</v>
       </c>
       <c r="F3">
-        <v>164.636</v>
+        <v>329.272</v>
       </c>
       <c r="G3">
         <v>1232.2</v>
@@ -1533,28 +1533,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M3">
-        <v>8.281190799999999</v>
+        <v>16.5623816</v>
       </c>
       <c r="N3">
-        <v>986.4555438938777</v>
+        <v>978.1743530938777</v>
       </c>
       <c r="O3">
-        <v>162.7651647424898</v>
+        <v>161.3987682604898</v>
       </c>
       <c r="P3">
-        <v>823.6903791513879</v>
+        <v>816.7755848333879</v>
       </c>
       <c r="Q3">
-        <v>2395.790379151388</v>
+        <v>2388.875584833388</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08740720347269711</v>
+        <v>0.0877622997376537</v>
       </c>
       <c r="T3">
-        <v>0.8110018391299652</v>
+        <v>0.8179233262742994</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>120.1200115681283</v>
+        <v>60.06000578406416</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08684706374290063</v>
+        <v>0.08674099104783112</v>
       </c>
       <c r="C4">
-        <v>15789.97087624993</v>
+        <v>15642.57358606628</v>
       </c>
       <c r="D4">
-        <v>14887.04287624993</v>
+        <v>14904.28158606628</v>
       </c>
       <c r="E4">
-        <v>-8227.027999999997</v>
+        <v>-8062.391999999997</v>
       </c>
       <c r="F4">
-        <v>329.272</v>
+        <v>493.908</v>
       </c>
       <c r="G4">
         <v>1232.2</v>
@@ -1615,28 +1615,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M4">
-        <v>16.5623816</v>
+        <v>24.8435724</v>
       </c>
       <c r="N4">
-        <v>978.1743530938777</v>
+        <v>969.8931622938777</v>
       </c>
       <c r="O4">
-        <v>161.3987682604898</v>
+        <v>160.0323717784898</v>
       </c>
       <c r="P4">
-        <v>816.7755848333879</v>
+        <v>809.8607905153879</v>
       </c>
       <c r="Q4">
-        <v>2388.875584833388</v>
+        <v>2381.960790515388</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0877622997376537</v>
+        <v>0.08812471757508362</v>
       </c>
       <c r="T4">
-        <v>0.8179233262742994</v>
+        <v>0.8249875244937748</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.06000578406416</v>
+        <v>40.04000385604277</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08674099104783112</v>
+        <v>0.0866349183527616</v>
       </c>
       <c r="C5">
-        <v>15642.57358606628</v>
+        <v>15495.21626589338</v>
       </c>
       <c r="D5">
-        <v>14904.28158606628</v>
+        <v>14921.56026589338</v>
       </c>
       <c r="E5">
-        <v>-8062.391999999997</v>
+        <v>-7897.755999999998</v>
       </c>
       <c r="F5">
-        <v>493.908</v>
+        <v>658.544</v>
       </c>
       <c r="G5">
         <v>1232.2</v>
@@ -1697,28 +1697,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M5">
-        <v>24.8435724</v>
+        <v>33.1247632</v>
       </c>
       <c r="N5">
-        <v>969.8931622938777</v>
+        <v>961.6119714938777</v>
       </c>
       <c r="O5">
-        <v>160.0323717784898</v>
+        <v>158.6659752964898</v>
       </c>
       <c r="P5">
-        <v>809.8607905153879</v>
+        <v>802.9459961973879</v>
       </c>
       <c r="Q5">
-        <v>2381.960790515388</v>
+        <v>2375.045996197388</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08812471757508362</v>
+        <v>0.08849468578412667</v>
       </c>
       <c r="T5">
-        <v>0.8249875244937748</v>
+        <v>0.8321988935094891</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.04000385604277</v>
+        <v>30.03000289203208</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0866349183527616</v>
+        <v>0.08652884565769209</v>
       </c>
       <c r="C6">
-        <v>15495.21626589338</v>
+        <v>15347.89905490544</v>
       </c>
       <c r="D6">
-        <v>14921.56026589338</v>
+        <v>14938.87905490544</v>
       </c>
       <c r="E6">
-        <v>-7897.755999999998</v>
+        <v>-7733.119999999997</v>
       </c>
       <c r="F6">
-        <v>658.544</v>
+        <v>823.1799999999999</v>
       </c>
       <c r="G6">
         <v>1232.2</v>
@@ -1779,28 +1779,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M6">
-        <v>33.1247632</v>
+        <v>41.40595399999999</v>
       </c>
       <c r="N6">
-        <v>961.6119714938777</v>
+        <v>953.3307806938777</v>
       </c>
       <c r="O6">
-        <v>158.6659752964898</v>
+        <v>157.2995788144898</v>
       </c>
       <c r="P6">
-        <v>802.9459961973879</v>
+        <v>796.0312018793879</v>
       </c>
       <c r="Q6">
-        <v>2375.045996197388</v>
+        <v>2368.131201879388</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08849468578412667</v>
+        <v>0.08887244279757062</v>
       </c>
       <c r="T6">
-        <v>0.8321988935094891</v>
+        <v>0.839562080820271</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.03000289203208</v>
+        <v>24.02400231362567</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08652884565769209</v>
+        <v>0.08642277296262256</v>
       </c>
       <c r="C7">
-        <v>15347.89905490544</v>
+        <v>15200.62209292357</v>
       </c>
       <c r="D7">
-        <v>14938.87905490544</v>
+        <v>14956.23809292357</v>
       </c>
       <c r="E7">
-        <v>-7733.119999999997</v>
+        <v>-7568.483999999998</v>
       </c>
       <c r="F7">
-        <v>823.1799999999999</v>
+        <v>987.816</v>
       </c>
       <c r="G7">
         <v>1232.2</v>
@@ -1861,28 +1861,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M7">
-        <v>41.40595399999999</v>
+        <v>49.6871448</v>
       </c>
       <c r="N7">
-        <v>953.3307806938777</v>
+        <v>945.0495898938777</v>
       </c>
       <c r="O7">
-        <v>157.2995788144898</v>
+        <v>155.9331823324898</v>
       </c>
       <c r="P7">
-        <v>796.0312018793879</v>
+        <v>789.1164075613879</v>
       </c>
       <c r="Q7">
-        <v>2368.131201879388</v>
+        <v>2361.216407561388</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08887244279757062</v>
+        <v>0.08925823719427932</v>
       </c>
       <c r="T7">
-        <v>0.839562080820271</v>
+        <v>0.8470819316908567</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.02400231362567</v>
+        <v>20.02000192802139</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08642277296262255</v>
+        <v>0.08631670026755305</v>
       </c>
       <c r="C8">
-        <v>15200.62209292357</v>
+        <v>15053.38552041953</v>
       </c>
       <c r="D8">
-        <v>14956.23809292357</v>
+        <v>14973.63752041953</v>
       </c>
       <c r="E8">
-        <v>-7568.483999999998</v>
+        <v>-7403.847999999998</v>
       </c>
       <c r="F8">
-        <v>987.8159999999999</v>
+        <v>1152.452</v>
       </c>
       <c r="G8">
         <v>1232.2</v>
@@ -1943,28 +1943,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M8">
-        <v>49.68714479999999</v>
+        <v>57.96833559999999</v>
       </c>
       <c r="N8">
-        <v>945.0495898938777</v>
+        <v>936.7683990938776</v>
       </c>
       <c r="O8">
-        <v>155.9331823324898</v>
+        <v>154.5667858504898</v>
       </c>
       <c r="P8">
-        <v>789.1164075613879</v>
+        <v>782.2016132433878</v>
       </c>
       <c r="Q8">
-        <v>2361.216407561388</v>
+        <v>2354.301613243388</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08925823719427932</v>
+        <v>0.0896523282446807</v>
       </c>
       <c r="T8">
-        <v>0.8470819316908567</v>
+        <v>0.8547634997844658</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.02000192802139</v>
+        <v>17.16000165258976</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08631670026755303</v>
+        <v>0.08621062757248352</v>
       </c>
       <c r="C9">
-        <v>15053.38552041953</v>
+        <v>14906.1894785195</v>
       </c>
       <c r="D9">
-        <v>14973.63752041953</v>
+        <v>14991.0774785195</v>
       </c>
       <c r="E9">
-        <v>-7403.847999999997</v>
+        <v>-7239.211999999998</v>
       </c>
       <c r="F9">
-        <v>1152.452</v>
+        <v>1317.088</v>
       </c>
       <c r="G9">
         <v>1232.2</v>
@@ -2025,28 +2025,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M9">
-        <v>57.9683356</v>
+        <v>66.24952639999999</v>
       </c>
       <c r="N9">
-        <v>936.7683990938776</v>
+        <v>928.4872082938776</v>
       </c>
       <c r="O9">
-        <v>154.5667858504898</v>
+        <v>153.2003893684898</v>
       </c>
       <c r="P9">
-        <v>782.2016132433878</v>
+        <v>775.2868189253878</v>
       </c>
       <c r="Q9">
-        <v>2354.301613243388</v>
+        <v>2347.386818925388</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0896523282446807</v>
+        <v>0.09005498649182991</v>
       </c>
       <c r="T9">
-        <v>0.8547634997844659</v>
+        <v>0.8626120584888055</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.16000165258976</v>
+        <v>15.01500144601604</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08621062757248352</v>
+        <v>0.08610455487741402</v>
       </c>
       <c r="C10">
-        <v>14906.1894785195</v>
+        <v>14759.03410900792</v>
       </c>
       <c r="D10">
-        <v>14991.0774785195</v>
+        <v>15008.55810900792</v>
       </c>
       <c r="E10">
-        <v>-7239.211999999998</v>
+        <v>-7074.575999999997</v>
       </c>
       <c r="F10">
-        <v>1317.088</v>
+        <v>1481.724</v>
       </c>
       <c r="G10">
         <v>1232.2</v>
@@ -2107,28 +2107,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M10">
-        <v>66.24952639999999</v>
+        <v>74.53071719999998</v>
       </c>
       <c r="N10">
-        <v>928.4872082938776</v>
+        <v>920.2060174938777</v>
       </c>
       <c r="O10">
-        <v>153.2003893684898</v>
+        <v>151.8339928864898</v>
       </c>
       <c r="P10">
-        <v>775.2868189253878</v>
+        <v>768.3720246073879</v>
       </c>
       <c r="Q10">
-        <v>2347.386818925388</v>
+        <v>2340.472024607388</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09005498649182991</v>
+        <v>0.09046649437078463</v>
       </c>
       <c r="T10">
-        <v>0.8626120584888055</v>
+        <v>0.870633112988845</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.01500144601604</v>
+        <v>13.34666795201426</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08610455487741402</v>
+        <v>0.08599848218234449</v>
       </c>
       <c r="C11">
-        <v>14759.03410900792</v>
+        <v>14611.91955433134</v>
       </c>
       <c r="D11">
-        <v>15008.55810900792</v>
+        <v>15026.07955433133</v>
       </c>
       <c r="E11">
-        <v>-7074.575999999997</v>
+        <v>-6909.939999999998</v>
       </c>
       <c r="F11">
-        <v>1481.724</v>
+        <v>1646.36</v>
       </c>
       <c r="G11">
         <v>1232.2</v>
@@ -2189,28 +2189,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M11">
-        <v>74.53071719999998</v>
+        <v>82.81190799999997</v>
       </c>
       <c r="N11">
-        <v>920.2060174938777</v>
+        <v>911.9248266938777</v>
       </c>
       <c r="O11">
-        <v>151.8339928864898</v>
+        <v>150.4675964044898</v>
       </c>
       <c r="P11">
-        <v>768.3720246073879</v>
+        <v>761.4572302893878</v>
       </c>
       <c r="Q11">
-        <v>2340.472024607388</v>
+        <v>2333.557230289388</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09046649437078463</v>
+        <v>0.09088714686927166</v>
       </c>
       <c r="T11">
-        <v>0.870633112988845</v>
+        <v>0.8788324131444412</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.34666795201426</v>
+        <v>12.01200115681283</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08599848218234449</v>
+        <v>0.08589240948727499</v>
       </c>
       <c r="C12">
-        <v>14611.91955433133</v>
+        <v>14464.84595760223</v>
       </c>
       <c r="D12">
-        <v>15026.07955433133</v>
+        <v>15043.64195760223</v>
       </c>
       <c r="E12">
-        <v>-6909.939999999998</v>
+        <v>-6745.303999999997</v>
       </c>
       <c r="F12">
-        <v>1646.36</v>
+        <v>1810.996</v>
       </c>
       <c r="G12">
         <v>1232.2</v>
@@ -2271,28 +2271,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M12">
-        <v>82.81190799999999</v>
+        <v>91.09309879999999</v>
       </c>
       <c r="N12">
-        <v>911.9248266938777</v>
+        <v>903.6436358938777</v>
       </c>
       <c r="O12">
-        <v>150.4675964044898</v>
+        <v>149.1011999224898</v>
       </c>
       <c r="P12">
-        <v>761.4572302893878</v>
+        <v>754.5424359713878</v>
       </c>
       <c r="Q12">
-        <v>2333.557230289388</v>
+        <v>2326.642435971388</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09088714686927166</v>
+        <v>0.09131725223289325</v>
       </c>
       <c r="T12">
-        <v>0.8788324131444412</v>
+        <v>0.887215967236118</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.01200115681283</v>
+        <v>10.92000105164803</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08589240948727499</v>
+        <v>0.08578633679220547</v>
       </c>
       <c r="C13">
-        <v>14464.84595760223</v>
+        <v>14317.81346260298</v>
       </c>
       <c r="D13">
-        <v>15043.64195760223</v>
+        <v>15061.24546260297</v>
       </c>
       <c r="E13">
-        <v>-6745.303999999997</v>
+        <v>-6580.667999999998</v>
       </c>
       <c r="F13">
-        <v>1810.996</v>
+        <v>1975.632</v>
       </c>
       <c r="G13">
         <v>1232.2</v>
@@ -2353,28 +2353,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M13">
-        <v>91.09309879999999</v>
+        <v>99.37428959999998</v>
       </c>
       <c r="N13">
-        <v>903.6436358938777</v>
+        <v>895.3624450938777</v>
       </c>
       <c r="O13">
-        <v>149.1011999224898</v>
+        <v>147.7348034404898</v>
       </c>
       <c r="P13">
-        <v>754.5424359713878</v>
+        <v>747.6276416533879</v>
       </c>
       <c r="Q13">
-        <v>2326.642435971388</v>
+        <v>2319.727641653388</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09131725223289325</v>
+        <v>0.0917571327184153</v>
       </c>
       <c r="T13">
-        <v>0.887215967236118</v>
+        <v>0.8957900566480601</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.92000105164803</v>
+        <v>10.01000096401069</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08578633679220547</v>
+        <v>0.08568026409713594</v>
       </c>
       <c r="C14">
-        <v>14317.81346260298</v>
+        <v>14170.8222137897</v>
       </c>
       <c r="D14">
-        <v>15061.24546260297</v>
+        <v>15078.8902137897</v>
       </c>
       <c r="E14">
-        <v>-6580.667999999998</v>
+        <v>-6416.031999999997</v>
       </c>
       <c r="F14">
-        <v>1975.632</v>
+        <v>2140.268</v>
       </c>
       <c r="G14">
         <v>1232.2</v>
@@ -2435,28 +2435,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M14">
-        <v>99.37428959999998</v>
+        <v>107.6554804</v>
       </c>
       <c r="N14">
-        <v>895.3624450938777</v>
+        <v>887.0812542938777</v>
       </c>
       <c r="O14">
-        <v>147.7348034404898</v>
+        <v>146.3684069584898</v>
       </c>
       <c r="P14">
-        <v>747.6276416533879</v>
+        <v>740.7128473353879</v>
       </c>
       <c r="Q14">
-        <v>2319.727641653388</v>
+        <v>2312.812847335388</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0917571327184153</v>
+        <v>0.09220712539900683</v>
       </c>
       <c r="T14">
-        <v>0.8957900566480601</v>
+        <v>0.904561251563725</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.01000096401069</v>
+        <v>9.240000889856024</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08568026409713594</v>
+        <v>0.08574954140206643</v>
       </c>
       <c r="C15">
-        <v>14170.8222137897</v>
+        <v>13994.65754288366</v>
       </c>
       <c r="D15">
-        <v>15078.8902137897</v>
+        <v>15067.36154288366</v>
       </c>
       <c r="E15">
-        <v>-6416.031999999997</v>
+        <v>-6251.395999999997</v>
       </c>
       <c r="F15">
-        <v>2140.268</v>
+        <v>2304.904</v>
       </c>
       <c r="G15">
         <v>1232.2</v>
@@ -2517,45 +2517,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M15">
-        <v>107.6554804</v>
+        <v>119.3940272</v>
       </c>
       <c r="N15">
-        <v>887.0812542938777</v>
+        <v>875.3427074938777</v>
       </c>
       <c r="O15">
-        <v>146.3684069584898</v>
+        <v>144.4315467364898</v>
       </c>
       <c r="P15">
-        <v>740.7128473353879</v>
+        <v>730.9111607573878</v>
       </c>
       <c r="Q15">
-        <v>2312.812847335388</v>
+        <v>2303.011160757388</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09220712539900683</v>
+        <v>0.09266758302565864</v>
       </c>
       <c r="T15">
-        <v>0.904561251563725</v>
+        <v>0.9135364277564986</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.165</v>
       </c>
       <c r="W15">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.240000889856024</v>
+        <v>8.331545203911823</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08574954140206643</v>
+        <v>0.08565599370699693</v>
       </c>
       <c r="C16">
-        <v>13994.65754288366</v>
+        <v>13845.59330572546</v>
       </c>
       <c r="D16">
-        <v>15067.36154288366</v>
+        <v>15082.93330572546</v>
       </c>
       <c r="E16">
-        <v>-6251.395999999997</v>
+        <v>-6086.759999999997</v>
       </c>
       <c r="F16">
-        <v>2304.904</v>
+        <v>2469.54</v>
       </c>
       <c r="G16">
         <v>1232.2</v>
@@ -2599,28 +2599,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M16">
-        <v>119.3940272</v>
+        <v>127.922172</v>
       </c>
       <c r="N16">
-        <v>875.3427074938777</v>
+        <v>866.8145626938776</v>
       </c>
       <c r="O16">
-        <v>144.4315467364898</v>
+        <v>143.0244028444898</v>
       </c>
       <c r="P16">
-        <v>730.9111607573878</v>
+        <v>723.7901598493878</v>
       </c>
       <c r="Q16">
-        <v>2303.011160757388</v>
+        <v>2295.890159849388</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09266758302565864</v>
+        <v>0.09313887494940815</v>
       </c>
       <c r="T16">
-        <v>0.9135364277564986</v>
+        <v>0.9227227845655728</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.331545203911823</v>
+        <v>7.776108856984368</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08565599370699693</v>
+        <v>0.08556244601192742</v>
       </c>
       <c r="C17">
-        <v>13845.59330572546</v>
+        <v>13696.56128796462</v>
       </c>
       <c r="D17">
-        <v>15082.93330572546</v>
+        <v>15098.53728796462</v>
       </c>
       <c r="E17">
-        <v>-6086.759999999998</v>
+        <v>-5922.123999999998</v>
       </c>
       <c r="F17">
-        <v>2469.54</v>
+        <v>2634.176</v>
       </c>
       <c r="G17">
         <v>1232.2</v>
@@ -2681,28 +2681,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M17">
-        <v>127.922172</v>
+        <v>136.4503168</v>
       </c>
       <c r="N17">
-        <v>866.8145626938777</v>
+        <v>858.2864178938777</v>
       </c>
       <c r="O17">
-        <v>143.0244028444898</v>
+        <v>141.6172589524898</v>
       </c>
       <c r="P17">
-        <v>723.7901598493879</v>
+        <v>716.6691589413879</v>
       </c>
       <c r="Q17">
-        <v>2295.890159849388</v>
+        <v>2288.769158941388</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09313887494940815</v>
+        <v>0.09362138810943739</v>
       </c>
       <c r="T17">
-        <v>0.9227227845655728</v>
+        <v>0.9321278641558152</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.776108856984369</v>
+        <v>7.290102053422845</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08556244601192742</v>
+        <v>0.08546889831685789</v>
       </c>
       <c r="C18">
-        <v>13696.56128796462</v>
+        <v>13547.56158970202</v>
       </c>
       <c r="D18">
-        <v>15098.53728796462</v>
+        <v>15114.17358970202</v>
       </c>
       <c r="E18">
-        <v>-5922.123999999998</v>
+        <v>-5757.487999999998</v>
       </c>
       <c r="F18">
-        <v>2634.176</v>
+        <v>2798.812</v>
       </c>
       <c r="G18">
         <v>1232.2</v>
@@ -2763,28 +2763,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M18">
-        <v>136.4503168</v>
+        <v>144.9784616</v>
       </c>
       <c r="N18">
-        <v>858.2864178938777</v>
+        <v>849.7582730938777</v>
       </c>
       <c r="O18">
-        <v>141.6172589524898</v>
+        <v>140.2101150604898</v>
       </c>
       <c r="P18">
-        <v>716.6691589413879</v>
+        <v>709.5481580333878</v>
       </c>
       <c r="Q18">
-        <v>2288.769158941388</v>
+        <v>2281.648158033388</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09362138810943739</v>
+        <v>0.09411552809259988</v>
       </c>
       <c r="T18">
-        <v>0.9321278641558152</v>
+        <v>0.9417595721699189</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.290102053422845</v>
+        <v>6.86127252086856</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08546889831685789</v>
+        <v>0.08563086062178837</v>
       </c>
       <c r="C19">
-        <v>13547.56158970202</v>
+        <v>13355.87439578655</v>
       </c>
       <c r="D19">
-        <v>15114.17358970202</v>
+        <v>15087.12239578655</v>
       </c>
       <c r="E19">
-        <v>-5757.487999999998</v>
+        <v>-5592.851999999997</v>
       </c>
       <c r="F19">
-        <v>2798.812</v>
+        <v>2963.448</v>
       </c>
       <c r="G19">
         <v>1232.2</v>
@@ -2845,45 +2845,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M19">
-        <v>144.9784616</v>
+        <v>158.544468</v>
       </c>
       <c r="N19">
-        <v>849.7582730938777</v>
+        <v>836.1922666938776</v>
       </c>
       <c r="O19">
-        <v>140.2101150604898</v>
+        <v>137.9717240044898</v>
       </c>
       <c r="P19">
-        <v>709.5481580333878</v>
+        <v>698.2205426893878</v>
       </c>
       <c r="Q19">
-        <v>2281.648158033388</v>
+        <v>2270.320542689388</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09411552809259988</v>
+        <v>0.09462172027047364</v>
       </c>
       <c r="T19">
-        <v>0.9417595721699189</v>
+        <v>0.9516261998916837</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.165</v>
       </c>
       <c r="W19">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.86127252086856</v>
+        <v>6.274181289591748</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08563086062178839</v>
+        <v>0.08555150792671887</v>
       </c>
       <c r="C20">
-        <v>13355.87439578654</v>
+        <v>13204.4798955667</v>
       </c>
       <c r="D20">
-        <v>15087.12239578654</v>
+        <v>15100.3638955667</v>
       </c>
       <c r="E20">
-        <v>-5592.851999999998</v>
+        <v>-5428.215999999998</v>
       </c>
       <c r="F20">
-        <v>2963.447999999999</v>
+        <v>3128.084</v>
       </c>
       <c r="G20">
         <v>1232.2</v>
@@ -2927,28 +2927,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M20">
-        <v>158.544468</v>
+        <v>167.352494</v>
       </c>
       <c r="N20">
-        <v>836.1922666938777</v>
+        <v>827.3842406938777</v>
       </c>
       <c r="O20">
-        <v>137.9717240044898</v>
+        <v>136.5183997144898</v>
       </c>
       <c r="P20">
-        <v>698.2205426893879</v>
+        <v>690.8658409793879</v>
       </c>
       <c r="Q20">
-        <v>2270.320542689388</v>
+        <v>2262.965840979388</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09462172027047364</v>
+        <v>0.09514041102064057</v>
       </c>
       <c r="T20">
-        <v>0.9516261998916837</v>
+        <v>0.9617364480510229</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.27418128959175</v>
+        <v>5.943961221718499</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08555150792671887</v>
+        <v>0.08547215523164935</v>
       </c>
       <c r="C21">
-        <v>13204.4798955667</v>
+        <v>13053.10865907272</v>
       </c>
       <c r="D21">
-        <v>15100.3638955667</v>
+        <v>15113.62865907272</v>
       </c>
       <c r="E21">
-        <v>-5428.215999999998</v>
+        <v>-5263.579999999998</v>
       </c>
       <c r="F21">
-        <v>3128.084</v>
+        <v>3292.72</v>
       </c>
       <c r="G21">
         <v>1232.2</v>
@@ -3009,28 +3009,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M21">
-        <v>167.352494</v>
+        <v>176.16052</v>
       </c>
       <c r="N21">
-        <v>827.3842406938777</v>
+        <v>818.5762146938777</v>
       </c>
       <c r="O21">
-        <v>136.5183997144898</v>
+        <v>135.0650754244898</v>
       </c>
       <c r="P21">
-        <v>690.8658409793879</v>
+        <v>683.5111392693879</v>
       </c>
       <c r="Q21">
-        <v>2262.965840979388</v>
+        <v>2255.611139269388</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09514041102064057</v>
+        <v>0.09567206903956169</v>
       </c>
       <c r="T21">
-        <v>0.9617364480510229</v>
+        <v>0.9720994524143456</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.943961221718499</v>
+        <v>5.646763160632574</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08547215523164935</v>
+        <v>0.08553308253657982</v>
       </c>
       <c r="C22">
-        <v>13053.10865907272</v>
+        <v>12878.28584657428</v>
       </c>
       <c r="D22">
-        <v>15113.62865907272</v>
+        <v>15103.44184657427</v>
       </c>
       <c r="E22">
-        <v>-5263.579999999998</v>
+        <v>-5098.943999999998</v>
       </c>
       <c r="F22">
-        <v>3292.72</v>
+        <v>3457.356</v>
       </c>
       <c r="G22">
         <v>1232.2</v>
@@ -3091,45 +3091,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M22">
-        <v>176.16052</v>
+        <v>187.7344308</v>
       </c>
       <c r="N22">
-        <v>818.5762146938777</v>
+        <v>807.0023038938776</v>
       </c>
       <c r="O22">
-        <v>135.0650754244898</v>
+        <v>133.1553801424898</v>
       </c>
       <c r="P22">
-        <v>683.5111392693879</v>
+        <v>673.8469237513879</v>
       </c>
       <c r="Q22">
-        <v>2255.611139269388</v>
+        <v>2245.946923751388</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09567206903956169</v>
+        <v>0.09621718675516433</v>
       </c>
       <c r="T22">
-        <v>0.9720994524143456</v>
+        <v>0.9827248113185119</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.165</v>
       </c>
       <c r="W22">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.646763160632574</v>
+        <v>5.298637711020655</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08553308253657982</v>
+        <v>0.08546040984151032</v>
       </c>
       <c r="C23">
-        <v>12878.28584657428</v>
+        <v>12725.80202346295</v>
       </c>
       <c r="D23">
-        <v>15103.44184657427</v>
+        <v>15115.59402346295</v>
       </c>
       <c r="E23">
-        <v>-5098.943999999998</v>
+        <v>-4934.307999999997</v>
       </c>
       <c r="F23">
-        <v>3457.356</v>
+        <v>3621.992</v>
       </c>
       <c r="G23">
         <v>1232.2</v>
@@ -3173,28 +3173,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M23">
-        <v>187.7344308</v>
+        <v>196.6741656</v>
       </c>
       <c r="N23">
-        <v>807.0023038938778</v>
+        <v>798.0625690938778</v>
       </c>
       <c r="O23">
-        <v>133.1553801424898</v>
+        <v>131.6803239004898</v>
       </c>
       <c r="P23">
-        <v>673.846923751388</v>
+        <v>666.3822451933879</v>
       </c>
       <c r="Q23">
-        <v>2245.946923751388</v>
+        <v>2238.482245193388</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09621718675516433</v>
+        <v>0.09677628184809015</v>
       </c>
       <c r="T23">
-        <v>0.9827248113185119</v>
+        <v>0.9936226153227851</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.298637711020657</v>
+        <v>5.0577905423379</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08546040984151032</v>
+        <v>0.0853877371464408</v>
       </c>
       <c r="C24">
-        <v>12725.80202346295</v>
+        <v>12573.33777129704</v>
       </c>
       <c r="D24">
-        <v>15115.59402346295</v>
+        <v>15127.76577129704</v>
       </c>
       <c r="E24">
-        <v>-4934.307999999997</v>
+        <v>-4769.671999999998</v>
       </c>
       <c r="F24">
-        <v>3621.992</v>
+        <v>3786.628</v>
       </c>
       <c r="G24">
         <v>1232.2</v>
@@ -3255,28 +3255,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M24">
-        <v>196.6741656</v>
+        <v>205.6139004</v>
       </c>
       <c r="N24">
-        <v>798.0625690938778</v>
+        <v>789.1228342938778</v>
       </c>
       <c r="O24">
-        <v>131.6803239004898</v>
+        <v>130.2052676584898</v>
       </c>
       <c r="P24">
-        <v>666.3822451933879</v>
+        <v>658.9175666353879</v>
       </c>
       <c r="Q24">
-        <v>2238.482245193388</v>
+        <v>2231.017566635388</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09677628184809015</v>
+        <v>0.09734989889148155</v>
       </c>
       <c r="T24">
-        <v>0.9936226153227851</v>
+        <v>1.004803479171325</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.0577905423379</v>
+        <v>4.837886605714512</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0853877371464408</v>
+        <v>0.08531506445137128</v>
       </c>
       <c r="C25">
-        <v>12573.33777129704</v>
+        <v>12420.89313739282</v>
       </c>
       <c r="D25">
-        <v>15127.76577129704</v>
+        <v>15139.95713739282</v>
       </c>
       <c r="E25">
-        <v>-4769.671999999998</v>
+        <v>-4605.035999999997</v>
       </c>
       <c r="F25">
-        <v>3786.628</v>
+        <v>3951.264</v>
       </c>
       <c r="G25">
         <v>1232.2</v>
@@ -3337,28 +3337,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M25">
-        <v>205.6139004</v>
+        <v>214.5536352</v>
       </c>
       <c r="N25">
-        <v>789.1228342938778</v>
+        <v>780.1830994938776</v>
       </c>
       <c r="O25">
-        <v>130.2052676584898</v>
+        <v>128.7302114164898</v>
       </c>
       <c r="P25">
-        <v>658.9175666353879</v>
+        <v>651.4528880773878</v>
       </c>
       <c r="Q25">
-        <v>2231.017566635388</v>
+        <v>2223.552888077388</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09734989889148155</v>
+        <v>0.09793861112022537</v>
       </c>
       <c r="T25">
-        <v>1.004803479171325</v>
+        <v>1.016278576279037</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.837886605714512</v>
+        <v>4.636307997143073</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08531506445137128</v>
+        <v>0.08524239175630177</v>
       </c>
       <c r="C26">
-        <v>12420.89313739282</v>
+        <v>12268.46816921923</v>
       </c>
       <c r="D26">
-        <v>15139.95713739282</v>
+        <v>15152.16816921923</v>
       </c>
       <c r="E26">
-        <v>-4605.035999999998</v>
+        <v>-4440.399999999998</v>
       </c>
       <c r="F26">
-        <v>3951.264</v>
+        <v>4115.9</v>
       </c>
       <c r="G26">
         <v>1232.2</v>
@@ -3419,28 +3419,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M26">
-        <v>214.5536352</v>
+        <v>223.49337</v>
       </c>
       <c r="N26">
-        <v>780.1830994938778</v>
+        <v>771.2433646938778</v>
       </c>
       <c r="O26">
-        <v>128.7302114164898</v>
+        <v>127.2551551744898</v>
       </c>
       <c r="P26">
-        <v>651.4528880773879</v>
+        <v>643.988209519388</v>
       </c>
       <c r="Q26">
-        <v>2223.552888077388</v>
+        <v>2216.088209519388</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09793861112022537</v>
+        <v>0.09854302234173569</v>
       </c>
       <c r="T26">
-        <v>1.016278576279037</v>
+        <v>1.028059675976288</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.636307997143074</v>
+        <v>4.450855677257351</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08524239175630177</v>
+        <v>0.08516971906123225</v>
       </c>
       <c r="C27">
-        <v>12268.46816921923</v>
+        <v>12116.06291439847</v>
       </c>
       <c r="D27">
-        <v>15152.16816921923</v>
+        <v>15164.39891439847</v>
       </c>
       <c r="E27">
-        <v>-4440.399999999998</v>
+        <v>-4275.763999999997</v>
       </c>
       <c r="F27">
-        <v>4115.9</v>
+        <v>4280.536</v>
       </c>
       <c r="G27">
         <v>1232.2</v>
@@ -3501,28 +3501,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M27">
-        <v>223.49337</v>
+        <v>232.4331048</v>
       </c>
       <c r="N27">
-        <v>771.2433646938778</v>
+        <v>762.3036298938777</v>
       </c>
       <c r="O27">
-        <v>127.2551551744898</v>
+        <v>125.7800989324898</v>
       </c>
       <c r="P27">
-        <v>643.988209519388</v>
+        <v>636.5235309613878</v>
       </c>
       <c r="Q27">
-        <v>2216.088209519388</v>
+        <v>2208.623530961388</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09854302234173569</v>
+        <v>0.09916376900166519</v>
       </c>
       <c r="T27">
-        <v>1.028059675976288</v>
+        <v>1.040159183773465</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.450855677257351</v>
+        <v>4.279668920439761</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08516971906123225</v>
+        <v>0.08532249636616274</v>
       </c>
       <c r="C28">
-        <v>12116.06291439847</v>
+        <v>11925.73747842805</v>
       </c>
       <c r="D28">
-        <v>15164.39891439847</v>
+        <v>15138.70947842805</v>
       </c>
       <c r="E28">
-        <v>-4275.763999999997</v>
+        <v>-4111.127999999998</v>
       </c>
       <c r="F28">
-        <v>4280.536</v>
+        <v>4445.172</v>
       </c>
       <c r="G28">
         <v>1232.2</v>
@@ -3583,45 +3583,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M28">
-        <v>232.4331048</v>
+        <v>245.8180116</v>
       </c>
       <c r="N28">
-        <v>762.3036298938777</v>
+        <v>748.9187230938777</v>
       </c>
       <c r="O28">
-        <v>125.7800989324898</v>
+        <v>123.5715893104898</v>
       </c>
       <c r="P28">
-        <v>636.5235309613878</v>
+        <v>625.3471337833879</v>
       </c>
       <c r="Q28">
-        <v>2208.623530961388</v>
+        <v>2197.447133783388</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09916376900166519</v>
+        <v>0.09980152241940102</v>
       </c>
       <c r="T28">
-        <v>1.040159183773465</v>
+        <v>1.052590184934948</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.165</v>
       </c>
       <c r="W28">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.279668920439761</v>
+        <v>4.04663892698202</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08532249636616274</v>
+        <v>0.08525817367109323</v>
       </c>
       <c r="C29">
-        <v>11925.73747842805</v>
+        <v>11771.9066950383</v>
       </c>
       <c r="D29">
-        <v>15138.70947842805</v>
+        <v>15149.5146950383</v>
       </c>
       <c r="E29">
-        <v>-4111.127999999998</v>
+        <v>-3946.491999999997</v>
       </c>
       <c r="F29">
-        <v>4445.172</v>
+        <v>4609.808</v>
       </c>
       <c r="G29">
         <v>1232.2</v>
@@ -3665,28 +3665,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M29">
-        <v>245.8180116</v>
+        <v>254.9223824</v>
       </c>
       <c r="N29">
-        <v>748.9187230938777</v>
+        <v>739.8143522938776</v>
       </c>
       <c r="O29">
-        <v>123.5715893104898</v>
+        <v>122.0693681284898</v>
       </c>
       <c r="P29">
-        <v>625.3471337833879</v>
+        <v>617.7449841653878</v>
       </c>
       <c r="Q29">
-        <v>2197.447133783388</v>
+        <v>2189.844984165388</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09980152241940102</v>
+        <v>0.1004569912098517</v>
       </c>
       <c r="T29">
-        <v>1.052590184934948</v>
+        <v>1.06536649168425</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.04663892698202</v>
+        <v>3.902116108161233</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08525817367109323</v>
+        <v>0.08519385097602369</v>
       </c>
       <c r="C30">
-        <v>11771.9066950383</v>
+        <v>11618.09134705903</v>
       </c>
       <c r="D30">
-        <v>15149.5146950383</v>
+        <v>15160.33534705904</v>
       </c>
       <c r="E30">
-        <v>-3946.491999999997</v>
+        <v>-3781.855999999997</v>
       </c>
       <c r="F30">
-        <v>4609.808</v>
+        <v>4774.444</v>
       </c>
       <c r="G30">
         <v>1232.2</v>
@@ -3747,28 +3747,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M30">
-        <v>254.9223824</v>
+        <v>264.0267532</v>
       </c>
       <c r="N30">
-        <v>739.8143522938776</v>
+        <v>730.7099814938776</v>
       </c>
       <c r="O30">
-        <v>122.0693681284898</v>
+        <v>120.5671469464898</v>
       </c>
       <c r="P30">
-        <v>617.7449841653878</v>
+        <v>610.1428345473878</v>
       </c>
       <c r="Q30">
-        <v>2189.844984165388</v>
+        <v>2182.242834547388</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1004569912098517</v>
+        <v>0.1011309239098925</v>
       </c>
       <c r="T30">
-        <v>1.06536649168425</v>
+        <v>1.078502694398321</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.902116108161233</v>
+        <v>3.767560380293604</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08519385097602369</v>
+        <v>0.08512952828095419</v>
       </c>
       <c r="C31">
-        <v>11618.09134705903</v>
+        <v>11464.29146758846</v>
       </c>
       <c r="D31">
-        <v>15160.33534705904</v>
+        <v>15171.17146758846</v>
       </c>
       <c r="E31">
-        <v>-3781.855999999998</v>
+        <v>-3617.219999999998</v>
       </c>
       <c r="F31">
-        <v>4774.444</v>
+        <v>4939.079999999999</v>
       </c>
       <c r="G31">
         <v>1232.2</v>
@@ -3829,28 +3829,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M31">
-        <v>264.0267532</v>
+        <v>273.1311239999999</v>
       </c>
       <c r="N31">
-        <v>730.7099814938776</v>
+        <v>721.6056106938777</v>
       </c>
       <c r="O31">
-        <v>120.5671469464898</v>
+        <v>119.0649257644898</v>
       </c>
       <c r="P31">
-        <v>610.1428345473878</v>
+        <v>602.5406849293879</v>
       </c>
       <c r="Q31">
-        <v>2182.242834547388</v>
+        <v>2174.640684929388</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1011309239098925</v>
+        <v>0.1018241118299346</v>
       </c>
       <c r="T31">
-        <v>1.078502694398321</v>
+        <v>1.092014217189937</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.767560380293605</v>
+        <v>3.641975034283818</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08512952828095419</v>
+        <v>0.08506520558588468</v>
       </c>
       <c r="C32">
-        <v>11464.29146758846</v>
+        <v>11310.50708981947</v>
       </c>
       <c r="D32">
-        <v>15171.17146758846</v>
+        <v>15182.02308981947</v>
       </c>
       <c r="E32">
-        <v>-3617.219999999998</v>
+        <v>-3452.583999999998</v>
       </c>
       <c r="F32">
-        <v>4939.079999999999</v>
+        <v>5103.715999999999</v>
       </c>
       <c r="G32">
         <v>1232.2</v>
@@ -3911,28 +3911,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M32">
-        <v>273.1311239999999</v>
+        <v>282.2354948</v>
       </c>
       <c r="N32">
-        <v>721.6056106938777</v>
+        <v>712.5012398938777</v>
       </c>
       <c r="O32">
-        <v>119.0649257644898</v>
+        <v>117.5627045824898</v>
       </c>
       <c r="P32">
-        <v>602.5406849293879</v>
+        <v>594.9385353113879</v>
       </c>
       <c r="Q32">
-        <v>2174.640684929388</v>
+        <v>2167.038535311388</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1018241118299346</v>
+        <v>0.1025373921534561</v>
       </c>
       <c r="T32">
-        <v>1.092014217189937</v>
+        <v>1.105917378323339</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.641975034283818</v>
+        <v>3.52449196866176</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08506520558588468</v>
+        <v>0.08500088289081514</v>
       </c>
       <c r="C33">
-        <v>11310.50708981947</v>
+        <v>11156.73824704002</v>
       </c>
       <c r="D33">
-        <v>15182.02308981947</v>
+        <v>15192.89024704001</v>
       </c>
       <c r="E33">
-        <v>-3452.583999999998</v>
+        <v>-3287.947999999998</v>
       </c>
       <c r="F33">
-        <v>5103.715999999999</v>
+        <v>5268.352</v>
       </c>
       <c r="G33">
         <v>1232.2</v>
@@ -3993,28 +3993,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M33">
-        <v>282.2354948</v>
+        <v>291.3398656</v>
       </c>
       <c r="N33">
-        <v>712.5012398938777</v>
+        <v>703.3968690938777</v>
       </c>
       <c r="O33">
-        <v>117.5627045824898</v>
+        <v>116.0604834004898</v>
       </c>
       <c r="P33">
-        <v>594.9385353113879</v>
+        <v>587.3363856933879</v>
       </c>
       <c r="Q33">
-        <v>2167.038535311388</v>
+        <v>2159.436385693388</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1025373921534561</v>
+        <v>0.1032716513100223</v>
       </c>
       <c r="T33">
-        <v>1.105917378323339</v>
+        <v>1.120229455960664</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.52449196866176</v>
+        <v>3.414351594641079</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08500088289081514</v>
+        <v>0.08493656019574565</v>
       </c>
       <c r="C34">
-        <v>11156.73824704002</v>
+        <v>11002.98497263341</v>
       </c>
       <c r="D34">
-        <v>15192.89024704001</v>
+        <v>15203.7729726334</v>
       </c>
       <c r="E34">
-        <v>-3287.947999999998</v>
+        <v>-3123.311999999998</v>
       </c>
       <c r="F34">
-        <v>5268.352</v>
+        <v>5432.987999999999</v>
       </c>
       <c r="G34">
         <v>1232.2</v>
@@ -4075,28 +4075,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M34">
-        <v>291.3398656</v>
+        <v>300.4442364</v>
       </c>
       <c r="N34">
-        <v>703.3968690938777</v>
+        <v>694.2924982938778</v>
       </c>
       <c r="O34">
-        <v>116.0604834004898</v>
+        <v>114.5582622184898</v>
       </c>
       <c r="P34">
-        <v>587.3363856933879</v>
+        <v>579.7342360753879</v>
       </c>
       <c r="Q34">
-        <v>2159.436385693388</v>
+        <v>2151.834236075388</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1032716513100223</v>
+        <v>0.1040278286503666</v>
       </c>
       <c r="T34">
-        <v>1.120229455960664</v>
+        <v>1.134968759796119</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.414351594641079</v>
+        <v>3.310886394803471</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08493656019574565</v>
+        <v>0.08487223750067611</v>
       </c>
       <c r="C35">
-        <v>11002.98497263341</v>
+        <v>10849.24730007868</v>
       </c>
       <c r="D35">
-        <v>15203.7729726334</v>
+        <v>15214.67130007868</v>
       </c>
       <c r="E35">
-        <v>-3123.311999999998</v>
+        <v>-2958.675999999998</v>
       </c>
       <c r="F35">
-        <v>5432.987999999999</v>
+        <v>5597.624</v>
       </c>
       <c r="G35">
         <v>1232.2</v>
@@ -4157,28 +4157,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M35">
-        <v>300.4442364</v>
+        <v>309.5486072</v>
       </c>
       <c r="N35">
-        <v>694.2924982938778</v>
+        <v>685.1881274938777</v>
       </c>
       <c r="O35">
-        <v>114.5582622184898</v>
+        <v>113.0560410364898</v>
       </c>
       <c r="P35">
-        <v>579.7342360753879</v>
+        <v>572.1320864573879</v>
       </c>
       <c r="Q35">
-        <v>2151.834236075388</v>
+        <v>2144.232086457388</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1040278286503666</v>
+        <v>0.1048069204555699</v>
       </c>
       <c r="T35">
-        <v>1.134968759796119</v>
+        <v>1.150154709202345</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.310886394803471</v>
+        <v>3.213507383191604</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08487223750067611</v>
+        <v>0.08480791480560662</v>
       </c>
       <c r="C36">
-        <v>10849.24730007868</v>
+        <v>10695.52526295094</v>
       </c>
       <c r="D36">
-        <v>15214.67130007868</v>
+        <v>15225.58526295094</v>
       </c>
       <c r="E36">
-        <v>-2958.675999999998</v>
+        <v>-2794.039999999997</v>
       </c>
       <c r="F36">
-        <v>5597.624</v>
+        <v>5762.26</v>
       </c>
       <c r="G36">
         <v>1232.2</v>
@@ -4239,28 +4239,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M36">
-        <v>309.5486072</v>
+        <v>318.652978</v>
       </c>
       <c r="N36">
-        <v>685.1881274938777</v>
+        <v>676.0837566938776</v>
       </c>
       <c r="O36">
-        <v>113.0560410364898</v>
+        <v>111.5538198544898</v>
       </c>
       <c r="P36">
-        <v>572.1320864573879</v>
+        <v>564.5299368393878</v>
       </c>
       <c r="Q36">
-        <v>2144.232086457388</v>
+        <v>2136.629936839387</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1048069204555699</v>
+        <v>0.1056099843163179</v>
       </c>
       <c r="T36">
-        <v>1.150154709202345</v>
+        <v>1.165807918590301</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.213507383191604</v>
+        <v>3.121692886528986</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08480791480560662</v>
+        <v>0.08474359211053709</v>
       </c>
       <c r="C37">
-        <v>10695.52526295094</v>
+        <v>10541.8188949217</v>
       </c>
       <c r="D37">
-        <v>15225.58526295094</v>
+        <v>15236.5148949217</v>
       </c>
       <c r="E37">
-        <v>-2794.039999999997</v>
+        <v>-2629.403999999998</v>
       </c>
       <c r="F37">
-        <v>5762.26</v>
+        <v>5926.896</v>
       </c>
       <c r="G37">
         <v>1232.2</v>
@@ -4321,28 +4321,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M37">
-        <v>318.652978</v>
+        <v>327.7573488</v>
       </c>
       <c r="N37">
-        <v>676.0837566938776</v>
+        <v>666.9793858938776</v>
       </c>
       <c r="O37">
-        <v>111.5538198544898</v>
+        <v>110.0515986724898</v>
       </c>
       <c r="P37">
-        <v>564.5299368393878</v>
+        <v>556.9277872213878</v>
       </c>
       <c r="Q37">
-        <v>2136.629936839387</v>
+        <v>2129.027787221388</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1056099843163179</v>
+        <v>0.1064381439227142</v>
       </c>
       <c r="T37">
-        <v>1.165807918590301</v>
+        <v>1.181950290771631</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.121692886528986</v>
+        <v>3.034979195236515</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0847435921105371</v>
+        <v>0.08545164441546758</v>
       </c>
       <c r="C38">
-        <v>10541.8188949217</v>
+        <v>10257.72908147033</v>
       </c>
       <c r="D38">
-        <v>15236.5148949217</v>
+        <v>15117.06108147033</v>
       </c>
       <c r="E38">
-        <v>-2629.403999999999</v>
+        <v>-2464.767999999998</v>
       </c>
       <c r="F38">
-        <v>5926.895999999999</v>
+        <v>6091.531999999999</v>
       </c>
       <c r="G38">
         <v>1232.2</v>
@@ -4403,45 +4403,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M38">
-        <v>327.7573487999999</v>
+        <v>352.0905496</v>
       </c>
       <c r="N38">
-        <v>666.9793858938777</v>
+        <v>642.6461850938776</v>
       </c>
       <c r="O38">
-        <v>110.0515986724898</v>
+        <v>106.0366205404898</v>
       </c>
       <c r="P38">
-        <v>556.9277872213879</v>
+        <v>536.6095645533878</v>
       </c>
       <c r="Q38">
-        <v>2129.027787221388</v>
+        <v>2108.709564553388</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1064381439227142</v>
+        <v>0.107292594310266</v>
       </c>
       <c r="T38">
-        <v>1.181950290771631</v>
+        <v>1.198605119212685</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.165</v>
       </c>
       <c r="W38">
-        <v>0.0461755</v>
+        <v>0.048263</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.034979195236515</v>
+        <v>2.825229861534113</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08545164441546758</v>
+        <v>0.08540819672039807</v>
       </c>
       <c r="C39">
-        <v>10257.72908147033</v>
+        <v>10100.36907202946</v>
       </c>
       <c r="D39">
-        <v>15117.06108147033</v>
+        <v>15124.33707202946</v>
       </c>
       <c r="E39">
-        <v>-2464.767999999998</v>
+        <v>-2300.131999999998</v>
       </c>
       <c r="F39">
-        <v>6091.531999999999</v>
+        <v>6256.168</v>
       </c>
       <c r="G39">
         <v>1232.2</v>
@@ -4485,28 +4485,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M39">
-        <v>352.0905496</v>
+        <v>361.6065104</v>
       </c>
       <c r="N39">
-        <v>642.6461850938776</v>
+        <v>633.1302242938777</v>
       </c>
       <c r="O39">
-        <v>106.0366205404898</v>
+        <v>104.4664870084898</v>
       </c>
       <c r="P39">
-        <v>536.6095645533878</v>
+        <v>528.6637372853879</v>
       </c>
       <c r="Q39">
-        <v>2108.709564553388</v>
+        <v>2100.763737285388</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.107292594310266</v>
+        <v>0.1081746076135453</v>
       </c>
       <c r="T39">
-        <v>1.198605119212685</v>
+        <v>1.215797200184096</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.825229861534113</v>
+        <v>2.750881707283215</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08540819672039807</v>
+        <v>0.08536474902532853</v>
       </c>
       <c r="C40">
-        <v>10100.36907202946</v>
+        <v>9943.016069973328</v>
       </c>
       <c r="D40">
-        <v>15124.33707202946</v>
+        <v>15131.62006997333</v>
       </c>
       <c r="E40">
-        <v>-2300.131999999998</v>
+        <v>-2135.495999999997</v>
       </c>
       <c r="F40">
-        <v>6256.168</v>
+        <v>6420.804</v>
       </c>
       <c r="G40">
         <v>1232.2</v>
@@ -4567,28 +4567,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M40">
-        <v>361.6065104</v>
+        <v>371.1224712</v>
       </c>
       <c r="N40">
-        <v>633.1302242938777</v>
+        <v>623.6142634938776</v>
       </c>
       <c r="O40">
-        <v>104.4664870084898</v>
+        <v>102.8963534764898</v>
       </c>
       <c r="P40">
-        <v>528.6637372853879</v>
+        <v>520.7179100173878</v>
       </c>
       <c r="Q40">
-        <v>2100.763737285388</v>
+        <v>2092.817910017387</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1081746076135453</v>
+        <v>0.1090855393857845</v>
       </c>
       <c r="T40">
-        <v>1.215797200184096</v>
+        <v>1.233552955941455</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.750881707283215</v>
+        <v>2.680346278891338</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08536474902532853</v>
+        <v>0.08532130133025903</v>
       </c>
       <c r="C41">
-        <v>9943.016069973328</v>
+        <v>9785.670085429829</v>
       </c>
       <c r="D41">
-        <v>15131.62006997333</v>
+        <v>15138.91008542983</v>
       </c>
       <c r="E41">
-        <v>-2135.495999999997</v>
+        <v>-1970.859999999998</v>
       </c>
       <c r="F41">
-        <v>6420.804</v>
+        <v>6585.44</v>
       </c>
       <c r="G41">
         <v>1232.2</v>
@@ -4649,28 +4649,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M41">
-        <v>371.1224712</v>
+        <v>380.638432</v>
       </c>
       <c r="N41">
-        <v>623.6142634938776</v>
+        <v>614.0983026938777</v>
       </c>
       <c r="O41">
-        <v>102.8963534764898</v>
+        <v>101.3262199444898</v>
       </c>
       <c r="P41">
-        <v>520.7179100173878</v>
+        <v>512.7720827493879</v>
       </c>
       <c r="Q41">
-        <v>2092.817910017387</v>
+        <v>2084.872082749388</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1090855393857845</v>
+        <v>0.1100268355504317</v>
       </c>
       <c r="T41">
-        <v>1.233552955941455</v>
+        <v>1.251900570224059</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.680346278891338</v>
+        <v>2.613337621919054</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08532130133025903</v>
+        <v>0.08527785363518953</v>
       </c>
       <c r="C42">
-        <v>9785.670085429829</v>
+        <v>9628.331128546422</v>
       </c>
       <c r="D42">
-        <v>15138.91008542983</v>
+        <v>15146.20712854642</v>
       </c>
       <c r="E42">
-        <v>-1970.859999999998</v>
+        <v>-1806.223999999997</v>
       </c>
       <c r="F42">
-        <v>6585.44</v>
+        <v>6750.076</v>
       </c>
       <c r="G42">
         <v>1232.2</v>
@@ -4731,28 +4731,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M42">
-        <v>380.638432</v>
+        <v>390.1543928</v>
       </c>
       <c r="N42">
-        <v>614.0983026938777</v>
+        <v>604.5823418938776</v>
       </c>
       <c r="O42">
-        <v>101.3262199444898</v>
+        <v>99.75608641248981</v>
       </c>
       <c r="P42">
-        <v>512.7720827493879</v>
+        <v>504.8262554813878</v>
       </c>
       <c r="Q42">
-        <v>2084.872082749388</v>
+        <v>2076.926255481388</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1100268355504317</v>
+        <v>0.1110000400596433</v>
       </c>
       <c r="T42">
-        <v>1.251900570224059</v>
+        <v>1.270870137533192</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.613337621919054</v>
+        <v>2.549597679921028</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08527785363518953</v>
+        <v>0.08646185594012</v>
       </c>
       <c r="C43">
-        <v>9628.331128546422</v>
+        <v>9267.325382923314</v>
       </c>
       <c r="D43">
-        <v>15146.20712854642</v>
+        <v>14949.83738292332</v>
       </c>
       <c r="E43">
-        <v>-1806.223999999997</v>
+        <v>-1641.587999999997</v>
       </c>
       <c r="F43">
-        <v>6750.076</v>
+        <v>6914.712</v>
       </c>
       <c r="G43">
         <v>1232.2</v>
@@ -4813,45 +4813,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M43">
-        <v>390.1543928</v>
+        <v>423.8718456</v>
       </c>
       <c r="N43">
-        <v>604.5823418938776</v>
+        <v>570.8648890938777</v>
       </c>
       <c r="O43">
-        <v>99.75608641248981</v>
+        <v>94.19270670048982</v>
       </c>
       <c r="P43">
-        <v>504.8262554813878</v>
+        <v>476.6721823933879</v>
       </c>
       <c r="Q43">
-        <v>2076.926255481388</v>
+        <v>2048.772182393388</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1110000400596433</v>
+        <v>0.1120068033450345</v>
       </c>
       <c r="T43">
-        <v>1.270870137533192</v>
+        <v>1.290493827852985</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.165</v>
       </c>
       <c r="W43">
-        <v>0.048263</v>
+        <v>0.05118549999999999</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.549597679921028</v>
+        <v>2.346786522907191</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08646185594012</v>
+        <v>0.0864476332450505</v>
       </c>
       <c r="C44">
-        <v>9267.325382923316</v>
+        <v>9105.018032546493</v>
       </c>
       <c r="D44">
-        <v>14949.83738292332</v>
+        <v>14952.16603254649</v>
       </c>
       <c r="E44">
-        <v>-1641.587999999998</v>
+        <v>-1476.951999999998</v>
       </c>
       <c r="F44">
-        <v>6914.712</v>
+        <v>7079.347999999999</v>
       </c>
       <c r="G44">
         <v>1232.2</v>
@@ -4895,28 +4895,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M44">
-        <v>423.8718456</v>
+        <v>433.9640324</v>
       </c>
       <c r="N44">
-        <v>570.8648890938778</v>
+        <v>560.7727022938777</v>
       </c>
       <c r="O44">
-        <v>94.19270670048984</v>
+        <v>92.52749587848983</v>
       </c>
       <c r="P44">
-        <v>476.6721823933879</v>
+        <v>468.2452064153879</v>
       </c>
       <c r="Q44">
-        <v>2048.772182393388</v>
+        <v>2040.345206415388</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1120068033450345</v>
+        <v>0.1130488916579833</v>
       </c>
       <c r="T44">
-        <v>1.290493827852985</v>
+        <v>1.310806068710314</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.346786522907191</v>
+        <v>2.292210092141908</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0864476332450505</v>
+        <v>0.08746213054998098</v>
       </c>
       <c r="C45">
-        <v>9105.018032546493</v>
+        <v>8776.080303153663</v>
       </c>
       <c r="D45">
-        <v>14952.16603254649</v>
+        <v>14787.86430315366</v>
       </c>
       <c r="E45">
-        <v>-1476.951999999998</v>
+        <v>-1312.315999999998</v>
       </c>
       <c r="F45">
-        <v>7079.347999999999</v>
+        <v>7243.983999999999</v>
       </c>
       <c r="G45">
         <v>1232.2</v>
@@ -4977,45 +4977,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M45">
-        <v>433.9640324</v>
+        <v>464.3393744</v>
       </c>
       <c r="N45">
-        <v>560.7727022938777</v>
+        <v>530.3973602938777</v>
       </c>
       <c r="O45">
-        <v>92.52749587848983</v>
+        <v>87.51556444848983</v>
       </c>
       <c r="P45">
-        <v>468.2452064153879</v>
+        <v>442.8817958453878</v>
       </c>
       <c r="Q45">
-        <v>2040.345206415388</v>
+        <v>2014.981795845388</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1130488916579833</v>
+        <v>0.1141281974106803</v>
       </c>
       <c r="T45">
-        <v>1.310806068710314</v>
+        <v>1.33184374674112</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.165</v>
       </c>
       <c r="W45">
-        <v>0.05118549999999999</v>
+        <v>0.0535235</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.292210092141908</v>
+        <v>2.142262296793665</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08746213054998098</v>
+        <v>0.08747128785491146</v>
       </c>
       <c r="C46">
-        <v>8776.080303153663</v>
+        <v>8609.977684566467</v>
       </c>
       <c r="D46">
-        <v>14787.86430315366</v>
+        <v>14786.39768456647</v>
       </c>
       <c r="E46">
-        <v>-1312.315999999998</v>
+        <v>-1147.679999999998</v>
       </c>
       <c r="F46">
-        <v>7243.983999999999</v>
+        <v>7408.62</v>
       </c>
       <c r="G46">
         <v>1232.2</v>
@@ -5059,28 +5059,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M46">
-        <v>464.3393744</v>
+        <v>474.892542</v>
       </c>
       <c r="N46">
-        <v>530.3973602938777</v>
+        <v>519.8441926938776</v>
       </c>
       <c r="O46">
-        <v>87.51556444848983</v>
+        <v>85.77429179448981</v>
       </c>
       <c r="P46">
-        <v>442.8817958453878</v>
+        <v>434.0699008993878</v>
       </c>
       <c r="Q46">
-        <v>2014.981795845388</v>
+        <v>2006.169900899388</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1141281974106803</v>
+        <v>0.1152467506452935</v>
       </c>
       <c r="T46">
-        <v>1.33184374674112</v>
+        <v>1.353646431245773</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.142262296793665</v>
+        <v>2.094656467976028</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08747128785491146</v>
+        <v>0.08748044515984196</v>
       </c>
       <c r="C47">
-        <v>8609.977684566467</v>
+        <v>8443.87535686059</v>
       </c>
       <c r="D47">
-        <v>14786.39768456647</v>
+        <v>14784.93135686059</v>
       </c>
       <c r="E47">
-        <v>-1147.679999999998</v>
+        <v>-983.0439999999981</v>
       </c>
       <c r="F47">
-        <v>7408.62</v>
+        <v>7573.255999999999</v>
       </c>
       <c r="G47">
         <v>1232.2</v>
@@ -5141,28 +5141,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M47">
-        <v>474.892542</v>
+        <v>485.4457096</v>
       </c>
       <c r="N47">
-        <v>519.8441926938776</v>
+        <v>509.2910250938777</v>
       </c>
       <c r="O47">
-        <v>85.77429179448981</v>
+        <v>84.03301914048983</v>
       </c>
       <c r="P47">
-        <v>434.0699008993878</v>
+        <v>425.2580059533879</v>
       </c>
       <c r="Q47">
-        <v>2006.169900899388</v>
+        <v>1997.358005953388</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1152467506452935</v>
+        <v>0.1164067317774851</v>
       </c>
       <c r="T47">
-        <v>1.353646431245773</v>
+        <v>1.376256622583932</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.094656467976028</v>
+        <v>2.049120457802637</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08748044515984196</v>
+        <v>0.08748960246477243</v>
       </c>
       <c r="C48">
-        <v>8443.87535686059</v>
+        <v>8277.773319949516</v>
       </c>
       <c r="D48">
-        <v>14784.93135686059</v>
+        <v>14783.46531994952</v>
       </c>
       <c r="E48">
-        <v>-983.0439999999981</v>
+        <v>-818.4079999999976</v>
       </c>
       <c r="F48">
-        <v>7573.255999999999</v>
+        <v>7737.892</v>
       </c>
       <c r="G48">
         <v>1232.2</v>
@@ -5223,28 +5223,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M48">
-        <v>485.4457096</v>
+        <v>495.9988772</v>
       </c>
       <c r="N48">
-        <v>509.2910250938777</v>
+        <v>498.7378574938776</v>
       </c>
       <c r="O48">
-        <v>84.03301914048983</v>
+        <v>82.29174648648981</v>
       </c>
       <c r="P48">
-        <v>425.2580059533879</v>
+        <v>416.4461110073878</v>
       </c>
       <c r="Q48">
-        <v>1997.358005953388</v>
+        <v>1988.546111007388</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1164067317774851</v>
+        <v>0.1176104857825895</v>
       </c>
       <c r="T48">
-        <v>1.376256622583932</v>
+        <v>1.399720028689568</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.049120457802637</v>
+        <v>2.005522150189814</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08748960246477243</v>
+        <v>0.09062499976970292</v>
       </c>
       <c r="C49">
-        <v>8277.773319949516</v>
+        <v>7627.707049770397</v>
       </c>
       <c r="D49">
-        <v>14783.46531994952</v>
+        <v>14298.0350497704</v>
       </c>
       <c r="E49">
-        <v>-818.4079999999976</v>
+        <v>-653.7719999999972</v>
       </c>
       <c r="F49">
-        <v>7737.892</v>
+        <v>7902.528</v>
       </c>
       <c r="G49">
         <v>1232.2</v>
@@ -5305,45 +5305,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M49">
-        <v>495.9988772</v>
+        <v>568.1917632000001</v>
       </c>
       <c r="N49">
-        <v>498.7378574938776</v>
+        <v>426.5449714938776</v>
       </c>
       <c r="O49">
-        <v>82.29174648648981</v>
+        <v>70.3799202964898</v>
       </c>
       <c r="P49">
-        <v>416.4461110073878</v>
+        <v>356.1650511973878</v>
       </c>
       <c r="Q49">
-        <v>1988.546111007388</v>
+        <v>1928.265051197388</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1176104857825895</v>
+        <v>0.1188605380186595</v>
       </c>
       <c r="T49">
-        <v>1.399720028689568</v>
+        <v>1.424085873491575</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.165</v>
       </c>
       <c r="W49">
-        <v>0.0535235</v>
+        <v>0.0600365</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.005522150189814</v>
+        <v>1.750706010047767</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09062499976970292</v>
+        <v>0.0922949720746334</v>
       </c>
       <c r="C50">
-        <v>7627.707049770398</v>
+        <v>7217.309526440724</v>
       </c>
       <c r="D50">
-        <v>14298.0350497704</v>
+        <v>14052.27352644072</v>
       </c>
       <c r="E50">
-        <v>-653.7719999999981</v>
+        <v>-489.1359999999986</v>
       </c>
       <c r="F50">
-        <v>7902.527999999999</v>
+        <v>8067.163999999999</v>
       </c>
       <c r="G50">
         <v>1232.2</v>
@@ -5387,45 +5387,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M50">
-        <v>568.1917632</v>
+        <v>611.4910312</v>
       </c>
       <c r="N50">
-        <v>426.5449714938777</v>
+        <v>383.2457034938777</v>
       </c>
       <c r="O50">
-        <v>70.37992029648983</v>
+        <v>63.23554107648983</v>
       </c>
       <c r="P50">
-        <v>356.1650511973879</v>
+        <v>320.0101624173879</v>
       </c>
       <c r="Q50">
-        <v>1928.265051197388</v>
+        <v>1892.110162417388</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1188605380186595</v>
+        <v>0.1201596119110459</v>
       </c>
       <c r="T50">
-        <v>1.424085873491575</v>
+        <v>1.449407241619151</v>
       </c>
       <c r="U50">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.165</v>
       </c>
       <c r="W50">
-        <v>0.0600365</v>
+        <v>0.063293</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.750706010047767</v>
+        <v>1.626739696806002</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0922949720746334</v>
+        <v>0.09240182437956387</v>
       </c>
       <c r="C51">
-        <v>7217.309526440724</v>
+        <v>7037.235869674429</v>
       </c>
       <c r="D51">
-        <v>14052.27352644072</v>
+        <v>14036.83586967443</v>
       </c>
       <c r="E51">
-        <v>-489.1359999999986</v>
+        <v>-324.4999999999982</v>
       </c>
       <c r="F51">
-        <v>8067.163999999999</v>
+        <v>8231.799999999999</v>
       </c>
       <c r="G51">
         <v>1232.2</v>
@@ -5469,28 +5469,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M51">
-        <v>611.4910312</v>
+        <v>623.9704399999999</v>
       </c>
       <c r="N51">
-        <v>383.2457034938777</v>
+        <v>370.7662946938777</v>
       </c>
       <c r="O51">
-        <v>63.23554107648983</v>
+        <v>61.17643862448983</v>
       </c>
       <c r="P51">
-        <v>320.0101624173879</v>
+        <v>309.5898560693879</v>
       </c>
       <c r="Q51">
-        <v>1892.110162417388</v>
+        <v>1881.689856069388</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1201596119110459</v>
+        <v>0.1215106487591278</v>
       </c>
       <c r="T51">
-        <v>1.449407241619151</v>
+        <v>1.47574146447183</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.626739696806002</v>
+        <v>1.594204902869882</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09240182437956387</v>
+        <v>0.09250867668449436</v>
       </c>
       <c r="C52">
-        <v>7037.235869674429</v>
+        <v>6857.196094929635</v>
       </c>
       <c r="D52">
-        <v>14036.83586967443</v>
+        <v>14021.43209492963</v>
       </c>
       <c r="E52">
-        <v>-324.4999999999982</v>
+        <v>-159.8639999999978</v>
       </c>
       <c r="F52">
-        <v>8231.799999999999</v>
+        <v>8396.436</v>
       </c>
       <c r="G52">
         <v>1232.2</v>
@@ -5551,28 +5551,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M52">
-        <v>623.9704399999999</v>
+        <v>636.4498488</v>
       </c>
       <c r="N52">
-        <v>370.7662946938777</v>
+        <v>358.2868858938776</v>
       </c>
       <c r="O52">
-        <v>61.17643862448983</v>
+        <v>59.11733617248981</v>
       </c>
       <c r="P52">
-        <v>309.5898560693879</v>
+        <v>299.1695497213879</v>
       </c>
       <c r="Q52">
-        <v>1881.689856069388</v>
+        <v>1871.269549721388</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1215106487591278</v>
+        <v>0.1229168299683558</v>
       </c>
       <c r="T52">
-        <v>1.47574146447183</v>
+        <v>1.503150553563394</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.594204902869882</v>
+        <v>1.562945983205767</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09250867668449436</v>
+        <v>0.09261552898942485</v>
       </c>
       <c r="C53">
-        <v>6857.196094929635</v>
+        <v>6677.190090784037</v>
       </c>
       <c r="D53">
-        <v>14021.43209492963</v>
+        <v>14006.06209078404</v>
       </c>
       <c r="E53">
-        <v>-159.8639999999978</v>
+        <v>4.772000000002663</v>
       </c>
       <c r="F53">
-        <v>8396.436</v>
+        <v>8561.072</v>
       </c>
       <c r="G53">
         <v>1232.2</v>
@@ -5633,28 +5633,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M53">
-        <v>636.4498488</v>
+        <v>648.9292576</v>
       </c>
       <c r="N53">
-        <v>358.2868858938776</v>
+        <v>345.8074770938777</v>
       </c>
       <c r="O53">
-        <v>59.11733617248981</v>
+        <v>57.05823372048982</v>
       </c>
       <c r="P53">
-        <v>299.1695497213879</v>
+        <v>288.7492433733879</v>
       </c>
       <c r="Q53">
-        <v>1871.269549721388</v>
+        <v>1860.849243373388</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1229168299683558</v>
+        <v>0.1243816020613018</v>
       </c>
       <c r="T53">
-        <v>1.503150553563394</v>
+        <v>1.531701688033773</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.562945983205767</v>
+        <v>1.532889329682579</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09261552898942485</v>
+        <v>0.09272238129435534</v>
       </c>
       <c r="C54">
-        <v>6677.190090784037</v>
+        <v>6497.217746303335</v>
       </c>
       <c r="D54">
-        <v>14006.06209078404</v>
+        <v>13990.72574630333</v>
       </c>
       <c r="E54">
-        <v>4.772000000002663</v>
+        <v>169.4080000000031</v>
       </c>
       <c r="F54">
-        <v>8561.072</v>
+        <v>8725.708000000001</v>
       </c>
       <c r="G54">
         <v>1232.2</v>
@@ -5715,28 +5715,28 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M54">
-        <v>648.9292576</v>
+        <v>661.4086664000001</v>
       </c>
       <c r="N54">
-        <v>345.8074770938777</v>
+        <v>333.3280682938775</v>
       </c>
       <c r="O54">
-        <v>57.05823372048982</v>
+        <v>54.9991312684898</v>
       </c>
       <c r="P54">
-        <v>288.7492433733879</v>
+        <v>278.3289370253877</v>
       </c>
       <c r="Q54">
-        <v>1860.849243373388</v>
+        <v>1850.428937025388</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1243816020613018</v>
+        <v>0.1259087048816071</v>
       </c>
       <c r="T54">
-        <v>1.531701688033773</v>
+        <v>1.561467764396508</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.532889329682579</v>
+        <v>1.503966889499889</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09272238129435534</v>
+        <v>0.1129336537980704</v>
       </c>
       <c r="C55">
-        <v>6497.217746303335</v>
+        <v>3932.055393881934</v>
       </c>
       <c r="D55">
-        <v>13990.72574630333</v>
+        <v>11590.19939388193</v>
       </c>
       <c r="E55">
-        <v>169.4080000000031</v>
+        <v>334.0440000000017</v>
       </c>
       <c r="F55">
-        <v>8725.708000000001</v>
+        <v>8890.343999999999</v>
       </c>
       <c r="G55">
         <v>1232.2</v>
@@ -5797,45 +5797,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M55">
-        <v>661.4086664000001</v>
+        <v>1054.3947984</v>
       </c>
       <c r="N55">
-        <v>333.3280682938775</v>
+        <v>-59.65806370612222</v>
       </c>
       <c r="O55">
-        <v>54.9991312684898</v>
+        <v>-9.843580511510167</v>
       </c>
       <c r="P55">
-        <v>278.3289370253877</v>
+        <v>-49.81448319461205</v>
       </c>
       <c r="Q55">
-        <v>1850.428937025388</v>
+        <v>1522.285516805388</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1259087048816071</v>
+        <v>0.1279543786047114</v>
       </c>
       <c r="T55">
-        <v>1.561467764396508</v>
+        <v>1.601341752870309</v>
       </c>
       <c r="U55">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.165</v>
+        <v>0.1556642364639437</v>
       </c>
       <c r="W55">
-        <v>0.063293</v>
+        <v>0.1001382215553763</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>1.503966889499889</v>
+        <v>0.9434196149329921</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1129336537980704</v>
+        <v>0.1136616537980704</v>
       </c>
       <c r="C56">
-        <v>3932.055393881934</v>
+        <v>3696.229378284517</v>
       </c>
       <c r="D56">
-        <v>11590.19939388193</v>
+        <v>11519.00937828452</v>
       </c>
       <c r="E56">
-        <v>334.0440000000017</v>
+        <v>498.6800000000021</v>
       </c>
       <c r="F56">
-        <v>8890.343999999999</v>
+        <v>9054.98</v>
       </c>
       <c r="G56">
         <v>1232.2</v>
@@ -5879,37 +5879,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M56">
-        <v>1054.3947984</v>
+        <v>1073.920628</v>
       </c>
       <c r="N56">
-        <v>-59.65806370612222</v>
+        <v>-79.1838933061224</v>
       </c>
       <c r="O56">
-        <v>-9.843580511510167</v>
+        <v>-13.0653423955102</v>
       </c>
       <c r="P56">
-        <v>-49.81448319461205</v>
+        <v>-66.1185509106122</v>
       </c>
       <c r="Q56">
-        <v>1522.285516805388</v>
+        <v>1505.981449089388</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1279543786047114</v>
+        <v>0.1297800314625938</v>
       </c>
       <c r="T56">
-        <v>1.601341752870309</v>
+        <v>1.636927125156315</v>
       </c>
       <c r="U56">
         <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.1556642364639437</v>
+        <v>0.1528339776191447</v>
       </c>
       <c r="W56">
-        <v>0.1001382215553763</v>
+        <v>0.1004738902543694</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9434196149329921</v>
+        <v>0.9262665310251192</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1136616537980704</v>
+        <v>0.1143896537980704</v>
       </c>
       <c r="C57">
-        <v>3696.229378284517</v>
+        <v>3461.27255899687</v>
       </c>
       <c r="D57">
-        <v>11519.00937828452</v>
+        <v>11448.68855899687</v>
       </c>
       <c r="E57">
-        <v>498.6800000000021</v>
+        <v>663.3160000000025</v>
       </c>
       <c r="F57">
-        <v>9054.98</v>
+        <v>9219.616</v>
       </c>
       <c r="G57">
         <v>1232.2</v>
@@ -5961,37 +5961,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M57">
-        <v>1073.920628</v>
+        <v>1093.4464576</v>
       </c>
       <c r="N57">
-        <v>-79.1838933061224</v>
+        <v>-98.70972290612235</v>
       </c>
       <c r="O57">
-        <v>-13.0653423955102</v>
+        <v>-16.28710427951019</v>
       </c>
       <c r="P57">
-        <v>-66.1185509106122</v>
+        <v>-82.42261862661216</v>
       </c>
       <c r="Q57">
-        <v>1505.981449089388</v>
+        <v>1489.677381373388</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1297800314625938</v>
+        <v>0.1316886685412892</v>
       </c>
       <c r="T57">
-        <v>1.636927125156315</v>
+        <v>1.674130014364414</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.1528339776191447</v>
+        <v>0.1501047994473743</v>
       </c>
       <c r="W57">
-        <v>0.1004738902543694</v>
+        <v>0.1007975707855414</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9262665310251192</v>
+        <v>0.9097260572568137</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1143896537980704</v>
+        <v>0.1151176537980704</v>
       </c>
       <c r="C58">
-        <v>3461.27255899687</v>
+        <v>3227.169113897548</v>
       </c>
       <c r="D58">
-        <v>11448.68855899687</v>
+        <v>11379.22111389755</v>
       </c>
       <c r="E58">
-        <v>663.3160000000025</v>
+        <v>827.952000000003</v>
       </c>
       <c r="F58">
-        <v>9219.616</v>
+        <v>9384.252</v>
       </c>
       <c r="G58">
         <v>1232.2</v>
@@ -6043,37 +6043,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M58">
-        <v>1093.4464576</v>
+        <v>1112.9722872</v>
       </c>
       <c r="N58">
-        <v>-98.70972290612235</v>
+        <v>-118.2355525061225</v>
       </c>
       <c r="O58">
-        <v>-16.28710427951019</v>
+        <v>-19.50886616351022</v>
       </c>
       <c r="P58">
-        <v>-82.42261862661216</v>
+        <v>-98.72668634261231</v>
       </c>
       <c r="Q58">
-        <v>1489.677381373388</v>
+        <v>1473.373313657388</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1316886685412892</v>
+        <v>0.1336860794375982</v>
       </c>
       <c r="T58">
-        <v>1.674130014364414</v>
+        <v>1.713063270512423</v>
       </c>
       <c r="U58">
         <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.1501047994473743</v>
+        <v>0.1474713819132098</v>
       </c>
       <c r="W58">
-        <v>0.1007975707855414</v>
+        <v>0.1011098941050933</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9097260572568137</v>
+        <v>0.8937659509891501</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1151176537980704</v>
+        <v>0.1158456537980704</v>
       </c>
       <c r="C59">
-        <v>3227.169113897548</v>
+        <v>2993.903602565906</v>
       </c>
       <c r="D59">
-        <v>11379.22111389755</v>
+        <v>11310.59160256591</v>
       </c>
       <c r="E59">
-        <v>827.952000000003</v>
+        <v>992.5880000000034</v>
       </c>
       <c r="F59">
-        <v>9384.252</v>
+        <v>9548.888000000001</v>
       </c>
       <c r="G59">
         <v>1232.2</v>
@@ -6125,37 +6125,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M59">
-        <v>1112.9722872</v>
+        <v>1132.4981168</v>
       </c>
       <c r="N59">
-        <v>-118.2355525061225</v>
+        <v>-137.7613821061225</v>
       </c>
       <c r="O59">
-        <v>-19.50886616351022</v>
+        <v>-22.73062804751021</v>
       </c>
       <c r="P59">
-        <v>-98.72668634261231</v>
+        <v>-115.0307540586123</v>
       </c>
       <c r="Q59">
-        <v>1473.373313657388</v>
+        <v>1457.069245941388</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1336860794375982</v>
+        <v>0.1357786051384934</v>
       </c>
       <c r="T59">
-        <v>1.713063270512423</v>
+        <v>1.75385049123891</v>
       </c>
       <c r="U59">
         <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.1474713819132098</v>
+        <v>0.1449287718802234</v>
       </c>
       <c r="W59">
-        <v>0.1011098941050933</v>
+        <v>0.1014114476550055</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8937659509891501</v>
+        <v>0.8783561932134751</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1158456537980704</v>
+        <v>0.1165736537980704</v>
       </c>
       <c r="C60">
-        <v>2993.90360256591</v>
+        <v>2761.46095484069</v>
       </c>
       <c r="D60">
-        <v>11310.59160256591</v>
+        <v>11242.78495484069</v>
       </c>
       <c r="E60">
-        <v>992.5880000000016</v>
+        <v>1157.224000000002</v>
       </c>
       <c r="F60">
-        <v>9548.887999999999</v>
+        <v>9713.523999999999</v>
       </c>
       <c r="G60">
         <v>1232.2</v>
@@ -6207,37 +6207,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M60">
-        <v>1132.4981168</v>
+        <v>1152.0239464</v>
       </c>
       <c r="N60">
-        <v>-137.7613821061223</v>
+        <v>-157.2872117061224</v>
       </c>
       <c r="O60">
-        <v>-22.73062804751017</v>
+        <v>-25.9523899315102</v>
       </c>
       <c r="P60">
-        <v>-115.0307540586121</v>
+        <v>-131.3348217746122</v>
       </c>
       <c r="Q60">
-        <v>1457.069245941388</v>
+        <v>1440.765178225388</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1357786051384934</v>
+        <v>0.1379732052638225</v>
       </c>
       <c r="T60">
-        <v>1.753850491238909</v>
+        <v>1.796627332488639</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.1449287718802234</v>
+        <v>0.1424723520178467</v>
       </c>
       <c r="W60">
-        <v>0.1014114476550055</v>
+        <v>0.1017027790506834</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8783561932134754</v>
+        <v>0.8634688001081621</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1165736537980704</v>
+        <v>0.1173016537980704</v>
       </c>
       <c r="C61">
-        <v>2761.46095484069</v>
+        <v>2529.826459787682</v>
       </c>
       <c r="D61">
-        <v>11242.78495484069</v>
+        <v>11175.78645978768</v>
       </c>
       <c r="E61">
-        <v>1157.224000000002</v>
+        <v>1321.860000000001</v>
       </c>
       <c r="F61">
-        <v>9713.523999999999</v>
+        <v>9878.159999999998</v>
       </c>
       <c r="G61">
         <v>1232.2</v>
@@ -6289,37 +6289,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M61">
-        <v>1152.0239464</v>
+        <v>1171.549776</v>
       </c>
       <c r="N61">
-        <v>-157.2872117061224</v>
+        <v>-176.8130413061222</v>
       </c>
       <c r="O61">
-        <v>-25.9523899315102</v>
+        <v>-29.17415181551016</v>
       </c>
       <c r="P61">
-        <v>-131.3348217746122</v>
+        <v>-147.638889490612</v>
       </c>
       <c r="Q61">
-        <v>1440.765178225388</v>
+        <v>1424.461110509388</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1379732052638225</v>
+        <v>0.140277535395418</v>
       </c>
       <c r="T61">
-        <v>1.796627332488639</v>
+        <v>1.841543015800855</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.1424723520178467</v>
+        <v>0.1400978128175493</v>
       </c>
       <c r="W61">
-        <v>0.1017027790506834</v>
+        <v>0.1019843993998387</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8634688001081621</v>
+        <v>0.8490776534396929</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1173016537980704</v>
+        <v>0.1180296537980704</v>
       </c>
       <c r="C62">
-        <v>2529.826459787682</v>
+        <v>2298.985755059526</v>
       </c>
       <c r="D62">
-        <v>11175.78645978768</v>
+        <v>11109.58175505952</v>
       </c>
       <c r="E62">
-        <v>1321.860000000001</v>
+        <v>1486.496000000001</v>
       </c>
       <c r="F62">
-        <v>9878.159999999998</v>
+        <v>10042.796</v>
       </c>
       <c r="G62">
         <v>1232.2</v>
@@ -6371,37 +6371,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M62">
-        <v>1171.549776</v>
+        <v>1191.0756056</v>
       </c>
       <c r="N62">
-        <v>-176.8130413061222</v>
+        <v>-196.3388709061223</v>
       </c>
       <c r="O62">
-        <v>-29.17415181551016</v>
+        <v>-32.39591369951019</v>
       </c>
       <c r="P62">
-        <v>-147.638889490612</v>
+        <v>-163.9429572066122</v>
       </c>
       <c r="Q62">
-        <v>1424.461110509388</v>
+        <v>1408.157042793388</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.140277535395418</v>
+        <v>0.1427000363029929</v>
       </c>
       <c r="T62">
-        <v>1.841543015800855</v>
+        <v>1.888762067488057</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.1400978128175493</v>
+        <v>0.1378011273615239</v>
       </c>
       <c r="W62">
-        <v>0.1019843993998387</v>
+        <v>0.1022567862949233</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8490776534396929</v>
+        <v>0.8351583476455995</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1180296537980704</v>
+        <v>0.1187576537980704</v>
       </c>
       <c r="C63">
-        <v>2298.985755059526</v>
+        <v>2068.924816631494</v>
       </c>
       <c r="D63">
-        <v>11109.58175505952</v>
+        <v>11044.15681663149</v>
       </c>
       <c r="E63">
-        <v>1486.496000000001</v>
+        <v>1651.132000000001</v>
       </c>
       <c r="F63">
-        <v>10042.796</v>
+        <v>10207.432</v>
       </c>
       <c r="G63">
         <v>1232.2</v>
@@ -6453,37 +6453,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M63">
-        <v>1191.0756056</v>
+        <v>1210.6014352</v>
       </c>
       <c r="N63">
-        <v>-196.3388709061223</v>
+        <v>-215.8647005061223</v>
       </c>
       <c r="O63">
-        <v>-32.39591369951019</v>
+        <v>-35.61767558351018</v>
       </c>
       <c r="P63">
-        <v>-163.9429572066122</v>
+        <v>-180.2470249226121</v>
       </c>
       <c r="Q63">
-        <v>1408.157042793388</v>
+        <v>1391.852975077388</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1427000363029929</v>
+        <v>0.1452500372583348</v>
       </c>
       <c r="T63">
-        <v>1.888762067488057</v>
+        <v>1.938466332421952</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.1378011273615239</v>
+        <v>0.1355785285331122</v>
       </c>
       <c r="W63">
-        <v>0.1022567862949233</v>
+        <v>0.1025203865159729</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8351583476455995</v>
+        <v>0.8216880517158317</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1187576537980704</v>
+        <v>0.1194856537980704</v>
       </c>
       <c r="C64">
-        <v>2068.924816631494</v>
+        <v>1839.629948897764</v>
       </c>
       <c r="D64">
-        <v>11044.15681663149</v>
+        <v>10979.49794889776</v>
       </c>
       <c r="E64">
-        <v>1651.132000000001</v>
+        <v>1815.768000000002</v>
       </c>
       <c r="F64">
-        <v>10207.432</v>
+        <v>10372.068</v>
       </c>
       <c r="G64">
         <v>1232.2</v>
@@ -6535,37 +6535,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M64">
-        <v>1210.6014352</v>
+        <v>1230.1272648</v>
       </c>
       <c r="N64">
-        <v>-215.8647005061223</v>
+        <v>-235.3905301061222</v>
       </c>
       <c r="O64">
-        <v>-35.61767558351018</v>
+        <v>-38.83943746751017</v>
       </c>
       <c r="P64">
-        <v>-180.2470249226121</v>
+        <v>-196.5510926386121</v>
       </c>
       <c r="Q64">
-        <v>1391.852975077388</v>
+        <v>1375.548907361388</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1452500372583348</v>
+        <v>0.1479378761031547</v>
       </c>
       <c r="T64">
-        <v>1.938466332421952</v>
+        <v>1.990857314379302</v>
       </c>
       <c r="U64">
         <v>0.1186</v>
       </c>
       <c r="V64">
-        <v>0.1355785285331122</v>
+        <v>0.133426488397666</v>
       </c>
       <c r="W64">
-        <v>0.1025203865159729</v>
+        <v>0.1027756184760368</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8216880517158317</v>
+        <v>0.8086453842282788</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1194856537980704</v>
+        <v>0.1742414029361905</v>
       </c>
       <c r="C65">
-        <v>1839.629948897764</v>
+        <v>-1681.683279171315</v>
       </c>
       <c r="D65">
-        <v>10979.49794889776</v>
+        <v>7622.820720828684</v>
       </c>
       <c r="E65">
-        <v>1815.768000000002</v>
+        <v>1980.404000000002</v>
       </c>
       <c r="F65">
-        <v>10372.068</v>
+        <v>10536.704</v>
       </c>
       <c r="G65">
         <v>1232.2</v>
@@ -6617,45 +6617,45 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M65">
-        <v>1230.1272648</v>
+        <v>2115.7701632</v>
       </c>
       <c r="N65">
-        <v>-235.3905301061222</v>
+        <v>-1121.033428506122</v>
       </c>
       <c r="O65">
-        <v>-38.83943746751017</v>
+        <v>-184.9705157035102</v>
       </c>
       <c r="P65">
-        <v>-196.5510926386121</v>
+        <v>-936.062912802612</v>
       </c>
       <c r="Q65">
-        <v>1375.548907361388</v>
+        <v>636.0370871973879</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1479378761031547</v>
+        <v>0.1547187869341314</v>
       </c>
       <c r="T65">
-        <v>1.990857314379302</v>
+        <v>2.123029887777732</v>
       </c>
       <c r="U65">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.133426488397666</v>
+        <v>0.07757532650722741</v>
       </c>
       <c r="W65">
-        <v>0.1027756184760368</v>
+        <v>0.1852228744373488</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8086453842282788</v>
+        <v>0.4701534939831964</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1742414029361905</v>
+        <v>0.1757914029361905</v>
       </c>
       <c r="C66">
-        <v>-1681.683279171315</v>
+        <v>-1911.723000524948</v>
       </c>
       <c r="D66">
-        <v>7622.820720828684</v>
+        <v>7557.416999475053</v>
       </c>
       <c r="E66">
-        <v>1980.404000000002</v>
+        <v>2145.040000000003</v>
       </c>
       <c r="F66">
-        <v>10536.704</v>
+        <v>10701.34</v>
       </c>
       <c r="G66">
         <v>1232.2</v>
@@ -6699,37 +6699,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M66">
-        <v>2115.7701632</v>
+        <v>2148.829072</v>
       </c>
       <c r="N66">
-        <v>-1121.033428506122</v>
+        <v>-1154.092337306122</v>
       </c>
       <c r="O66">
-        <v>-184.9705157035102</v>
+        <v>-190.4252356555102</v>
       </c>
       <c r="P66">
-        <v>-936.062912802612</v>
+        <v>-963.6671016506122</v>
       </c>
       <c r="Q66">
-        <v>636.0370871973879</v>
+        <v>608.4328983493878</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1547187869341314</v>
+        <v>0.1578307522751066</v>
       </c>
       <c r="T66">
-        <v>2.123029887777732</v>
+        <v>2.183687884571382</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.07757532650722741</v>
+        <v>0.07638185994557777</v>
       </c>
       <c r="W66">
-        <v>0.1852228744373488</v>
+        <v>0.185462522522928</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4701534939831964</v>
+        <v>0.4629203633065319</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1757914029361905</v>
+        <v>0.1773414029361905</v>
       </c>
       <c r="C67">
-        <v>-1911.723000524948</v>
+        <v>-2140.649943031114</v>
       </c>
       <c r="D67">
-        <v>7557.416999475053</v>
+        <v>7493.126056968884</v>
       </c>
       <c r="E67">
-        <v>2145.040000000003</v>
+        <v>2309.676000000001</v>
       </c>
       <c r="F67">
-        <v>10701.34</v>
+        <v>10865.976</v>
       </c>
       <c r="G67">
         <v>1232.2</v>
@@ -6781,37 +6781,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M67">
-        <v>2148.829072</v>
+        <v>2181.8879808</v>
       </c>
       <c r="N67">
-        <v>-1154.092337306122</v>
+        <v>-1187.151246106122</v>
       </c>
       <c r="O67">
-        <v>-190.4252356555102</v>
+        <v>-195.8799556075101</v>
       </c>
       <c r="P67">
-        <v>-963.6671016506122</v>
+        <v>-991.2712904986118</v>
       </c>
       <c r="Q67">
-        <v>608.4328983493878</v>
+        <v>580.8287095013881</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1578307522751066</v>
+        <v>0.1611257744008451</v>
       </c>
       <c r="T67">
-        <v>2.183687884571382</v>
+        <v>2.247913998823481</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.07638185994557777</v>
+        <v>0.07522455903731144</v>
       </c>
       <c r="W67">
-        <v>0.185462522522928</v>
+        <v>0.1856949085453079</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4629203633065319</v>
+        <v>0.4559064184079481</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1773414029361905</v>
+        <v>0.1788914029361905</v>
       </c>
       <c r="C68">
-        <v>-2140.649943031114</v>
+        <v>-2368.49226636274</v>
       </c>
       <c r="D68">
-        <v>7493.126056968884</v>
+        <v>7429.919733637259</v>
       </c>
       <c r="E68">
-        <v>2309.676000000001</v>
+        <v>2474.312000000002</v>
       </c>
       <c r="F68">
-        <v>10865.976</v>
+        <v>11030.612</v>
       </c>
       <c r="G68">
         <v>1232.2</v>
@@ -6863,37 +6863,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M68">
-        <v>2181.8879808</v>
+        <v>2214.9468896</v>
       </c>
       <c r="N68">
-        <v>-1187.151246106122</v>
+        <v>-1220.210154906122</v>
       </c>
       <c r="O68">
-        <v>-195.8799556075101</v>
+        <v>-201.3346755595102</v>
       </c>
       <c r="P68">
-        <v>-991.2712904986118</v>
+        <v>-1018.875479346612</v>
       </c>
       <c r="Q68">
-        <v>580.8287095013881</v>
+        <v>553.2245206533879</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1611257744008451</v>
+        <v>0.1646204948372343</v>
       </c>
       <c r="T68">
-        <v>2.247913998823481</v>
+        <v>2.316032604848435</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.07522455903731144</v>
+        <v>0.07410180442481425</v>
       </c>
       <c r="W68">
-        <v>0.1856949085453079</v>
+        <v>0.1859203576714973</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4559064184079481</v>
+        <v>0.4491018449988742</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1788914029361905</v>
+        <v>0.1804414029361905</v>
       </c>
       <c r="C69">
-        <v>-2368.49226636274</v>
+        <v>-2595.27718800581</v>
       </c>
       <c r="D69">
-        <v>7429.919733637259</v>
+        <v>7367.77081199419</v>
       </c>
       <c r="E69">
-        <v>2474.312000000002</v>
+        <v>2638.948000000002</v>
       </c>
       <c r="F69">
-        <v>11030.612</v>
+        <v>11195.248</v>
       </c>
       <c r="G69">
         <v>1232.2</v>
@@ -6945,37 +6945,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M69">
-        <v>2214.9468896</v>
+        <v>2248.0057984</v>
       </c>
       <c r="N69">
-        <v>-1220.210154906122</v>
+        <v>-1253.269063706122</v>
       </c>
       <c r="O69">
-        <v>-201.3346755595102</v>
+        <v>-206.7893955115102</v>
       </c>
       <c r="P69">
-        <v>-1018.875479346612</v>
+        <v>-1046.479668194612</v>
       </c>
       <c r="Q69">
-        <v>553.2245206533879</v>
+        <v>525.6203318053879</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1646204948372343</v>
+        <v>0.1683336353008979</v>
       </c>
       <c r="T69">
-        <v>2.316032604848435</v>
+        <v>2.388408623749949</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.07410180442481425</v>
+        <v>0.07301207200680226</v>
       </c>
       <c r="W69">
-        <v>0.1859203576714973</v>
+        <v>0.1861391759410341</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4491018449988742</v>
+        <v>0.4424974061018319</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1804414029361905</v>
+        <v>0.1819914029361905</v>
       </c>
       <c r="C70">
-        <v>-2595.27718800581</v>
+        <v>-2821.031022337987</v>
       </c>
       <c r="D70">
-        <v>7367.77081199419</v>
+        <v>7306.652977662012</v>
       </c>
       <c r="E70">
-        <v>2638.948000000002</v>
+        <v>2803.584000000003</v>
       </c>
       <c r="F70">
-        <v>11195.248</v>
+        <v>11359.884</v>
       </c>
       <c r="G70">
         <v>1232.2</v>
@@ -7027,37 +7027,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M70">
-        <v>2248.0057984</v>
+        <v>2281.0647072</v>
       </c>
       <c r="N70">
-        <v>-1253.269063706122</v>
+        <v>-1286.327972506122</v>
       </c>
       <c r="O70">
-        <v>-206.7893955115102</v>
+        <v>-212.2441154635102</v>
       </c>
       <c r="P70">
-        <v>-1046.479668194612</v>
+        <v>-1074.083857042612</v>
       </c>
       <c r="Q70">
-        <v>525.6203318053879</v>
+        <v>498.0161429573877</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1683336353008979</v>
+        <v>0.1722863332138301</v>
       </c>
       <c r="T70">
-        <v>2.388408623749949</v>
+        <v>2.465454063225754</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.07301207200680226</v>
+        <v>0.07195392603568919</v>
       </c>
       <c r="W70">
-        <v>0.1861391759410341</v>
+        <v>0.1863516516520336</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4424974061018319</v>
+        <v>0.4360844002162981</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1819914029361905</v>
+        <v>0.1835414029361905</v>
       </c>
       <c r="C71">
-        <v>-2821.031022337987</v>
+        <v>-3045.779217778188</v>
       </c>
       <c r="D71">
-        <v>7306.652977662012</v>
+        <v>7246.540782221812</v>
       </c>
       <c r="E71">
-        <v>2803.584000000003</v>
+        <v>2968.220000000003</v>
       </c>
       <c r="F71">
-        <v>11359.884</v>
+        <v>11524.52</v>
       </c>
       <c r="G71">
         <v>1232.2</v>
@@ -7109,37 +7109,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M71">
-        <v>2281.0647072</v>
+        <v>2314.123616</v>
       </c>
       <c r="N71">
-        <v>-1286.327972506122</v>
+        <v>-1319.386881306123</v>
       </c>
       <c r="O71">
-        <v>-212.2441154635102</v>
+        <v>-217.6988354155102</v>
       </c>
       <c r="P71">
-        <v>-1074.083857042612</v>
+        <v>-1101.688045890612</v>
       </c>
       <c r="Q71">
-        <v>498.0161429573877</v>
+        <v>470.4119541093876</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1722863332138301</v>
+        <v>0.1765025443209577</v>
       </c>
       <c r="T71">
-        <v>2.465454063225754</v>
+        <v>2.547635865333279</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.07195392603568919</v>
+        <v>0.0709260128066079</v>
       </c>
       <c r="W71">
-        <v>0.1863516516520336</v>
+        <v>0.1865580566284331</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4360844002162981</v>
+        <v>0.4298546230703509</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1835414029361905</v>
+        <v>0.1850914029361905</v>
       </c>
       <c r="C72">
-        <v>-3045.779217778188</v>
+        <v>-3269.54639211734</v>
       </c>
       <c r="D72">
-        <v>7246.540782221812</v>
+        <v>7187.409607882661</v>
       </c>
       <c r="E72">
-        <v>2968.220000000003</v>
+        <v>3132.856000000003</v>
       </c>
       <c r="F72">
-        <v>11524.52</v>
+        <v>11689.156</v>
       </c>
       <c r="G72">
         <v>1232.2</v>
@@ -7191,37 +7191,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M72">
-        <v>2314.123616</v>
+        <v>2347.1825248</v>
       </c>
       <c r="N72">
-        <v>-1319.386881306123</v>
+        <v>-1352.445790106123</v>
       </c>
       <c r="O72">
-        <v>-217.6988354155102</v>
+        <v>-223.1535553675103</v>
       </c>
       <c r="P72">
-        <v>-1101.688045890612</v>
+        <v>-1129.292234738612</v>
       </c>
       <c r="Q72">
-        <v>470.4119541093876</v>
+        <v>442.8077652613874</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1765025443209577</v>
+        <v>0.1810095286078873</v>
       </c>
       <c r="T72">
-        <v>2.547635865333279</v>
+        <v>2.635485377930979</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.0709260128066079</v>
+        <v>0.06992705487975427</v>
       </c>
       <c r="W72">
-        <v>0.1865580566284331</v>
+        <v>0.1867586473801454</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4298546230703509</v>
+        <v>0.4238003326045713</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1850914029361905</v>
+        <v>0.1866414029361905</v>
       </c>
       <c r="C73">
-        <v>-3269.546392117338</v>
+        <v>-3492.356366133365</v>
       </c>
       <c r="D73">
-        <v>7187.409607882661</v>
+        <v>7129.235633866632</v>
       </c>
       <c r="E73">
-        <v>3132.856000000002</v>
+        <v>3297.492</v>
       </c>
       <c r="F73">
-        <v>11689.156</v>
+        <v>11853.792</v>
       </c>
       <c r="G73">
         <v>1232.2</v>
@@ -7273,37 +7273,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M73">
-        <v>2347.1825248</v>
+        <v>2380.2414336</v>
       </c>
       <c r="N73">
-        <v>-1352.445790106122</v>
+        <v>-1385.504698906122</v>
       </c>
       <c r="O73">
-        <v>-223.1535553675102</v>
+        <v>-228.6082753195101</v>
       </c>
       <c r="P73">
-        <v>-1129.292234738612</v>
+        <v>-1156.896423586612</v>
       </c>
       <c r="Q73">
-        <v>442.8077652613879</v>
+        <v>415.203576413388</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1810095286078873</v>
+        <v>0.1858384403438833</v>
       </c>
       <c r="T73">
-        <v>2.635485377930978</v>
+        <v>2.729609855714227</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.06992705487975429</v>
+        <v>0.06895584578420215</v>
       </c>
       <c r="W73">
-        <v>0.1867586473801454</v>
+        <v>0.1869536661665322</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4238003326045714</v>
+        <v>0.4179142168739524</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1866414029361905</v>
+        <v>0.1881914029361905</v>
       </c>
       <c r="C74">
-        <v>-3492.356366133365</v>
+        <v>-3714.232195586828</v>
       </c>
       <c r="D74">
-        <v>7129.235633866632</v>
+        <v>7071.995804413169</v>
       </c>
       <c r="E74">
-        <v>3297.492</v>
+        <v>3462.128000000001</v>
       </c>
       <c r="F74">
-        <v>11853.792</v>
+        <v>12018.428</v>
       </c>
       <c r="G74">
         <v>1232.2</v>
@@ -7355,37 +7355,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M74">
-        <v>2380.2414336</v>
+        <v>2413.3003424</v>
       </c>
       <c r="N74">
-        <v>-1385.504698906122</v>
+        <v>-1418.563607706122</v>
       </c>
       <c r="O74">
-        <v>-228.6082753195101</v>
+        <v>-234.0629952715102</v>
       </c>
       <c r="P74">
-        <v>-1156.896423586612</v>
+        <v>-1184.500612434612</v>
       </c>
       <c r="Q74">
-        <v>415.203576413388</v>
+        <v>387.5993875653878</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1858384403438833</v>
+        <v>0.1910250492455086</v>
       </c>
       <c r="T74">
-        <v>2.729609855714227</v>
+        <v>2.830706517036976</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.06895584578420215</v>
+        <v>0.0680112451570213</v>
       </c>
       <c r="W74">
-        <v>0.1869536661665322</v>
+        <v>0.1871433419724701</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4179142168739524</v>
+        <v>0.4121893645880078</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1881914029361905</v>
+        <v>0.1897414029361905</v>
       </c>
       <c r="C75">
-        <v>-3714.232195586828</v>
+        <v>-3935.196201687502</v>
       </c>
       <c r="D75">
-        <v>7071.995804413169</v>
+        <v>7015.667798312496</v>
       </c>
       <c r="E75">
-        <v>3462.128000000001</v>
+        <v>3626.764000000001</v>
       </c>
       <c r="F75">
-        <v>12018.428</v>
+        <v>12183.064</v>
       </c>
       <c r="G75">
         <v>1232.2</v>
@@ -7437,37 +7437,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M75">
-        <v>2413.3003424</v>
+        <v>2446.3592512</v>
       </c>
       <c r="N75">
-        <v>-1418.563607706122</v>
+        <v>-1451.622516506122</v>
       </c>
       <c r="O75">
-        <v>-234.0629952715102</v>
+        <v>-239.5177152235101</v>
       </c>
       <c r="P75">
-        <v>-1184.500612434612</v>
+        <v>-1212.104801282612</v>
       </c>
       <c r="Q75">
-        <v>387.5993875653878</v>
+        <v>359.9951987173881</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1910250492455086</v>
+        <v>0.1966106280626435</v>
       </c>
       <c r="T75">
-        <v>2.830706517036976</v>
+        <v>2.939579844615321</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.0680112451570213</v>
+        <v>0.06709217427652102</v>
       </c>
       <c r="W75">
-        <v>0.1871433419724701</v>
+        <v>0.1873278914052746</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4121893645880078</v>
+        <v>0.4066192380395213</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1897414029361905</v>
+        <v>0.1912914029361905</v>
       </c>
       <c r="C76">
-        <v>-3935.196201687502</v>
+        <v>-4155.270000116463</v>
       </c>
       <c r="D76">
-        <v>7015.667798312496</v>
+        <v>6960.229999883535</v>
       </c>
       <c r="E76">
-        <v>3626.764000000001</v>
+        <v>3791.400000000001</v>
       </c>
       <c r="F76">
-        <v>12183.064</v>
+        <v>12347.7</v>
       </c>
       <c r="G76">
         <v>1232.2</v>
@@ -7519,37 +7519,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M76">
-        <v>2446.3592512</v>
+        <v>2479.41816</v>
       </c>
       <c r="N76">
-        <v>-1451.622516506122</v>
+        <v>-1484.681425306122</v>
       </c>
       <c r="O76">
-        <v>-239.5177152235101</v>
+        <v>-244.9724351755102</v>
       </c>
       <c r="P76">
-        <v>-1212.104801282612</v>
+        <v>-1239.708990130612</v>
       </c>
       <c r="Q76">
-        <v>359.9951987173881</v>
+        <v>332.391009869388</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1966106280626435</v>
+        <v>0.2026430531851493</v>
       </c>
       <c r="T76">
-        <v>2.939579844615321</v>
+        <v>3.057163038399934</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.06709217427652102</v>
+        <v>0.06619761195283407</v>
       </c>
       <c r="W76">
-        <v>0.1873278914052746</v>
+        <v>0.1875075195198709</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4066192380395213</v>
+        <v>0.4011976481989943</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1912914029361905</v>
+        <v>0.1928414029361905</v>
       </c>
       <c r="C77">
-        <v>-4155.270000116463</v>
+        <v>-4374.474528682998</v>
       </c>
       <c r="D77">
-        <v>6960.229999883535</v>
+        <v>6905.661471317001</v>
       </c>
       <c r="E77">
-        <v>3791.400000000001</v>
+        <v>3956.036000000002</v>
       </c>
       <c r="F77">
-        <v>12347.7</v>
+        <v>12512.336</v>
       </c>
       <c r="G77">
         <v>1232.2</v>
@@ -7601,37 +7601,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M77">
-        <v>2479.41816</v>
+        <v>2512.4770688</v>
       </c>
       <c r="N77">
-        <v>-1484.681425306122</v>
+        <v>-1517.740334106122</v>
       </c>
       <c r="O77">
-        <v>-244.9724351755102</v>
+        <v>-250.4271551275102</v>
       </c>
       <c r="P77">
-        <v>-1239.708990130612</v>
+        <v>-1267.313178978612</v>
       </c>
       <c r="Q77">
-        <v>332.391009869388</v>
+        <v>304.7868210213878</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2026430531851493</v>
+        <v>0.2091781804011972</v>
       </c>
       <c r="T77">
-        <v>3.057163038399934</v>
+        <v>3.184544831666599</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.06619761195283407</v>
+        <v>0.06532659074292835</v>
       </c>
       <c r="W77">
-        <v>0.1875075195198709</v>
+        <v>0.18768242057882</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4011976481989943</v>
+        <v>0.3959187317753233</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1928414029361905</v>
+        <v>0.1943914029361905</v>
       </c>
       <c r="C78">
-        <v>-4374.474528682998</v>
+        <v>-4592.830073690605</v>
       </c>
       <c r="D78">
-        <v>6905.661471317001</v>
+        <v>6851.941926309395</v>
       </c>
       <c r="E78">
-        <v>3956.036000000002</v>
+        <v>4120.672000000002</v>
       </c>
       <c r="F78">
-        <v>12512.336</v>
+        <v>12676.972</v>
       </c>
       <c r="G78">
         <v>1232.2</v>
@@ -7683,37 +7683,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M78">
-        <v>2512.4770688</v>
+        <v>2545.5359776</v>
       </c>
       <c r="N78">
-        <v>-1517.740334106122</v>
+        <v>-1550.799242906122</v>
       </c>
       <c r="O78">
-        <v>-250.4271551275102</v>
+        <v>-255.8818750795102</v>
       </c>
       <c r="P78">
-        <v>-1267.313178978612</v>
+        <v>-1294.917367826612</v>
       </c>
       <c r="Q78">
-        <v>304.7868210213878</v>
+        <v>277.1826321733877</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2091781804011972</v>
+        <v>0.2162815795490753</v>
       </c>
       <c r="T78">
-        <v>3.184544831666599</v>
+        <v>3.323003302608624</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.06532659074292835</v>
+        <v>0.06447819346055265</v>
       </c>
       <c r="W78">
-        <v>0.18768242057882</v>
+        <v>0.187852778753121</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3959187317753233</v>
+        <v>0.3907769300639554</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1943914029361905</v>
+        <v>0.1959414029361905</v>
       </c>
       <c r="C79">
-        <v>-4592.830073690605</v>
+        <v>-4810.356295081915</v>
       </c>
       <c r="D79">
-        <v>6851.941926309395</v>
+        <v>6799.051704918085</v>
       </c>
       <c r="E79">
-        <v>4120.672000000002</v>
+        <v>4285.308000000003</v>
       </c>
       <c r="F79">
-        <v>12676.972</v>
+        <v>12841.608</v>
       </c>
       <c r="G79">
         <v>1232.2</v>
@@ -7765,37 +7765,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M79">
-        <v>2545.5359776</v>
+        <v>2578.5948864</v>
       </c>
       <c r="N79">
-        <v>-1550.799242906122</v>
+        <v>-1583.858151706122</v>
       </c>
       <c r="O79">
-        <v>-255.8818750795102</v>
+        <v>-261.3365950315102</v>
       </c>
       <c r="P79">
-        <v>-1294.917367826612</v>
+        <v>-1322.521556674612</v>
       </c>
       <c r="Q79">
-        <v>277.1826321733877</v>
+        <v>249.5784433253875</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2162815795490753</v>
+        <v>0.2240307422558515</v>
       </c>
       <c r="T79">
-        <v>3.323003302608624</v>
+        <v>3.474048907272653</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.06447819346055265</v>
+        <v>0.06365154995464813</v>
       </c>
       <c r="W79">
-        <v>0.187852778753121</v>
+        <v>0.1880187687691066</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3907769300639554</v>
+        <v>0.3857669694221099</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1959414029361905</v>
+        <v>0.1974914029361905</v>
       </c>
       <c r="C80">
-        <v>-4810.356295081915</v>
+        <v>-5027.072250427943</v>
       </c>
       <c r="D80">
-        <v>6799.051704918085</v>
+        <v>6746.971749572056</v>
       </c>
       <c r="E80">
-        <v>4285.308000000003</v>
+        <v>4449.944000000001</v>
       </c>
       <c r="F80">
-        <v>12841.608</v>
+        <v>13006.244</v>
       </c>
       <c r="G80">
         <v>1232.2</v>
@@ -7847,37 +7847,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M80">
-        <v>2578.5948864</v>
+        <v>2611.6537952</v>
       </c>
       <c r="N80">
-        <v>-1583.858151706122</v>
+        <v>-1616.917060506122</v>
       </c>
       <c r="O80">
-        <v>-261.3365950315102</v>
+        <v>-266.7913149835102</v>
       </c>
       <c r="P80">
-        <v>-1322.521556674612</v>
+        <v>-1350.125745522612</v>
       </c>
       <c r="Q80">
-        <v>249.5784433253875</v>
+        <v>221.9742544773878</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2240307422558515</v>
+        <v>0.2325179204585111</v>
       </c>
       <c r="T80">
-        <v>3.474048907272653</v>
+        <v>3.63947980761897</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.06365154995464813</v>
+        <v>0.0628458341324374</v>
       </c>
       <c r="W80">
-        <v>0.1880187687691066</v>
+        <v>0.1881805565062066</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3857669694221099</v>
+        <v>0.3808838432268933</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1974914029361905</v>
+        <v>0.1990414029361905</v>
       </c>
       <c r="C81">
-        <v>-5027.072250427943</v>
+        <v>-5242.996417823209</v>
       </c>
       <c r="D81">
-        <v>6746.971749572056</v>
+        <v>6695.683582176791</v>
       </c>
       <c r="E81">
-        <v>4449.944000000001</v>
+        <v>4614.580000000002</v>
       </c>
       <c r="F81">
-        <v>13006.244</v>
+        <v>13170.88</v>
       </c>
       <c r="G81">
         <v>1232.2</v>
@@ -7929,37 +7929,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M81">
-        <v>2611.6537952</v>
+        <v>2644.712704</v>
       </c>
       <c r="N81">
-        <v>-1616.917060506122</v>
+        <v>-1649.975969306122</v>
       </c>
       <c r="O81">
-        <v>-266.7913149835102</v>
+        <v>-272.2460349355102</v>
       </c>
       <c r="P81">
-        <v>-1350.125745522612</v>
+        <v>-1377.729934370612</v>
       </c>
       <c r="Q81">
-        <v>221.9742544773878</v>
+        <v>194.3700656293877</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2325179204585111</v>
+        <v>0.2418538164814366</v>
       </c>
       <c r="T81">
-        <v>3.63947980761897</v>
+        <v>3.821453797999919</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.0628458341324374</v>
+        <v>0.06206026120578192</v>
       </c>
       <c r="W81">
-        <v>0.1881805565062066</v>
+        <v>0.188338299549879</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3808838432268933</v>
+        <v>0.3761227951865571</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1990414029361905</v>
+        <v>0.2005914029361905</v>
       </c>
       <c r="C82">
-        <v>-5242.996417823209</v>
+        <v>-5458.146717744475</v>
       </c>
       <c r="D82">
-        <v>6695.683582176791</v>
+        <v>6645.169282255525</v>
       </c>
       <c r="E82">
-        <v>4614.580000000002</v>
+        <v>4779.216000000002</v>
       </c>
       <c r="F82">
-        <v>13170.88</v>
+        <v>13335.516</v>
       </c>
       <c r="G82">
         <v>1232.2</v>
@@ -8011,37 +8011,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M82">
-        <v>2644.712704</v>
+        <v>2677.7716128</v>
       </c>
       <c r="N82">
-        <v>-1649.975969306122</v>
+        <v>-1683.034878106123</v>
       </c>
       <c r="O82">
-        <v>-272.2460349355102</v>
+        <v>-277.7007548875102</v>
       </c>
       <c r="P82">
-        <v>-1377.729934370612</v>
+        <v>-1405.334123218612</v>
       </c>
       <c r="Q82">
-        <v>194.3700656293877</v>
+        <v>166.7658767813878</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2418538164814366</v>
+        <v>0.2521724384015122</v>
       </c>
       <c r="T82">
-        <v>3.821453797999919</v>
+        <v>4.022582945263072</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.06206026120578192</v>
+        <v>0.06129408514151301</v>
       </c>
       <c r="W82">
-        <v>0.188338299549879</v>
+        <v>0.1884921477035842</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3761227951865571</v>
+        <v>0.3714793038879576</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2005914029361905</v>
+        <v>0.2021414029361905</v>
       </c>
       <c r="C83">
-        <v>-5458.146717744475</v>
+        <v>-5672.540533927457</v>
       </c>
       <c r="D83">
-        <v>6645.169282255525</v>
+        <v>6595.411466072544</v>
       </c>
       <c r="E83">
-        <v>4779.216000000002</v>
+        <v>4943.852000000003</v>
       </c>
       <c r="F83">
-        <v>13335.516</v>
+        <v>13500.152</v>
       </c>
       <c r="G83">
         <v>1232.2</v>
@@ -8093,37 +8093,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M83">
-        <v>2677.7716128</v>
+        <v>2710.8305216</v>
       </c>
       <c r="N83">
-        <v>-1683.034878106123</v>
+        <v>-1716.093786906122</v>
       </c>
       <c r="O83">
-        <v>-277.7007548875102</v>
+        <v>-283.1554748395102</v>
       </c>
       <c r="P83">
-        <v>-1405.334123218612</v>
+        <v>-1432.938312066612</v>
       </c>
       <c r="Q83">
-        <v>166.7658767813878</v>
+        <v>139.1616879333878</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2521724384015122</v>
+        <v>0.2636375738682629</v>
       </c>
       <c r="T83">
-        <v>4.022582945263072</v>
+        <v>4.246059775555466</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.06129408514151301</v>
+        <v>0.06054659629832383</v>
       </c>
       <c r="W83">
-        <v>0.1884921477035842</v>
+        <v>0.1886422434632966</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3714793038879576</v>
+        <v>0.3669490684746899</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2021414029361905</v>
+        <v>0.2036914029361905</v>
       </c>
       <c r="C84">
-        <v>-5672.540533927457</v>
+        <v>-5886.194733312555</v>
       </c>
       <c r="D84">
-        <v>6595.411466072544</v>
+        <v>6546.393266687445</v>
       </c>
       <c r="E84">
-        <v>4943.852000000003</v>
+        <v>5108.488000000003</v>
       </c>
       <c r="F84">
-        <v>13500.152</v>
+        <v>13664.788</v>
       </c>
       <c r="G84">
         <v>1232.2</v>
@@ -8175,37 +8175,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M84">
-        <v>2710.8305216</v>
+        <v>2743.8894304</v>
       </c>
       <c r="N84">
-        <v>-1716.093786906122</v>
+        <v>-1749.152695706122</v>
       </c>
       <c r="O84">
-        <v>-283.1554748395102</v>
+        <v>-288.6101947915102</v>
       </c>
       <c r="P84">
-        <v>-1432.938312066612</v>
+        <v>-1460.542500914612</v>
       </c>
       <c r="Q84">
-        <v>139.1616879333878</v>
+        <v>111.5574990853877</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2636375738682629</v>
+        <v>0.2764515488016902</v>
       </c>
       <c r="T84">
-        <v>4.246059775555466</v>
+        <v>4.495827997646964</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.06054659629832383</v>
+        <v>0.0598171192344886</v>
       </c>
       <c r="W84">
-        <v>0.1886422434632966</v>
+        <v>0.1887887224577147</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3669490684746899</v>
+        <v>0.362527995360537</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2036914029361905</v>
+        <v>0.2052414029361905</v>
       </c>
       <c r="C85">
-        <v>-5886.194733312555</v>
+        <v>-6099.125685107739</v>
       </c>
       <c r="D85">
-        <v>6546.393266687445</v>
+        <v>6498.098314892262</v>
       </c>
       <c r="E85">
-        <v>5108.488000000003</v>
+        <v>5273.124000000003</v>
       </c>
       <c r="F85">
-        <v>13664.788</v>
+        <v>13829.424</v>
       </c>
       <c r="G85">
         <v>1232.2</v>
@@ -8257,37 +8257,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M85">
-        <v>2743.8894304</v>
+        <v>2776.9483392</v>
       </c>
       <c r="N85">
-        <v>-1749.152695706122</v>
+        <v>-1782.211604506123</v>
       </c>
       <c r="O85">
-        <v>-288.6101947915102</v>
+        <v>-294.0649147435102</v>
       </c>
       <c r="P85">
-        <v>-1460.542500914612</v>
+        <v>-1488.146689762612</v>
       </c>
       <c r="Q85">
-        <v>111.5574990853877</v>
+        <v>83.95331023738754</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2764515488016902</v>
+        <v>0.2908672706017958</v>
       </c>
       <c r="T85">
-        <v>4.495827997646964</v>
+        <v>4.7768172474999</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.0598171192344886</v>
+        <v>0.05910501067217326</v>
       </c>
       <c r="W85">
-        <v>0.1887887224577147</v>
+        <v>0.1889317138570276</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.362527995360537</v>
+        <v>0.3582121858919591</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2052414029361905</v>
+        <v>0.2067914029361905</v>
       </c>
       <c r="C86">
-        <v>-6099.125685107735</v>
+        <v>-6311.349279013771</v>
       </c>
       <c r="D86">
-        <v>6498.098314892264</v>
+        <v>6450.510720986227</v>
       </c>
       <c r="E86">
-        <v>5273.124000000002</v>
+        <v>5437.76</v>
       </c>
       <c r="F86">
-        <v>13829.424</v>
+        <v>13994.06</v>
       </c>
       <c r="G86">
         <v>1232.2</v>
@@ -8339,37 +8339,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M86">
-        <v>2776.9483392</v>
+        <v>2810.007247999999</v>
       </c>
       <c r="N86">
-        <v>-1782.211604506122</v>
+        <v>-1815.270513306122</v>
       </c>
       <c r="O86">
-        <v>-294.0649147435101</v>
+        <v>-299.5196346955101</v>
       </c>
       <c r="P86">
-        <v>-1488.146689762612</v>
+        <v>-1515.750878610612</v>
       </c>
       <c r="Q86">
-        <v>83.953310237388</v>
+        <v>56.3491213893883</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2908672706017957</v>
+        <v>0.3072050886419154</v>
       </c>
       <c r="T86">
-        <v>4.776817247499896</v>
+        <v>5.095271730666557</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.05910501067217327</v>
+        <v>0.05840965760544183</v>
       </c>
       <c r="W86">
-        <v>0.1889317138570276</v>
+        <v>0.1890713407528273</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3582121858919592</v>
+        <v>0.3539979248814656</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2067914029361905</v>
+        <v>0.2083414029361905</v>
       </c>
       <c r="C87">
-        <v>-6311.349279013771</v>
+        <v>-6522.880942654496</v>
       </c>
       <c r="D87">
-        <v>6450.510720986227</v>
+        <v>6403.615057345502</v>
       </c>
       <c r="E87">
-        <v>5437.76</v>
+        <v>5602.396000000001</v>
       </c>
       <c r="F87">
-        <v>13994.06</v>
+        <v>14158.696</v>
       </c>
       <c r="G87">
         <v>1232.2</v>
@@ -8421,37 +8421,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M87">
-        <v>2810.007247999999</v>
+        <v>2843.0661568</v>
       </c>
       <c r="N87">
-        <v>-1815.270513306122</v>
+        <v>-1848.329422106122</v>
       </c>
       <c r="O87">
-        <v>-299.5196346955101</v>
+        <v>-304.9743546475102</v>
       </c>
       <c r="P87">
-        <v>-1515.750878610612</v>
+        <v>-1543.355067458612</v>
       </c>
       <c r="Q87">
-        <v>56.3491213893883</v>
+        <v>28.74493254138815</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3072050886419154</v>
+        <v>0.3258768806877665</v>
       </c>
       <c r="T87">
-        <v>5.095271730666557</v>
+        <v>5.459219711428454</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.05840965760544183</v>
+        <v>0.05773047554026226</v>
       </c>
       <c r="W87">
-        <v>0.1890713407528273</v>
+        <v>0.1892077205115154</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3539979248814656</v>
+        <v>0.3498816699409835</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2083414029361905</v>
+        <v>0.2098914029361905</v>
       </c>
       <c r="C88">
-        <v>-6522.880942654496</v>
+        <v>-6733.735658252224</v>
       </c>
       <c r="D88">
-        <v>6403.615057345502</v>
+        <v>6357.396341747774</v>
       </c>
       <c r="E88">
-        <v>5602.396000000001</v>
+        <v>5767.032000000001</v>
       </c>
       <c r="F88">
-        <v>14158.696</v>
+        <v>14323.332</v>
       </c>
       <c r="G88">
         <v>1232.2</v>
@@ -8503,37 +8503,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M88">
-        <v>2843.0661568</v>
+        <v>2876.1250656</v>
       </c>
       <c r="N88">
-        <v>-1848.329422106122</v>
+        <v>-1881.388330906122</v>
       </c>
       <c r="O88">
-        <v>-304.9743546475102</v>
+        <v>-310.4290745995102</v>
       </c>
       <c r="P88">
-        <v>-1543.355067458612</v>
+        <v>-1570.959256306612</v>
       </c>
       <c r="Q88">
-        <v>28.74493254138815</v>
+        <v>1.140743693388004</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3258768806877665</v>
+        <v>0.347421256125287</v>
       </c>
       <c r="T88">
-        <v>5.459219711428454</v>
+        <v>5.879159689230642</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.05773047554026226</v>
+        <v>0.05706690685589143</v>
       </c>
       <c r="W88">
-        <v>0.1892077205115154</v>
+        <v>0.189340965103337</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3498816699409835</v>
+        <v>0.3458600415508571</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2098914029361905</v>
+        <v>0.2114414029361905</v>
       </c>
       <c r="C89">
-        <v>-6733.735658252224</v>
+        <v>-6943.92797858623</v>
       </c>
       <c r="D89">
-        <v>6357.396341747774</v>
+        <v>6311.840021413769</v>
       </c>
       <c r="E89">
-        <v>5767.032000000001</v>
+        <v>5931.668000000001</v>
       </c>
       <c r="F89">
-        <v>14323.332</v>
+        <v>14487.968</v>
       </c>
       <c r="G89">
         <v>1232.2</v>
@@ -8585,37 +8585,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M89">
-        <v>2876.1250656</v>
+        <v>2909.1839744</v>
       </c>
       <c r="N89">
-        <v>-1881.388330906122</v>
+        <v>-1914.447239706122</v>
       </c>
       <c r="O89">
-        <v>-310.4290745995102</v>
+        <v>-315.8837945515102</v>
       </c>
       <c r="P89">
-        <v>-1570.959256306612</v>
+        <v>-1598.563445154612</v>
       </c>
       <c r="Q89">
-        <v>1.140743693388004</v>
+        <v>-26.46344515461215</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.347421256125287</v>
+        <v>0.3725563608023943</v>
       </c>
       <c r="T89">
-        <v>5.879159689230642</v>
+        <v>6.369089663333197</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.05706690685589143</v>
+        <v>0.05641841927798358</v>
       </c>
       <c r="W89">
-        <v>0.189340965103337</v>
+        <v>0.1894711814089809</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3458600415508571</v>
+        <v>0.341929813805961</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2114414029361905</v>
+        <v>0.2129914029361905</v>
       </c>
       <c r="C90">
-        <v>-6943.92797858623</v>
+        <v>-7153.472042269936</v>
       </c>
       <c r="D90">
-        <v>6311.840021413769</v>
+        <v>6266.931957730064</v>
       </c>
       <c r="E90">
-        <v>5931.668000000001</v>
+        <v>6096.304000000002</v>
       </c>
       <c r="F90">
-        <v>14487.968</v>
+        <v>14652.604</v>
       </c>
       <c r="G90">
         <v>1232.2</v>
@@ -8667,37 +8667,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M90">
-        <v>2909.1839744</v>
+        <v>2942.2428832</v>
       </c>
       <c r="N90">
-        <v>-1914.447239706122</v>
+        <v>-1947.506148506122</v>
       </c>
       <c r="O90">
-        <v>-315.8837945515102</v>
+        <v>-321.3385145035102</v>
       </c>
       <c r="P90">
-        <v>-1598.563445154612</v>
+        <v>-1626.167634002612</v>
       </c>
       <c r="Q90">
-        <v>-26.46344515461215</v>
+        <v>-54.06763400261229</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3725563608023943</v>
+        <v>0.4022614845117029</v>
       </c>
       <c r="T90">
-        <v>6.369089663333197</v>
+        <v>6.948097814545306</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.05641841927798358</v>
+        <v>0.05578450445463544</v>
       </c>
       <c r="W90">
-        <v>0.1894711814089809</v>
+        <v>0.1895984715055092</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.341929813805961</v>
+        <v>0.3380879057856693</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2129914029361905</v>
+        <v>0.2145414029361905</v>
       </c>
       <c r="C91">
-        <v>-7153.472042269936</v>
+        <v>-7362.381588380564</v>
       </c>
       <c r="D91">
-        <v>6266.931957730064</v>
+        <v>6222.658411619436</v>
       </c>
       <c r="E91">
-        <v>6096.304000000002</v>
+        <v>6260.940000000002</v>
       </c>
       <c r="F91">
-        <v>14652.604</v>
+        <v>14817.24</v>
       </c>
       <c r="G91">
         <v>1232.2</v>
@@ -8749,37 +8749,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M91">
-        <v>2942.2428832</v>
+        <v>2975.301792</v>
       </c>
       <c r="N91">
-        <v>-1947.506148506122</v>
+        <v>-1980.565057306123</v>
       </c>
       <c r="O91">
-        <v>-321.3385145035102</v>
+        <v>-326.7932344555102</v>
       </c>
       <c r="P91">
-        <v>-1626.167634002612</v>
+        <v>-1653.771822850612</v>
       </c>
       <c r="Q91">
-        <v>-54.06763400261229</v>
+        <v>-81.67182285061244</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4022614845117029</v>
+        <v>0.4379076329628732</v>
       </c>
       <c r="T91">
-        <v>6.948097814545306</v>
+        <v>7.642907595999837</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.05578450445463544</v>
+        <v>0.05516467662736171</v>
       </c>
       <c r="W91">
-        <v>0.1895984715055092</v>
+        <v>0.1897229329332258</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3380879057856693</v>
+        <v>0.3343313734991619</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2145414029361905</v>
+        <v>0.2160914029361905</v>
       </c>
       <c r="C92">
-        <v>-7362.381588380564</v>
+        <v>-7570.669970472992</v>
       </c>
       <c r="D92">
-        <v>6222.658411619436</v>
+        <v>6179.006029527007</v>
       </c>
       <c r="E92">
-        <v>6260.940000000002</v>
+        <v>6425.576000000001</v>
       </c>
       <c r="F92">
-        <v>14817.24</v>
+        <v>14981.876</v>
       </c>
       <c r="G92">
         <v>1232.2</v>
@@ -8831,37 +8831,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M92">
-        <v>2975.301792</v>
+        <v>3008.3607008</v>
       </c>
       <c r="N92">
-        <v>-1980.565057306123</v>
+        <v>-2013.623966106122</v>
       </c>
       <c r="O92">
-        <v>-326.7932344555102</v>
+        <v>-332.2479544075102</v>
       </c>
       <c r="P92">
-        <v>-1653.771822850612</v>
+        <v>-1681.376011698612</v>
       </c>
       <c r="Q92">
-        <v>-81.67182285061244</v>
+        <v>-109.2760116986121</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4379076329628732</v>
+        <v>0.4814751477365259</v>
       </c>
       <c r="T92">
-        <v>7.642907595999837</v>
+        <v>8.492119551110932</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.05516467662736171</v>
+        <v>0.0545584713896984</v>
       </c>
       <c r="W92">
-        <v>0.1897229329332258</v>
+        <v>0.1898446589449486</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3343313734991619</v>
+        <v>0.3306574023618085</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2160914029361905</v>
+        <v>0.2176414029361905</v>
       </c>
       <c r="C93">
-        <v>-7570.669970472992</v>
+        <v>-7778.35017000791</v>
       </c>
       <c r="D93">
-        <v>6179.006029527007</v>
+        <v>6135.961829992088</v>
       </c>
       <c r="E93">
-        <v>6425.576000000001</v>
+        <v>6590.212000000001</v>
       </c>
       <c r="F93">
-        <v>14981.876</v>
+        <v>15146.512</v>
       </c>
       <c r="G93">
         <v>1232.2</v>
@@ -8913,37 +8913,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M93">
-        <v>3008.3607008</v>
+        <v>3041.4196096</v>
       </c>
       <c r="N93">
-        <v>-2013.623966106122</v>
+        <v>-2046.682874906122</v>
       </c>
       <c r="O93">
-        <v>-332.2479544075102</v>
+        <v>-337.7026743595102</v>
       </c>
       <c r="P93">
-        <v>-1681.376011698612</v>
+        <v>-1708.980200546612</v>
       </c>
       <c r="Q93">
-        <v>-109.2760116986121</v>
+        <v>-136.8802005466123</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4814751477365259</v>
+        <v>0.5359345412035916</v>
       </c>
       <c r="T93">
-        <v>8.492119551110932</v>
+        <v>9.5536344949998</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.0545584713896984</v>
+        <v>0.05396544452676689</v>
       </c>
       <c r="W93">
-        <v>0.1898446589449486</v>
+        <v>0.1899637387390252</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3306574023618085</v>
+        <v>0.3270633001622236</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2176414029361905</v>
+        <v>0.2191914029361905</v>
       </c>
       <c r="C94">
-        <v>-7778.35017000791</v>
+        <v>-7985.434809222547</v>
       </c>
       <c r="D94">
-        <v>6135.961829992088</v>
+        <v>6093.513190777452</v>
       </c>
       <c r="E94">
-        <v>6590.212000000001</v>
+        <v>6754.848000000002</v>
       </c>
       <c r="F94">
-        <v>15146.512</v>
+        <v>15311.148</v>
       </c>
       <c r="G94">
         <v>1232.2</v>
@@ -8995,37 +8995,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M94">
-        <v>3041.4196096</v>
+        <v>3074.4785184</v>
       </c>
       <c r="N94">
-        <v>-2046.682874906122</v>
+        <v>-2079.741783706122</v>
       </c>
       <c r="O94">
-        <v>-337.7026743595102</v>
+        <v>-343.1573943115101</v>
       </c>
       <c r="P94">
-        <v>-1708.980200546612</v>
+        <v>-1736.584389394612</v>
       </c>
       <c r="Q94">
-        <v>-136.8802005466123</v>
+        <v>-164.484389394612</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5359345412035916</v>
+        <v>0.6059537613755334</v>
       </c>
       <c r="T94">
-        <v>9.5536344949998</v>
+        <v>10.91843942285692</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.05396544452676689</v>
+        <v>0.05338517092970489</v>
       </c>
       <c r="W94">
-        <v>0.1899637387390252</v>
+        <v>0.1900802576773153</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3270633001622236</v>
+        <v>0.3235464904830599</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2191914029361905</v>
+        <v>0.2207414029361905</v>
       </c>
       <c r="C95">
-        <v>-7985.434809222547</v>
+        <v>-8191.936163470887</v>
       </c>
       <c r="D95">
-        <v>6093.513190777452</v>
+        <v>6051.647836529113</v>
       </c>
       <c r="E95">
-        <v>6754.848000000002</v>
+        <v>6919.484000000002</v>
       </c>
       <c r="F95">
-        <v>15311.148</v>
+        <v>15475.784</v>
       </c>
       <c r="G95">
         <v>1232.2</v>
@@ -9077,37 +9077,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M95">
-        <v>3074.4785184</v>
+        <v>3107.5374272</v>
       </c>
       <c r="N95">
-        <v>-2079.741783706122</v>
+        <v>-2112.800692506122</v>
       </c>
       <c r="O95">
-        <v>-343.1573943115101</v>
+        <v>-348.6121142635102</v>
       </c>
       <c r="P95">
-        <v>-1736.584389394612</v>
+        <v>-1764.188578242612</v>
       </c>
       <c r="Q95">
-        <v>-164.484389394612</v>
+        <v>-192.0885782426121</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6059537613755334</v>
+        <v>0.6993127216047892</v>
       </c>
       <c r="T95">
-        <v>10.91843942285692</v>
+        <v>12.7381793266664</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.05338517092970489</v>
+        <v>0.05281724357938888</v>
       </c>
       <c r="W95">
-        <v>0.1900802576773153</v>
+        <v>0.1901942974892587</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3235464904830599</v>
+        <v>0.3201045065417507</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2207414029361905</v>
+        <v>0.2222914029361905</v>
       </c>
       <c r="C96">
-        <v>-8191.936163470887</v>
+        <v>-8397.866173058585</v>
       </c>
       <c r="D96">
-        <v>6051.647836529113</v>
+        <v>6010.353826941415</v>
       </c>
       <c r="E96">
-        <v>6919.484000000002</v>
+        <v>7084.120000000003</v>
       </c>
       <c r="F96">
-        <v>15475.784</v>
+        <v>15640.42</v>
       </c>
       <c r="G96">
         <v>1232.2</v>
@@ -9159,37 +9159,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M96">
-        <v>3107.5374272</v>
+        <v>3140.596336</v>
       </c>
       <c r="N96">
-        <v>-2112.800692506122</v>
+        <v>-2145.859601306122</v>
       </c>
       <c r="O96">
-        <v>-348.6121142635102</v>
+        <v>-354.0668342155102</v>
       </c>
       <c r="P96">
-        <v>-1764.188578242612</v>
+        <v>-1791.792767090612</v>
       </c>
       <c r="Q96">
-        <v>-192.0885782426121</v>
+        <v>-219.6927670906123</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6993127216047892</v>
+        <v>0.8300152659257474</v>
       </c>
       <c r="T96">
-        <v>12.7381793266664</v>
+        <v>15.28581519199969</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.05281724357938888</v>
+        <v>0.05226127259434268</v>
       </c>
       <c r="W96">
-        <v>0.1901942974892587</v>
+        <v>0.190305936463056</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3201045065417507</v>
+        <v>0.3167349854202586</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2222914029361905</v>
+        <v>0.2238414029361905</v>
       </c>
       <c r="C97">
-        <v>-8397.866173058585</v>
+        <v>-8603.236454596718</v>
       </c>
       <c r="D97">
-        <v>6010.353826941415</v>
+        <v>5969.619545403283</v>
       </c>
       <c r="E97">
-        <v>7084.120000000003</v>
+        <v>7248.756000000003</v>
       </c>
       <c r="F97">
-        <v>15640.42</v>
+        <v>15805.056</v>
       </c>
       <c r="G97">
         <v>1232.2</v>
@@ -9241,37 +9241,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M97">
-        <v>3140.596336</v>
+        <v>3173.6552448</v>
       </c>
       <c r="N97">
-        <v>-2145.859601306122</v>
+        <v>-2178.918510106123</v>
       </c>
       <c r="O97">
-        <v>-354.0668342155102</v>
+        <v>-359.5215541675103</v>
       </c>
       <c r="P97">
-        <v>-1791.792767090612</v>
+        <v>-1819.396955938612</v>
       </c>
       <c r="Q97">
-        <v>-219.6927670906123</v>
+        <v>-247.2969559386124</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8300152659257474</v>
+        <v>1.026069082407185</v>
       </c>
       <c r="T97">
-        <v>15.28581519199969</v>
+        <v>19.10726898999962</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.05226127259434268</v>
+        <v>0.0517168843381516</v>
       </c>
       <c r="W97">
-        <v>0.190305936463056</v>
+        <v>0.1904152496248992</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3167349854202586</v>
+        <v>0.3134356626554643</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2238414029361905</v>
+        <v>0.2253914029361905</v>
       </c>
       <c r="C98">
-        <v>-8603.236454596716</v>
+        <v>-8808.058311896864</v>
       </c>
       <c r="D98">
-        <v>5969.619545403283</v>
+        <v>5929.433688103133</v>
       </c>
       <c r="E98">
-        <v>7248.756000000001</v>
+        <v>7413.392</v>
       </c>
       <c r="F98">
-        <v>15805.056</v>
+        <v>15969.692</v>
       </c>
       <c r="G98">
         <v>1232.2</v>
@@ -9323,37 +9323,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M98">
-        <v>3173.6552448</v>
+        <v>3206.714153599999</v>
       </c>
       <c r="N98">
-        <v>-2178.918510106122</v>
+        <v>-2211.977418906122</v>
       </c>
       <c r="O98">
-        <v>-359.5215541675101</v>
+        <v>-364.9762741195101</v>
       </c>
       <c r="P98">
-        <v>-1819.396955938612</v>
+        <v>-1847.001144786612</v>
       </c>
       <c r="Q98">
-        <v>-247.296955938612</v>
+        <v>-274.9011447866119</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.026069082407182</v>
+        <v>1.352825443209576</v>
       </c>
       <c r="T98">
-        <v>19.10726898999958</v>
+        <v>25.47635865333276</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.05171688433815161</v>
+        <v>0.0511837205820882</v>
       </c>
       <c r="W98">
-        <v>0.1904152496248992</v>
+        <v>0.1905223089071167</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3134356626554643</v>
+        <v>0.3102043671641709</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2253914029361905</v>
+        <v>0.2269414029361905</v>
       </c>
       <c r="C99">
-        <v>-8808.058311896864</v>
+        <v>-9012.342746429142</v>
       </c>
       <c r="D99">
-        <v>5929.433688103133</v>
+        <v>5889.785253570855</v>
       </c>
       <c r="E99">
-        <v>7413.392</v>
+        <v>7578.028</v>
       </c>
       <c r="F99">
-        <v>15969.692</v>
+        <v>16134.328</v>
       </c>
       <c r="G99">
         <v>1232.2</v>
@@ -9405,37 +9405,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M99">
-        <v>3206.714153599999</v>
+        <v>3239.7730624</v>
       </c>
       <c r="N99">
-        <v>-2211.977418906122</v>
+        <v>-2245.036327706122</v>
       </c>
       <c r="O99">
-        <v>-364.9762741195101</v>
+        <v>-370.4309940715102</v>
       </c>
       <c r="P99">
-        <v>-1847.001144786612</v>
+        <v>-1874.605333634612</v>
       </c>
       <c r="Q99">
-        <v>-274.9011447866119</v>
+        <v>-302.5053336346118</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.352825443209576</v>
+        <v>2.006338164814364</v>
       </c>
       <c r="T99">
-        <v>25.47635865333276</v>
+        <v>38.21453797999914</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.0511837205820882</v>
+        <v>0.05066143771900566</v>
       </c>
       <c r="W99">
-        <v>0.1905223089071167</v>
+        <v>0.1906271833060237</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3102043671641709</v>
+        <v>0.3070390164788221</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2269414029361905</v>
+        <v>0.2284914029361905</v>
       </c>
       <c r="C100">
-        <v>-9012.342746429142</v>
+        <v>-9216.100467363392</v>
       </c>
       <c r="D100">
-        <v>5889.785253570855</v>
+        <v>5850.663532636606</v>
       </c>
       <c r="E100">
-        <v>7578.028</v>
+        <v>7742.664000000001</v>
       </c>
       <c r="F100">
-        <v>16134.328</v>
+        <v>16298.964</v>
       </c>
       <c r="G100">
         <v>1232.2</v>
@@ -9487,37 +9487,37 @@
         <v>994.7367346938777</v>
       </c>
       <c r="M100">
-        <v>3239.7730624</v>
+        <v>3272.8319712</v>
       </c>
       <c r="N100">
-        <v>-2245.036327706122</v>
+        <v>-2278.095236506122</v>
       </c>
       <c r="O100">
-        <v>-370.4309940715102</v>
+        <v>-375.8857140235102</v>
       </c>
       <c r="P100">
-        <v>-1874.605333634612</v>
+        <v>-1902.209522482612</v>
       </c>
       <c r="Q100">
-        <v>-302.5053336346118</v>
+        <v>-330.109522482612</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.006338164814364</v>
+        <v>3.966876329628727</v>
       </c>
       <c r="T100">
-        <v>38.21453797999914</v>
+        <v>76.42907595999829</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.05066143771900566</v>
+        <v>0.05014970602487429</v>
       </c>
       <c r="W100">
-        <v>0.1906271833060237</v>
+        <v>0.1907299390302052</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3070390164788221</v>
+        <v>0.3039376122719654</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2284914029361905</v>
-      </c>
-      <c r="C101">
-        <v>-9216.100467363392</v>
-      </c>
-      <c r="D101">
-        <v>5850.663532636606</v>
-      </c>
-      <c r="E101">
-        <v>7742.664000000001</v>
-      </c>
-      <c r="F101">
-        <v>16298.964</v>
-      </c>
-      <c r="G101">
-        <v>1232.2</v>
-      </c>
-      <c r="H101">
-        <v>7907.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2566.836734693878</v>
-      </c>
-      <c r="K101">
-        <v>1572.1</v>
-      </c>
-      <c r="L101">
-        <v>994.7367346938777</v>
-      </c>
-      <c r="M101">
-        <v>3272.8319712</v>
-      </c>
-      <c r="N101">
-        <v>-2278.095236506122</v>
-      </c>
-      <c r="O101">
-        <v>-375.8857140235102</v>
-      </c>
-      <c r="P101">
-        <v>-1902.209522482612</v>
-      </c>
-      <c r="Q101">
-        <v>-330.109522482612</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.966876329628727</v>
-      </c>
-      <c r="T101">
-        <v>76.42907595999829</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.05014970602487429</v>
-      </c>
-      <c r="W101">
-        <v>0.1907299390302052</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3039376122719654</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
